--- a/Regex 04.02.25.xlsx
+++ b/Regex 04.02.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="787" activeTab="13"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="787" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="1827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3188" uniqueCount="1829">
   <si>
     <t>with (?mx) with description</t>
   </si>
@@ -15347,6 +15347,12 @@
   </si>
   <si>
     <t xml:space="preserve">    "MI.04.02.99.04.0.02": "200 353 90",</t>
+  </si>
+  <si>
+    <t>\s+</t>
+  </si>
+  <si>
+    <t>includes: space, tab, newline, carriage return</t>
   </si>
 </sst>
 </file>
@@ -21925,17 +21931,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$B$54&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>$B$52&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$B$32=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22308,17 +22314,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="17" priority="7">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>$C$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="13" priority="8">
       <formula>$C$33&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="15" priority="9">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>$C$15=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22465,17 +22471,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>$B$53&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$B$51&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$B$33=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22613,17 +22619,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>$B$38&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="7" priority="11">
       <formula>$B$36&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="9" priority="12">
+    <cfRule type="expression" dxfId="6" priority="12">
       <formula>$B$16=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22636,7 +22642,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O363"/>
+  <dimension ref="A1:O367"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
@@ -22820,97 +22826,54 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="8" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="8" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="8"/>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="8" t="s">
+    <row r="36" spans="1:12">
+      <c r="A36" s="8"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B37" s="8" t="s">
         <v>1184</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D37" s="8" t="s">
         <v>1169</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F37" s="8" t="s">
         <v>1171</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J37" s="8" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
-      <c r="A34" t="s">
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
         <v>1166</v>
       </c>
-      <c r="B34" s="49" t="s">
+      <c r="B38" s="49" t="s">
         <v>1179</v>
       </c>
-      <c r="D34">
+      <c r="D38">
         <v>1</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F38" t="s">
         <v>29</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J38" t="s">
         <v>1180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B35" s="49" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="F35" t="s">
-        <v>29</v>
-      </c>
-      <c r="J35" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B36" s="49" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D36">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J36" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B37" s="49" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D37">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>29</v>
-      </c>
-      <c r="J37" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -22918,7 +22881,7 @@
         <v>1168</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -22927,7 +22890,7 @@
         <v>29</v>
       </c>
       <c r="J39" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -22935,19 +22898,16 @@
         <v>1174</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
         <v>29</v>
       </c>
       <c r="J40" t="s">
-        <v>1175</v>
-      </c>
-      <c r="L40" t="s">
-        <v>1189</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -22955,7 +22915,7 @@
         <v>1176</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -22964,649 +22924,682 @@
         <v>29</v>
       </c>
       <c r="J41" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B42" s="49" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B43" s="49" t="s">
         <v>1167</v>
       </c>
-      <c r="D42">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
         <v>29</v>
       </c>
-      <c r="J42" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="B43" s="49"/>
+      <c r="J43" t="s">
+        <v>1173</v>
+      </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>1185</v>
+        <v>1174</v>
       </c>
       <c r="B44" s="49" t="s">
         <v>1167</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F44" t="s">
         <v>29</v>
       </c>
       <c r="J44" t="s">
-        <v>1172</v>
+        <v>1175</v>
+      </c>
+      <c r="L44" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>1185</v>
+        <v>1176</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>1178</v>
+        <v>1167</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
         <v>29</v>
       </c>
       <c r="J45" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B46" s="49" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+      <c r="F46" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="B47" s="49"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B48" s="49" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="F48" t="s">
+        <v>29</v>
+      </c>
+      <c r="J48" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B49" s="49" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="F49" t="s">
+        <v>29</v>
+      </c>
+      <c r="J49" t="s">
         <v>1186</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
-      <c r="B46" s="49"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="10" t="s">
+    <row r="50" spans="1:10">
+      <c r="B50" s="49"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="10" t="s">
+    <row r="54" spans="1:10">
+      <c r="A54" s="10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="10"/>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24" t="s">
+    <row r="55" spans="1:10">
+      <c r="A55" s="10"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C56" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24" t="s">
+    <row r="57" spans="1:10">
+      <c r="A57" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C57" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24"/>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="8" t="s">
+    <row r="58" spans="1:10">
+      <c r="A58" s="24"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="8" t="s">
         <v>1148</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="8"/>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="8"/>
-      <c r="B57" t="s">
+    <row r="60" spans="1:10">
+      <c r="A60" s="8"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="8"/>
+      <c r="B61" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="8"/>
-      <c r="C58" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="8"/>
-      <c r="C59" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="8"/>
-      <c r="C60" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="8"/>
-    </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:10">
       <c r="A62" s="8"/>
       <c r="C62" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="8"/>
       <c r="C63" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="8"/>
+      <c r="C64" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="8"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="8"/>
+      <c r="C66" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="8"/>
+      <c r="C67" t="s">
         <v>1161</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="8"/>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24"/>
-      <c r="B65" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24"/>
-      <c r="C66" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24"/>
-      <c r="C67" t="s">
-        <v>1154</v>
-      </c>
-    </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="24"/>
-      <c r="C68" t="s">
-        <v>1155</v>
-      </c>
+      <c r="A68" s="8"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="24"/>
-      <c r="C69" t="s">
-        <v>1156</v>
+      <c r="B69" t="s">
+        <v>1152</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="24"/>
       <c r="C70" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="24"/>
+      <c r="C71" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="48" t="s">
+      <c r="A72" s="24"/>
+      <c r="C72" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="24"/>
+      <c r="C73" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="24"/>
+      <c r="C74" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="24"/>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="48" t="s">
         <v>1158</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="48"/>
-      <c r="B73" t="s">
+    <row r="77" spans="1:3">
+      <c r="A77" s="48"/>
+      <c r="B77" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="48"/>
-      <c r="B74" t="s">
+    <row r="78" spans="1:3">
+      <c r="A78" s="48"/>
+      <c r="B78" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="48"/>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="48"/>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="34" t="s">
+    <row r="79" spans="1:3">
+      <c r="A79" s="48"/>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="48"/>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="34" t="s">
         <v>730</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="B79" s="34" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="B80" s="34" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="B81" s="34" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="B82" s="34" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="B83" s="34" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="B84" s="34" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="B85" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="B86" s="34" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="B87" s="34" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="B88" s="34" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="B85" s="34"/>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" t="s">
-        <v>771</v>
-      </c>
-      <c r="B86" s="34"/>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
-        <v>770</v>
-      </c>
-      <c r="B87" s="34"/>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" t="s">
-        <v>4</v>
-      </c>
-      <c r="B88" s="34"/>
     </row>
     <row r="89" spans="1:2">
       <c r="B89" s="34"/>
     </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>771</v>
+      </c>
+      <c r="B90" s="34"/>
+    </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="8" t="s">
+      <c r="A91" t="s">
+        <v>770</v>
+      </c>
+      <c r="B91" s="34"/>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" s="34"/>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="B93" s="34"/>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="8" t="s">
         <v>298</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="B93" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="B95" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="B96" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="B97" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="B98" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="B99" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="B100" t="s">
-        <v>291</v>
+        <v>296</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="B101" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="B102" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="B103" t="s">
-        <v>292</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="B105" t="s">
-        <v>293</v>
-      </c>
-      <c r="E105" s="5">
-        <v>3000025478</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="B104" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="B106" t="s">
-        <v>294</v>
-      </c>
-      <c r="E106" s="5">
-        <v>3000025469</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="8" t="s">
-        <v>304</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="B107" t="s">
+        <v>292</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="8"/>
+      <c r="B109" t="s">
+        <v>293</v>
+      </c>
+      <c r="E109" s="5">
+        <v>3000025478</v>
+      </c>
     </row>
     <row r="110" spans="1:5">
       <c r="B110" t="s">
-        <v>1</v>
+        <v>294</v>
+      </c>
+      <c r="E110" s="5">
+        <v>3000025469</v>
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="B112" t="s">
-        <v>2</v>
+      <c r="A112" s="8" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="B113" t="s">
-        <v>302</v>
-      </c>
+      <c r="A113" s="8"/>
     </row>
     <row r="114" spans="1:6">
       <c r="B114" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="B115" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="B117" t="s">
-        <v>299</v>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="B119" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="B120" t="s">
-        <v>292</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="B122" t="s">
-        <v>293</v>
-      </c>
-      <c r="F122" s="27">
-        <v>45246</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="B121" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" t="s">
-        <v>300</v>
-      </c>
-      <c r="F123" s="27">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="B124" t="s">
+        <v>292</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" t="s">
+        <v>293</v>
+      </c>
+      <c r="F126" s="27">
         <v>45246</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" s="8" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="B127" t="s">
+        <v>300</v>
+      </c>
+      <c r="F127" s="27">
+        <v>45246</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="B131" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" t="s">
+    <row r="132" spans="1:2">
+      <c r="B132" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="130" spans="2:2">
-      <c r="B130" t="s">
+    <row r="134" spans="1:2">
+      <c r="B134" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="2:2">
-      <c r="B131" t="s">
+    <row r="135" spans="1:2">
+      <c r="B135" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="132" spans="2:2">
-      <c r="B132" t="s">
+    <row r="136" spans="1:2">
+      <c r="B136" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="133" spans="2:2">
-      <c r="B133" t="s">
+    <row r="137" spans="1:2">
+      <c r="B137" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="2:2">
-      <c r="B135" t="s">
+    <row r="139" spans="1:2">
+      <c r="B139" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="137" spans="2:2">
-      <c r="B137" t="s">
+    <row r="141" spans="1:2">
+      <c r="B141" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="2:2">
-      <c r="B139" t="s">
+    <row r="143" spans="1:2">
+      <c r="B143" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="140" spans="2:2">
-      <c r="B140" t="s">
+    <row r="144" spans="1:2">
+      <c r="B144" t="s">
         <v>310</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2">
-      <c r="B142" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2">
-      <c r="B143" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9">
-      <c r="B145" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="B146" t="s">
-        <v>312</v>
-      </c>
-      <c r="F146" s="27">
-        <v>45246</v>
+        <v>315</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="B147" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="B149" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="B150" t="s">
+        <v>312</v>
+      </c>
+      <c r="F150" s="27">
+        <v>45246</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="B151" t="s">
         <v>313</v>
       </c>
-      <c r="F147" s="27">
+      <c r="F151" s="27">
         <v>45248</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
-      <c r="A149" s="8" t="s">
+    <row r="153" spans="1:9">
+      <c r="A153" s="8" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
-      <c r="A150" s="8"/>
-      <c r="B150" t="s">
+    <row r="154" spans="1:9">
+      <c r="A154" s="8"/>
+      <c r="B154" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
-      <c r="A151" s="8"/>
-    </row>
-    <row r="152" spans="1:9">
-      <c r="C152" t="s">
+    <row r="155" spans="1:9">
+      <c r="A155" s="8"/>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="C156" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9">
-      <c r="C153" t="s">
-        <v>749</v>
-      </c>
-      <c r="I153" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9">
-      <c r="C155" t="s">
-        <v>747</v>
-      </c>
-      <c r="I155" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="C157" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="I157" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="C159" t="s">
+        <v>747</v>
+      </c>
+      <c r="I159" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="C161" t="s">
+        <v>744</v>
+      </c>
+      <c r="I161" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="C163" t="s">
         <v>745</v>
       </c>
-      <c r="E159" s="5" t="s">
+      <c r="E163" s="5" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="A161" s="8" t="s">
+    <row r="165" spans="1:9">
+      <c r="A165" s="8" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="A162" s="8"/>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="B163" t="s">
+    <row r="166" spans="1:9">
+      <c r="A166" s="8"/>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="B167" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" t="s">
+    <row r="168" spans="1:9">
+      <c r="B168" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" t="s">
+    <row r="169" spans="1:9">
+      <c r="B169" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
-      <c r="B166" s="3" t="s">
+    <row r="170" spans="1:9">
+      <c r="B170" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
-      <c r="B168" t="s">
+    <row r="172" spans="1:9">
+      <c r="B172" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
-      <c r="B169" t="s">
+    <row r="173" spans="1:9">
+      <c r="B173" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
-      <c r="B170" t="s">
+    <row r="174" spans="1:9">
+      <c r="B174" t="s">
         <v>292</v>
       </c>
-      <c r="F170" s="5" t="s">
+      <c r="F174" s="5" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
-      <c r="F171" s="5"/>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="F172" s="5"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="F173" s="5"/>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="F174" s="5"/>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" t="s">
-        <v>780</v>
-      </c>
+    <row r="175" spans="1:9">
       <c r="F175" s="5"/>
     </row>
-    <row r="176" spans="1:6">
-      <c r="B176" t="s">
-        <v>781</v>
-      </c>
+    <row r="176" spans="1:9">
       <c r="F176" s="5"/>
     </row>
     <row r="177" spans="2:6">
       <c r="F177" s="5"/>
     </row>
     <row r="178" spans="2:6">
-      <c r="C178">
+      <c r="B178" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="F178" s="5"/>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" t="s">
+        <v>780</v>
+      </c>
+      <c r="F179" s="5"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" t="s">
+        <v>781</v>
+      </c>
+      <c r="F180" s="5"/>
+    </row>
+    <row r="181" spans="2:6">
+      <c r="F181" s="5"/>
+    </row>
+    <row r="182" spans="2:6">
+      <c r="C182">
         <v>1</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D182" t="s">
         <v>779</v>
       </c>
-      <c r="F178" s="5"/>
-    </row>
-    <row r="179" spans="2:6">
-      <c r="C179">
+      <c r="F182" s="5"/>
+    </row>
+    <row r="183" spans="2:6">
+      <c r="C183">
         <v>2</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D183" t="s">
         <v>782</v>
-      </c>
-      <c r="F179" s="5"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="F180" s="5"/>
-    </row>
-    <row r="181" spans="2:6">
-      <c r="B181" t="s">
-        <v>783</v>
-      </c>
-      <c r="F181" s="5"/>
-    </row>
-    <row r="182" spans="2:6">
-      <c r="B182" t="s">
-        <v>784</v>
-      </c>
-      <c r="F182" s="5"/>
-    </row>
-    <row r="183" spans="2:6">
-      <c r="B183" t="s">
-        <v>785</v>
       </c>
       <c r="F183" s="5"/>
     </row>
@@ -23614,12 +23607,21 @@
       <c r="F184" s="5"/>
     </row>
     <row r="185" spans="2:6">
+      <c r="B185" t="s">
+        <v>783</v>
+      </c>
       <c r="F185" s="5"/>
     </row>
     <row r="186" spans="2:6">
+      <c r="B186" t="s">
+        <v>784</v>
+      </c>
       <c r="F186" s="5"/>
     </row>
     <row r="187" spans="2:6">
+      <c r="B187" t="s">
+        <v>785</v>
+      </c>
       <c r="F187" s="5"/>
     </row>
     <row r="188" spans="2:6">
@@ -23631,934 +23633,946 @@
     <row r="190" spans="2:6">
       <c r="F190" s="5"/>
     </row>
+    <row r="191" spans="2:6">
+      <c r="F191" s="5"/>
+    </row>
     <row r="192" spans="2:6">
-      <c r="B192" t="s">
+      <c r="F192" s="5"/>
+    </row>
+    <row r="193" spans="2:6">
+      <c r="F193" s="5"/>
+    </row>
+    <row r="194" spans="2:6">
+      <c r="F194" s="5"/>
+    </row>
+    <row r="196" spans="2:6">
+      <c r="B196" t="s">
         <v>1232</v>
       </c>
     </row>
-    <row r="194" spans="2:4">
-      <c r="B194" t="s">
+    <row r="198" spans="2:6">
+      <c r="B198" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="195" spans="2:4">
-      <c r="C195" s="35" t="s">
+    <row r="199" spans="2:6">
+      <c r="C199" s="35" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="196" spans="2:4">
-      <c r="C196" s="35" t="s">
+    <row r="200" spans="2:6">
+      <c r="C200" s="35" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="197" spans="2:4">
-      <c r="C197" s="35" t="s">
+    <row r="201" spans="2:6">
+      <c r="C201" s="35" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="198" spans="2:4">
-      <c r="D198" t="s">
+    <row r="202" spans="2:6">
+      <c r="D202" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="200" spans="2:4">
-      <c r="B200" t="s">
+    <row r="204" spans="2:6">
+      <c r="B204" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="202" spans="2:4">
-      <c r="B202" s="8" t="s">
+    <row r="206" spans="2:6">
+      <c r="B206" s="8" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="203" spans="2:4">
-      <c r="C203" s="35" t="s">
+    <row r="207" spans="2:6">
+      <c r="C207" s="35" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="205" spans="2:4">
-      <c r="C205" t="s">
+    <row r="209" spans="2:13">
+      <c r="C209" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="207" spans="2:4">
-      <c r="B207" s="36" t="s">
+    <row r="211" spans="2:13">
+      <c r="B211" s="36" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="208" spans="2:4" ht="15">
-      <c r="B208" s="36" t="s">
+    <row r="212" spans="2:13" ht="15">
+      <c r="B212" s="36" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="209" spans="2:13">
-      <c r="B209" s="36"/>
-    </row>
-    <row r="210" spans="2:13">
-      <c r="B210" s="36" t="s">
+    <row r="213" spans="2:13">
+      <c r="B213" s="36"/>
+    </row>
+    <row r="214" spans="2:13">
+      <c r="B214" s="36" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="211" spans="2:13">
-      <c r="B211" s="36"/>
-    </row>
-    <row r="212" spans="2:13">
-      <c r="B212" s="36" t="s">
+    <row r="215" spans="2:13">
+      <c r="B215" s="36"/>
+    </row>
+    <row r="216" spans="2:13">
+      <c r="B216" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="E212" s="8" t="s">
+      <c r="E216" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="G212" s="8" t="s">
+      <c r="G216" s="8" t="s">
         <v>994</v>
       </c>
-      <c r="J212" s="8"/>
-      <c r="K212" s="8"/>
-      <c r="L212" s="8"/>
-      <c r="M212" s="8"/>
-    </row>
-    <row r="213" spans="2:13">
-      <c r="B213" s="50" t="s">
-        <v>872</v>
-      </c>
-      <c r="E213" s="50" t="s">
-        <v>1266</v>
-      </c>
-      <c r="G213" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="J213" s="8"/>
-      <c r="K213" s="8"/>
-      <c r="L213" s="8"/>
-      <c r="M213" s="8"/>
-    </row>
-    <row r="214" spans="2:13">
-      <c r="B214" s="36"/>
-      <c r="E214" s="8"/>
-      <c r="G214" s="50" t="s">
-        <v>292</v>
-      </c>
-      <c r="J214" s="8"/>
-      <c r="K214" s="8"/>
-      <c r="L214" s="8"/>
-      <c r="M214" s="8"/>
-    </row>
-    <row r="215" spans="2:13">
-      <c r="B215" s="50" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E215" s="8"/>
-      <c r="G215" s="8"/>
-      <c r="J215" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K215" s="50" t="s">
-        <v>1241</v>
-      </c>
-      <c r="L215" s="8"/>
-      <c r="M215" s="8"/>
-    </row>
-    <row r="216" spans="2:13">
-      <c r="B216" s="50" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E216" t="s">
-        <v>1254</v>
-      </c>
-      <c r="G216" t="s">
-        <v>1244</v>
-      </c>
-      <c r="J216" t="s">
-        <v>1245</v>
-      </c>
-      <c r="K216" t="s">
-        <v>1246</v>
-      </c>
+      <c r="J216" s="8"/>
+      <c r="K216" s="8"/>
       <c r="L216" s="8"/>
       <c r="M216" s="8"/>
     </row>
     <row r="217" spans="2:13">
-      <c r="B217" s="50"/>
+      <c r="B217" s="50" t="s">
+        <v>872</v>
+      </c>
+      <c r="E217" s="50" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G217" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J217" s="8"/>
+      <c r="K217" s="8"/>
       <c r="L217" s="8"/>
       <c r="M217" s="8"/>
     </row>
     <row r="218" spans="2:13">
-      <c r="B218" s="50"/>
-      <c r="J218" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K218" s="50" t="s">
-        <v>1248</v>
-      </c>
-      <c r="L218" s="50" t="s">
-        <v>1241</v>
-      </c>
-      <c r="M218" s="50" t="s">
-        <v>1248</v>
-      </c>
+      <c r="B218" s="36"/>
+      <c r="E218" s="8"/>
+      <c r="G218" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="J218" s="8"/>
+      <c r="K218" s="8"/>
+      <c r="L218" s="8"/>
+      <c r="M218" s="8"/>
     </row>
     <row r="219" spans="2:13">
       <c r="B219" s="50" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E219" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G219" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E219" s="8"/>
+      <c r="G219" s="8"/>
+      <c r="J219" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K219" s="50" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L219" s="8"/>
+      <c r="M219" s="8"/>
+    </row>
+    <row r="220" spans="2:13">
+      <c r="B220" s="50" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G220" t="s">
         <v>1244</v>
       </c>
-      <c r="J219" t="s">
+      <c r="J220" t="s">
         <v>1245</v>
       </c>
-      <c r="K219" t="s">
-        <v>1245</v>
-      </c>
-      <c r="L219" t="s">
+      <c r="K220" t="s">
         <v>1246</v>
       </c>
-      <c r="M219" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="220" spans="2:13">
-      <c r="B220" s="50"/>
+      <c r="L220" s="8"/>
+      <c r="M220" s="8"/>
     </row>
     <row r="221" spans="2:13">
       <c r="B221" s="50"/>
-      <c r="J221" s="50" t="s">
+      <c r="L221" s="8"/>
+      <c r="M221" s="8"/>
+    </row>
+    <row r="222" spans="2:13">
+      <c r="B222" s="50"/>
+      <c r="J222" s="50" t="s">
         <v>1240</v>
       </c>
-      <c r="K221" s="50" t="s">
+      <c r="K222" s="50" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L222" s="50" t="s">
         <v>1241</v>
       </c>
-      <c r="L221" s="50" t="s">
+      <c r="M222" s="50" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="223" spans="2:13">
+      <c r="B223" s="50" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G223" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J223" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K223" t="s">
+        <v>1245</v>
+      </c>
+      <c r="L223" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M223" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="224" spans="2:13">
+      <c r="B224" s="50"/>
+    </row>
+    <row r="225" spans="2:15">
+      <c r="B225" s="50"/>
+      <c r="J225" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K225" s="50" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L225" s="50" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="222" spans="2:13">
-      <c r="B222" s="50" t="s">
+    <row r="226" spans="2:15">
+      <c r="B226" s="50" t="s">
         <v>1255</v>
       </c>
-      <c r="E222" t="s">
+      <c r="E226" t="s">
         <v>1252</v>
       </c>
-      <c r="G222" t="s">
+      <c r="G226" t="s">
         <v>1234</v>
       </c>
-      <c r="J222" t="s">
+      <c r="J226" t="s">
         <v>1237</v>
       </c>
-      <c r="K222" t="s">
+      <c r="K226" t="s">
         <v>1238</v>
       </c>
-      <c r="L222" t="s">
+      <c r="L226" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="223" spans="2:13">
-      <c r="B223" s="50"/>
-    </row>
-    <row r="224" spans="2:13">
-      <c r="B224" s="50" t="s">
-        <v>1268</v>
-      </c>
-      <c r="J224" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K224" s="50" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="225" spans="2:15">
-      <c r="B225" s="50" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E225" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G225" t="s">
-        <v>1235</v>
-      </c>
-      <c r="J225" t="s">
-        <v>1238</v>
-      </c>
-      <c r="K225" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="226" spans="2:15">
-      <c r="B226" s="50"/>
-    </row>
     <row r="227" spans="2:15">
-      <c r="B227" s="50" t="s">
-        <v>1267</v>
-      </c>
-      <c r="J227" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K227" s="50" t="s">
-        <v>1241</v>
-      </c>
-      <c r="L227" s="50" t="s">
-        <v>1243</v>
-      </c>
+      <c r="B227" s="50"/>
     </row>
     <row r="228" spans="2:15">
       <c r="B228" s="50" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E228" t="s">
-        <v>1250</v>
-      </c>
-      <c r="G228" t="s">
-        <v>1257</v>
-      </c>
-      <c r="J228" t="s">
-        <v>1258</v>
-      </c>
-      <c r="K228" t="s">
-        <v>1259</v>
-      </c>
-      <c r="L228">
-        <v>0</v>
+        <v>1268</v>
+      </c>
+      <c r="J228" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K228" s="50" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="229" spans="2:15">
-      <c r="B229" s="50"/>
+      <c r="B229" s="50" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E229" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G229" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J229" t="s">
+        <v>1238</v>
+      </c>
+      <c r="K229" t="s">
+        <v>1239</v>
+      </c>
     </row>
     <row r="230" spans="2:15">
       <c r="B230" s="50"/>
-      <c r="J230" s="50" t="s">
+    </row>
+    <row r="231" spans="2:15">
+      <c r="B231" s="50" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J231" s="50" t="s">
         <v>1240</v>
       </c>
-      <c r="K230" s="50" t="s">
+      <c r="K231" s="50" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L231" s="50" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="232" spans="2:15">
+      <c r="B232" s="50" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G232" t="s">
+        <v>1257</v>
+      </c>
+      <c r="J232" t="s">
+        <v>1258</v>
+      </c>
+      <c r="K232" t="s">
+        <v>1259</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="2:15">
+      <c r="B233" s="50"/>
+    </row>
+    <row r="234" spans="2:15">
+      <c r="B234" s="50"/>
+      <c r="J234" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K234" s="50" t="s">
         <v>1248</v>
       </c>
-      <c r="L230" s="50" t="s">
+      <c r="L234" s="50" t="s">
         <v>1241</v>
       </c>
-      <c r="M230" s="50" t="s">
+      <c r="M234" s="50" t="s">
         <v>1248</v>
       </c>
     </row>
-    <row r="231" spans="2:15">
-      <c r="B231" s="32" t="s">
+    <row r="235" spans="2:15">
+      <c r="B235" s="32" t="s">
         <v>1263</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E235" t="s">
         <v>1261</v>
       </c>
-      <c r="G231" t="s">
+      <c r="G235" t="s">
         <v>1262</v>
       </c>
-      <c r="J231" t="s">
+      <c r="J235" t="s">
         <v>1258</v>
       </c>
-      <c r="K231" t="s">
+      <c r="K235" t="s">
         <v>1264</v>
       </c>
-      <c r="L231" t="s">
+      <c r="L235" t="s">
         <v>1259</v>
       </c>
-      <c r="M231" t="s">
+      <c r="M235" t="s">
         <v>1265</v>
       </c>
-    </row>
-    <row r="232" spans="2:15">
-      <c r="B232" s="50"/>
-    </row>
-    <row r="233" spans="2:15">
-      <c r="B233" s="50" t="s">
-        <v>1275</v>
-      </c>
-      <c r="J233" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K233" s="50" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="234" spans="2:15">
-      <c r="B234" s="50" t="s">
-        <v>1272</v>
-      </c>
-      <c r="E234" t="s">
-        <v>1270</v>
-      </c>
-      <c r="G234" t="s">
-        <v>1271</v>
-      </c>
-      <c r="J234" t="s">
-        <v>1273</v>
-      </c>
-      <c r="K234" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="235" spans="2:15">
-      <c r="B235" s="50"/>
     </row>
     <row r="236" spans="2:15">
       <c r="B236" s="50"/>
-      <c r="J236" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K236" s="50" t="s">
-        <v>1248</v>
-      </c>
-      <c r="L236" s="50" t="s">
-        <v>1241</v>
-      </c>
-      <c r="M236" s="50" t="s">
-        <v>1248</v>
-      </c>
-      <c r="N236" s="50" t="s">
-        <v>1242</v>
-      </c>
-      <c r="O236" s="50" t="s">
-        <v>1248</v>
-      </c>
     </row>
     <row r="237" spans="2:15">
       <c r="B237" s="50" t="s">
+        <v>1275</v>
+      </c>
+      <c r="J237" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K237" s="50" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="238" spans="2:15">
+      <c r="B238" s="50" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E238" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G238" t="s">
+        <v>1271</v>
+      </c>
+      <c r="J238" t="s">
+        <v>1273</v>
+      </c>
+      <c r="K238" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="239" spans="2:15">
+      <c r="B239" s="50"/>
+    </row>
+    <row r="240" spans="2:15">
+      <c r="B240" s="50"/>
+      <c r="J240" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K240" s="50" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L240" s="50" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M240" s="50" t="s">
+        <v>1248</v>
+      </c>
+      <c r="N240" s="50" t="s">
+        <v>1242</v>
+      </c>
+      <c r="O240" s="50" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="241" spans="2:15">
+      <c r="B241" s="50" t="s">
         <v>1278</v>
       </c>
-      <c r="E237" t="s">
+      <c r="E241" t="s">
         <v>1276</v>
       </c>
-      <c r="G237" t="s">
+      <c r="G241" t="s">
         <v>1277</v>
       </c>
-      <c r="J237" t="s">
+      <c r="J241" t="s">
         <v>1279</v>
       </c>
-      <c r="K237">
+      <c r="K241">
         <v>1</v>
       </c>
-      <c r="L237" t="s">
+      <c r="L241" t="s">
         <v>1280</v>
       </c>
-      <c r="M237">
+      <c r="M241">
         <v>22</v>
       </c>
-      <c r="N237" t="s">
+      <c r="N241" t="s">
         <v>1281</v>
       </c>
-      <c r="O237">
+      <c r="O241">
         <v>333</v>
       </c>
     </row>
-    <row r="238" spans="2:15">
-      <c r="B238" s="36"/>
-    </row>
-    <row r="239" spans="2:15">
-      <c r="B239" s="50" t="s">
+    <row r="242" spans="2:15">
+      <c r="B242" s="36"/>
+    </row>
+    <row r="243" spans="2:15">
+      <c r="B243" s="50" t="s">
         <v>1286</v>
       </c>
-      <c r="J239" s="50" t="s">
+      <c r="J243" s="50" t="s">
         <v>1240</v>
       </c>
-      <c r="K239" s="50" t="s">
+      <c r="K243" s="50" t="s">
         <v>1241</v>
       </c>
     </row>
-    <row r="240" spans="2:15">
-      <c r="B240" s="50" t="s">
+    <row r="244" spans="2:15">
+      <c r="B244" s="50" t="s">
         <v>1284</v>
       </c>
-      <c r="E240" t="s">
+      <c r="E244" t="s">
         <v>1282</v>
       </c>
-      <c r="G240" t="s">
+      <c r="G244" t="s">
         <v>1283</v>
       </c>
-      <c r="J240" t="s">
+      <c r="J244" t="s">
         <v>1285</v>
       </c>
-      <c r="K240" t="s">
+      <c r="K244" t="s">
         <v>1285</v>
       </c>
     </row>
-    <row r="241" spans="2:8">
-      <c r="B241" s="36"/>
-    </row>
-    <row r="242" spans="2:8">
-      <c r="B242" s="36"/>
-    </row>
-    <row r="243" spans="2:8">
-      <c r="B243" s="36" t="s">
+    <row r="245" spans="2:15">
+      <c r="B245" s="36"/>
+    </row>
+    <row r="246" spans="2:15">
+      <c r="B246" s="36"/>
+    </row>
+    <row r="247" spans="2:15">
+      <c r="B247" s="36" t="s">
         <v>1287</v>
       </c>
     </row>
-    <row r="244" spans="2:8">
-      <c r="B244" s="36"/>
-      <c r="C244" t="s">
-        <v>49</v>
-      </c>
-      <c r="H244" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="245" spans="2:8">
-      <c r="B245" s="36"/>
-      <c r="C245" t="s">
-        <v>278</v>
-      </c>
-      <c r="H245" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="246" spans="2:8">
-      <c r="B246" s="36"/>
-      <c r="C246" t="s">
-        <v>600</v>
-      </c>
-      <c r="H246" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="247" spans="2:8">
-      <c r="B247" s="36"/>
-      <c r="C247" t="s">
-        <v>1289</v>
-      </c>
-      <c r="H247" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="248" spans="2:8">
+    <row r="248" spans="2:15">
       <c r="B248" s="36"/>
       <c r="C248" t="s">
-        <v>1291</v>
+        <v>49</v>
       </c>
       <c r="H248" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="249" spans="2:8">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="249" spans="2:15">
       <c r="B249" s="36"/>
       <c r="C249" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="250" spans="2:8">
+        <v>278</v>
+      </c>
+      <c r="H249" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="250" spans="2:15">
       <c r="B250" s="36"/>
-    </row>
-    <row r="251" spans="2:8">
+      <c r="C250" t="s">
+        <v>600</v>
+      </c>
+      <c r="H250" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="251" spans="2:15">
       <c r="B251" s="36"/>
       <c r="C251" t="s">
         <v>1289</v>
       </c>
-    </row>
-    <row r="252" spans="2:8">
+      <c r="H251" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="252" spans="2:15">
       <c r="B252" s="36"/>
-      <c r="C252" s="8" t="s">
+      <c r="C252" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H252" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="253" spans="2:15">
+      <c r="B253" s="36"/>
+      <c r="C253" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="254" spans="2:15">
+      <c r="B254" s="36"/>
+    </row>
+    <row r="255" spans="2:15">
+      <c r="B255" s="36"/>
+      <c r="C255" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="256" spans="2:15">
+      <c r="B256" s="36"/>
+      <c r="C256" s="8" t="s">
         <v>1297</v>
-      </c>
-    </row>
-    <row r="253" spans="2:8">
-      <c r="B253" s="36"/>
-      <c r="D253" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="254" spans="2:8">
-      <c r="B254" s="36"/>
-    </row>
-    <row r="255" spans="2:8">
-      <c r="B255" s="36"/>
-      <c r="D255" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="256" spans="2:8">
-      <c r="B256" s="36"/>
-      <c r="D256" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="B257" s="36"/>
       <c r="D257" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="B258" s="36"/>
     </row>
+    <row r="259" spans="1:6">
+      <c r="B259" s="36"/>
+      <c r="D259" t="s">
+        <v>1298</v>
+      </c>
+    </row>
     <row r="260" spans="1:6">
-      <c r="A260" s="8" t="s">
+      <c r="B260" s="36"/>
+      <c r="D260" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="B261" s="36"/>
+      <c r="D261" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="B262" s="36"/>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="8" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
-      <c r="B262" t="s">
+    <row r="266" spans="1:6">
+      <c r="B266" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="B264" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
-      <c r="B265" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="B267" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="B268" t="s">
-        <v>790</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
-      <c r="A270" s="8" t="s">
-        <v>792</v>
+        <v>787</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="B269" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="B271" t="s">
+        <v>789</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="B272" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8">
-      <c r="B273" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8">
-      <c r="B275" t="s">
-        <v>794</v>
+        <v>790</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274" s="8" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="B276" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="B277" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8">
+      <c r="B279" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="B280" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
-      <c r="C277" s="5" t="s">
+    <row r="281" spans="1:8">
+      <c r="C281" s="5" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
-      <c r="A279" s="8" t="s">
+    <row r="283" spans="1:8">
+      <c r="A283" s="8" t="s">
         <v>797</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8">
-      <c r="B281" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8">
-      <c r="B283" t="s">
-        <v>798</v>
-      </c>
-      <c r="H283" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8">
-      <c r="B284" t="s">
-        <v>799</v>
-      </c>
-      <c r="H284" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="B285" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8">
+      <c r="B287" t="s">
+        <v>798</v>
+      </c>
+      <c r="H287" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
+      <c r="B288" t="s">
+        <v>799</v>
+      </c>
+      <c r="H288" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9">
+      <c r="B289" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
-      <c r="C286" s="5" t="s">
+    <row r="290" spans="1:9">
+      <c r="C290" s="5" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
-      <c r="A288" s="8" t="s">
+    <row r="292" spans="1:9">
+      <c r="A292" s="8" t="s">
         <v>802</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9">
-      <c r="B290" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9">
-      <c r="B292" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9">
-      <c r="B293" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="B294" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9">
+      <c r="B296" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9">
+      <c r="B297" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9">
+      <c r="B298" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
-      <c r="C295" s="5" t="s">
+    <row r="299" spans="1:9">
+      <c r="C299" s="5" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
-      <c r="A298" s="8" t="s">
+    <row r="302" spans="1:9">
+      <c r="A302" s="8" t="s">
         <v>809</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9">
-      <c r="B300" t="s">
-        <v>810</v>
-      </c>
-      <c r="I300" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9">
-      <c r="B302" t="s">
-        <v>1</v>
-      </c>
-      <c r="I302" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9">
-      <c r="B303" t="s">
-        <v>811</v>
-      </c>
-      <c r="I303" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="B304" t="s">
+        <v>810</v>
+      </c>
+      <c r="I304" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10">
+      <c r="B306" t="s">
+        <v>1</v>
+      </c>
+      <c r="I306" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10">
+      <c r="B307" t="s">
+        <v>811</v>
+      </c>
+      <c r="I307" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10">
+      <c r="B308" t="s">
         <v>815</v>
       </c>
-      <c r="I304" t="s">
+      <c r="I308" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
-      <c r="B305" t="s">
+    <row r="309" spans="1:10">
+      <c r="B309" t="s">
         <v>813</v>
       </c>
-      <c r="I305" t="s">
+      <c r="I309" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
-      <c r="C306" s="5" t="b">
+    <row r="310" spans="1:10">
+      <c r="C310" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="J306" s="5" t="s">
+      <c r="J310" s="5" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
-      <c r="A309" s="8" t="s">
+    <row r="313" spans="1:10">
+      <c r="A313" s="8" t="s">
         <v>817</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10">
-      <c r="B311" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313" spans="1:10">
-      <c r="B313" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="314" spans="1:10">
-      <c r="B314" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="315" spans="1:10">
       <c r="B315" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="316" spans="1:10">
-      <c r="C316" s="5" t="s">
-        <v>821</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10">
+      <c r="B317" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="318" spans="1:10">
-      <c r="A318" s="8" t="s">
-        <v>822</v>
+      <c r="B318" t="s">
+        <v>819</v>
       </c>
     </row>
     <row r="319" spans="1:10">
       <c r="B319" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3">
-      <c r="B321" t="s">
-        <v>1</v>
+        <v>820</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10">
+      <c r="C320" s="5" t="s">
+        <v>821</v>
       </c>
     </row>
     <row r="322" spans="1:3">
-      <c r="B322" t="s">
-        <v>824</v>
+      <c r="A322" s="8" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="B323" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="B325" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="B326" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="B327" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
-      <c r="B324" t="s">
+    <row r="328" spans="1:3">
+      <c r="B328" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
-      <c r="C325" s="5" t="s">
+    <row r="329" spans="1:3">
+      <c r="C329" s="5" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
-      <c r="A327" s="8" t="s">
+    <row r="331" spans="1:3">
+      <c r="A331" s="8" t="s">
         <v>828</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3">
-      <c r="B329" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3">
-      <c r="B331" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3">
-      <c r="B332" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="B333" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="B335" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="B336" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="B337" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="334" spans="1:3">
-      <c r="C334" s="5" t="s">
+    <row r="338" spans="1:5">
+      <c r="C338" s="5" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
-      <c r="A337" s="8" t="s">
+    <row r="341" spans="1:5">
+      <c r="A341" s="8" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
-      <c r="B338" t="s">
+    <row r="342" spans="1:5">
+      <c r="B342" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
-      <c r="B340" t="s">
+    <row r="344" spans="1:5">
+      <c r="B344" t="s">
         <v>900</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5">
-      <c r="B341" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5">
-      <c r="B343" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="345" spans="1:5">
       <c r="B345" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="B347" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="B349" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
-      <c r="B346" t="s">
+    <row r="350" spans="1:5">
+      <c r="B350" t="s">
         <v>80</v>
       </c>
-      <c r="E346" s="5" t="s">
+      <c r="E350" s="5" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
-      <c r="A349" s="8" t="s">
+    <row r="353" spans="1:7">
+      <c r="A353" s="8" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
-      <c r="B351" t="s">
+    <row r="355" spans="1:7">
+      <c r="B355" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="2:7">
-      <c r="B353" t="s">
+    <row r="357" spans="1:7">
+      <c r="B357" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="2:7">
-      <c r="B354" t="s">
+    <row r="358" spans="1:7">
+      <c r="B358" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="355" spans="2:7">
-      <c r="B355" t="s">
+    <row r="359" spans="1:7">
+      <c r="B359" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="356" spans="2:7">
-      <c r="B356" t="s">
+    <row r="360" spans="1:7">
+      <c r="B360" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="2:7">
-      <c r="B358" t="s">
+    <row r="362" spans="1:7">
+      <c r="B362" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="360" spans="2:7">
-      <c r="B360" t="s">
+    <row r="364" spans="1:7">
+      <c r="B364" t="s">
         <v>904</v>
       </c>
-      <c r="G360" s="5" t="s">
+      <c r="G364" s="5" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="361" spans="2:7">
-      <c r="B361" t="s">
+    <row r="365" spans="1:7">
+      <c r="B365" t="s">
         <v>905</v>
       </c>
-      <c r="G361" s="5" t="s">
+      <c r="G365" s="5" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="362" spans="2:7">
-      <c r="B362" t="s">
+    <row r="366" spans="1:7">
+      <c r="B366" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="363" spans="2:7">
-      <c r="B363" t="s">
+    <row r="367" spans="1:7">
+      <c r="B367" t="s">
         <v>907</v>
       </c>
     </row>
@@ -30853,17 +30867,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="5" priority="10">
       <formula>$B$82&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="7" priority="11">
+    <cfRule type="expression" dxfId="4" priority="11">
       <formula>$B$80&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="3" priority="12">
       <formula>$B$49=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32189,17 +32203,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$B$82&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$B$80&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B$49=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Regex 04.02.25.xlsx
+++ b/Regex 04.02.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="787" activeTab="17"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="787" firstSheet="3" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="4" r:id="rId1"/>
@@ -30,13 +30,14 @@
     <sheet name="Pyxl" sheetId="21" r:id="rId21"/>
     <sheet name="Universal" sheetId="22" r:id="rId22"/>
     <sheet name="Niki" sheetId="23" r:id="rId23"/>
+    <sheet name="Felo" sheetId="24" r:id="rId24"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3188" uniqueCount="1829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3283" uniqueCount="1906">
   <si>
     <t>with (?mx) with description</t>
   </si>
@@ -15354,12 +15355,1647 @@
   <si>
     <t>includes: space, tab, newline, carriage return</t>
   </si>
+  <si>
+    <t>Felo</t>
+  </si>
+  <si>
+    <t>code_pattern = re.compile(r'^000\d{8}$')</t>
+  </si>
+  <si>
+    <t>while i &lt; len(lines):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    line = lines[i]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        try:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            data.append([</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                int(quantity),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            ])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        except IndexError:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        sheet.cell(row=row_idx, column=col_idx, value=value)</t>
+  </si>
+  <si>
+    <t>wb.save("regex/felo/excract_fitz.xlsx")</t>
+  </si>
+  <si>
+    <t>Document('regex/felo/invoice.pdf')</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>doc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = fitz.open("regex/felo/invoice.pdf")</t>
+    </r>
+  </si>
+  <si>
+    <t>0 of regex/felo/invoice.pdf</t>
+  </si>
+  <si>
+    <t>1 of regex/felo/invoice.pdf</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in doc:</t>
+    </r>
+  </si>
+  <si>
+    <t>print(doc)</t>
+  </si>
+  <si>
+    <t>print(type(doc))</t>
+  </si>
+  <si>
+    <t>page</t>
+  </si>
+  <si>
+    <t>doc</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    text += page.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>get_text</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>doc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>close</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>SD CA Nail-lifter x 100</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = [line.strip() for line in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.splitlines() if line.strip()]</t>
+    </r>
+  </si>
+  <si>
+    <t>премахва празните линии и прави променливата text в list</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'1', '00049400330', 'SD CA Nail-lifter x 100', '12', '8,46', '101,52', '65,00', '35,53', ……</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>re.compile('^000\\d{8}$')</t>
+  </si>
+  <si>
+    <t>&lt;re.Match object; span=(0, 11), match='00049400330'&gt;</t>
+  </si>
+  <si>
+    <t>00049400330</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>artical_number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = artical_number[3:6] + " " + artical_number[6:9] + " " + artical_number[9:11]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>code_match</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = code_pattern.match(line)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    if </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>code_match</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>artical_number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>code_match</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>group</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>total_price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[i + 1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[i + 5]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[i + 3]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[i + 2]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = price.replace(" ", "")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = price.replace(",", ".")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = discount.replace(" ", "")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = discount.replace(",", ".")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>net_amount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(quantity) * price) * (1 - discount/100)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(price) if price.replace('.', '', 1).isdigit() else price</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(discount) if discount.replace('.', '', 1).isdigit() else discount</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>total_price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>net_amount</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>artical_number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>net_amount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>break</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(f"Number of rows: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(f"Total price: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>total_price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:.2f}")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>headers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = ["Index", "Artical_number", "Description", "Quantity", "Price", "Discount", "Net_amount"]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = openpyxl.Workbook()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">sheet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.active</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>for col, header in enumerate(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>headers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, start=1):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.font = Font(bold=True)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  cell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.alignment = Alignment(horizontal="center")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'1', '00049400330', 'SD CA Nail-lifter x 100', '12', '8,46', '101,52', '65,00', '35,53', ……</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>Попълване на имената на колоните "index", "Artical_number"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = sheet.cell(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, column=col, value=header)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Хардкодваме </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, защото искаме всичките да са на ред1</t>
+    </r>
+  </si>
+  <si>
+    <t>На всяка итерация: column=1, column=2, column=3</t>
+  </si>
+  <si>
+    <t>For loop за попълване на редовете</t>
+  </si>
+  <si>
+    <t>For loop за попълване на колоните</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Попълване на таблицата от list </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for row_idx, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in enumerate(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, start=2):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    for col_idx, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in enumerate(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, start=1):</t>
+    </r>
+  </si>
+  <si>
+    <t>row</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1, '494 003 30', 'SD CA Nail-lifter x 100', 12, 8.46, 65.0, 35.532000000000004]</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="69">
+  <fonts count="72">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15901,6 +17537,30 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF179A77"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -16122,7 +17782,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -16276,12 +17936,709 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="194">
+  <dxfs count="293">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -17645,10 +20002,10 @@
   <colors>
     <mruColors>
       <color rgb="FFDA7BB9"/>
-      <color rgb="FF7D7DFF"/>
       <color rgb="FF179A77"/>
       <color rgb="FFA626A4"/>
       <color rgb="FFA47A20"/>
+      <color rgb="FF7D7DFF"/>
       <color rgb="FFFF33CC"/>
     </mruColors>
   </colors>
@@ -18141,7 +20498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C3:F7"/>
+  <dimension ref="C3:F8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="6" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -18217,675 +20574,1155 @@
         <v>1580</v>
       </c>
     </row>
+    <row r="8" spans="3:6" ht="34.799999999999997" customHeight="1">
+      <c r="C8" s="19" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="193" priority="123">
+    <cfRule type="expression" dxfId="292" priority="219">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E5">
-    <cfRule type="expression" dxfId="192" priority="124">
+    <cfRule type="expression" dxfId="291" priority="220">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="191" priority="125">
+    <cfRule type="expression" dxfId="290" priority="221">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:F4 C4:C5 D3:F5">
-    <cfRule type="expression" dxfId="190" priority="126">
+    <cfRule type="expression" dxfId="289" priority="222">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="189" priority="127">
+    <cfRule type="expression" dxfId="288" priority="223">
       <formula>$B$27&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5 C3:F3 C4:D4">
-    <cfRule type="expression" dxfId="188" priority="128">
+    <cfRule type="expression" dxfId="287" priority="224">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="expression" dxfId="187" priority="164">
+    <cfRule type="expression" dxfId="286" priority="260">
       <formula>$B$9&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="165">
+    <cfRule type="expression" dxfId="285" priority="261">
       <formula>$B$9&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="expression" dxfId="185" priority="166">
+    <cfRule type="expression" dxfId="284" priority="262">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="167">
+    <cfRule type="expression" dxfId="283" priority="263">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="183" priority="168">
+    <cfRule type="expression" dxfId="282" priority="264">
       <formula>$B$15&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="182" priority="171">
+    <cfRule type="expression" dxfId="281" priority="267">
       <formula>$B$21&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:F5">
-    <cfRule type="expression" dxfId="181" priority="175">
+    <cfRule type="expression" dxfId="280" priority="271">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D5">
-    <cfRule type="expression" dxfId="180" priority="176">
+    <cfRule type="expression" dxfId="279" priority="272">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="179" priority="122">
+    <cfRule type="expression" dxfId="278" priority="218">
       <formula>$B$27&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="178" priority="121">
+    <cfRule type="expression" dxfId="277" priority="217">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="177" priority="120">
+    <cfRule type="expression" dxfId="276" priority="216">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="expression" dxfId="176" priority="119">
+    <cfRule type="expression" dxfId="275" priority="215">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="expression" dxfId="175" priority="118">
+    <cfRule type="expression" dxfId="274" priority="214">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="174" priority="117">
+    <cfRule type="expression" dxfId="273" priority="213">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="173" priority="116">
+    <cfRule type="expression" dxfId="272" priority="212">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="172" priority="115">
+    <cfRule type="expression" dxfId="271" priority="211">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="171" priority="114">
+    <cfRule type="expression" dxfId="270" priority="210">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="170" priority="113">
+    <cfRule type="expression" dxfId="269" priority="209">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="169" priority="112">
+    <cfRule type="expression" dxfId="268" priority="208">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="168" priority="111">
+    <cfRule type="expression" dxfId="267" priority="207">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="167" priority="110">
+    <cfRule type="expression" dxfId="266" priority="206">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="166" priority="109">
+    <cfRule type="expression" dxfId="265" priority="205">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:F6">
-    <cfRule type="expression" dxfId="165" priority="108">
+    <cfRule type="expression" dxfId="264" priority="204">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="164" priority="107">
+    <cfRule type="expression" dxfId="263" priority="203">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="163" priority="105">
+    <cfRule type="expression" dxfId="262" priority="201">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="106">
+    <cfRule type="expression" dxfId="261" priority="202">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:F6">
-    <cfRule type="expression" dxfId="161" priority="104">
+    <cfRule type="expression" dxfId="260" priority="200">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="160" priority="103">
+    <cfRule type="expression" dxfId="259" priority="199">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="159" priority="102">
+    <cfRule type="expression" dxfId="258" priority="198">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="158" priority="101">
+    <cfRule type="expression" dxfId="257" priority="197">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="157" priority="100">
+    <cfRule type="expression" dxfId="256" priority="196">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="156" priority="99">
+    <cfRule type="expression" dxfId="255" priority="195">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="155" priority="98">
+    <cfRule type="expression" dxfId="254" priority="194">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="154" priority="97">
+    <cfRule type="expression" dxfId="253" priority="193">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="153" priority="96">
+    <cfRule type="expression" dxfId="252" priority="192">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="152" priority="95">
+    <cfRule type="expression" dxfId="251" priority="191">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="151" priority="94">
+    <cfRule type="expression" dxfId="250" priority="190">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="150" priority="93">
+    <cfRule type="expression" dxfId="249" priority="189">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="149" priority="92">
+    <cfRule type="expression" dxfId="248" priority="188">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="148" priority="91">
+    <cfRule type="expression" dxfId="247" priority="187">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="147" priority="90">
+    <cfRule type="expression" dxfId="246" priority="186">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="146" priority="89">
+    <cfRule type="expression" dxfId="245" priority="185">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="145" priority="88">
+    <cfRule type="expression" dxfId="244" priority="184">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="144" priority="87">
+    <cfRule type="expression" dxfId="243" priority="183">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="143" priority="86">
+    <cfRule type="expression" dxfId="242" priority="182">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="142" priority="85">
+    <cfRule type="expression" dxfId="241" priority="181">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="141" priority="84">
+    <cfRule type="expression" dxfId="240" priority="180">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="140" priority="83">
+    <cfRule type="expression" dxfId="239" priority="179">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="139" priority="82">
+    <cfRule type="expression" dxfId="238" priority="178">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="138" priority="81">
+    <cfRule type="expression" dxfId="237" priority="177">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="137" priority="80">
+    <cfRule type="expression" dxfId="236" priority="176">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="136" priority="79">
+    <cfRule type="expression" dxfId="235" priority="175">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="135" priority="78">
+    <cfRule type="expression" dxfId="234" priority="174">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="134" priority="77">
+    <cfRule type="expression" dxfId="233" priority="173">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="133" priority="76">
+    <cfRule type="expression" dxfId="232" priority="172">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="132" priority="75">
+    <cfRule type="expression" dxfId="231" priority="171">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="131" priority="74">
+    <cfRule type="expression" dxfId="230" priority="170">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:F7">
-    <cfRule type="expression" dxfId="130" priority="73">
+    <cfRule type="expression" dxfId="229" priority="169">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="129" priority="72">
+    <cfRule type="expression" dxfId="228" priority="168">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="128" priority="70">
+    <cfRule type="expression" dxfId="227" priority="166">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="71">
+    <cfRule type="expression" dxfId="226" priority="167">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:F7">
-    <cfRule type="expression" dxfId="126" priority="69">
+    <cfRule type="expression" dxfId="225" priority="165">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="125" priority="68">
+    <cfRule type="expression" dxfId="224" priority="164">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="124" priority="67">
+    <cfRule type="expression" dxfId="223" priority="163">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="123" priority="66">
+    <cfRule type="expression" dxfId="222" priority="162">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="122" priority="65">
+    <cfRule type="expression" dxfId="221" priority="161">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="121" priority="64">
+    <cfRule type="expression" dxfId="220" priority="160">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="120" priority="63">
+    <cfRule type="expression" dxfId="219" priority="159">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="119" priority="62">
+    <cfRule type="expression" dxfId="218" priority="158">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="118" priority="61">
+    <cfRule type="expression" dxfId="217" priority="157">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="117" priority="60">
+    <cfRule type="expression" dxfId="216" priority="156">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="116" priority="59">
+    <cfRule type="expression" dxfId="215" priority="155">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="115" priority="58">
+    <cfRule type="expression" dxfId="214" priority="154">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="114" priority="57">
+    <cfRule type="expression" dxfId="213" priority="153">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="113" priority="56">
+    <cfRule type="expression" dxfId="212" priority="152">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="112" priority="55">
+    <cfRule type="expression" dxfId="211" priority="151">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="111" priority="54">
+    <cfRule type="expression" dxfId="210" priority="150">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="110" priority="53">
+    <cfRule type="expression" dxfId="209" priority="149">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="109" priority="52">
+    <cfRule type="expression" dxfId="208" priority="148">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="108" priority="51">
+    <cfRule type="expression" dxfId="207" priority="147">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="107" priority="50">
+    <cfRule type="expression" dxfId="206" priority="146">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="106" priority="49">
+    <cfRule type="expression" dxfId="205" priority="145">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="105" priority="48">
+    <cfRule type="expression" dxfId="204" priority="144">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="104" priority="47">
+    <cfRule type="expression" dxfId="203" priority="143">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="103" priority="46">
+    <cfRule type="expression" dxfId="202" priority="142">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="102" priority="45">
+    <cfRule type="expression" dxfId="201" priority="141">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="101" priority="44">
+    <cfRule type="expression" dxfId="200" priority="140">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="100" priority="43">
+    <cfRule type="expression" dxfId="199" priority="139">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="99" priority="42">
+    <cfRule type="expression" dxfId="198" priority="138">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="98" priority="41">
+    <cfRule type="expression" dxfId="197" priority="137">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="97" priority="39">
+    <cfRule type="expression" dxfId="196" priority="135">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="40">
+    <cfRule type="expression" dxfId="195" priority="136">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="95" priority="38">
+    <cfRule type="expression" dxfId="194" priority="134">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="94" priority="37">
+    <cfRule type="expression" dxfId="193" priority="133">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="93" priority="36">
+    <cfRule type="expression" dxfId="192" priority="132">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="92" priority="35">
+    <cfRule type="expression" dxfId="191" priority="131">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="91" priority="34">
+    <cfRule type="expression" dxfId="190" priority="130">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="90" priority="33">
+    <cfRule type="expression" dxfId="189" priority="129">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="89" priority="32">
+    <cfRule type="expression" dxfId="188" priority="128">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="88" priority="31">
+    <cfRule type="expression" dxfId="187" priority="127">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="87" priority="30">
+    <cfRule type="expression" dxfId="186" priority="126">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="86" priority="29">
+    <cfRule type="expression" dxfId="185" priority="125">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="85" priority="28">
+    <cfRule type="expression" dxfId="184" priority="124">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="84" priority="27">
+    <cfRule type="expression" dxfId="183" priority="123">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="83" priority="26">
+    <cfRule type="expression" dxfId="182" priority="122">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="82" priority="25">
+    <cfRule type="expression" dxfId="181" priority="121">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="81" priority="24">
+    <cfRule type="expression" dxfId="180" priority="120">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="80" priority="23">
+    <cfRule type="expression" dxfId="179" priority="119">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="79" priority="22">
+    <cfRule type="expression" dxfId="178" priority="118">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="78" priority="21">
+    <cfRule type="expression" dxfId="177" priority="117">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="77" priority="20">
+    <cfRule type="expression" dxfId="176" priority="116">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="76" priority="19">
+    <cfRule type="expression" dxfId="175" priority="115">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="75" priority="18">
+    <cfRule type="expression" dxfId="174" priority="114">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="74" priority="17">
+    <cfRule type="expression" dxfId="173" priority="113">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="73" priority="16">
+    <cfRule type="expression" dxfId="172" priority="112">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="72" priority="15">
+    <cfRule type="expression" dxfId="171" priority="111">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="71" priority="14">
+    <cfRule type="expression" dxfId="170" priority="110">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="70" priority="13">
+    <cfRule type="expression" dxfId="169" priority="109">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="69" priority="12">
+    <cfRule type="expression" dxfId="168" priority="108">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="68" priority="11">
+    <cfRule type="expression" dxfId="167" priority="107">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="67" priority="10">
+    <cfRule type="expression" dxfId="166" priority="106">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="66" priority="9">
+    <cfRule type="expression" dxfId="165" priority="105">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="65" priority="8">
+    <cfRule type="expression" dxfId="164" priority="104">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="64" priority="7">
+    <cfRule type="expression" dxfId="163" priority="103">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="63" priority="6">
+    <cfRule type="expression" dxfId="162" priority="102">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="62" priority="5">
+    <cfRule type="expression" dxfId="161" priority="101">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="61" priority="4">
+    <cfRule type="expression" dxfId="160" priority="100">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="60" priority="3">
+    <cfRule type="expression" dxfId="159" priority="99">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="59" priority="2">
+    <cfRule type="expression" dxfId="158" priority="98">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="157" priority="97">
       <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="98" priority="96">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="97" priority="95">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="96" priority="94">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:F8">
+    <cfRule type="expression" dxfId="95" priority="93">
+      <formula>$B$26&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="94" priority="92">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="93" priority="90">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="91">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:F8">
+    <cfRule type="expression" dxfId="91" priority="89">
+      <formula>$B$8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="90" priority="88">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="89" priority="87">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="88" priority="86">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="87" priority="85">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="86" priority="84">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="85" priority="83">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="84" priority="82">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="83" priority="81">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="82" priority="80">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="81" priority="79">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="80" priority="78">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="79" priority="77">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="78" priority="76">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="77" priority="75">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="76" priority="74">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="75" priority="73">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="74" priority="72">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="73" priority="71">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="72" priority="70">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="71" priority="69">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="70" priority="68">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="69" priority="67">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="68" priority="66">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="67" priority="65">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="66" priority="64">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="65" priority="63">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="64" priority="62">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="63" priority="61">
+      <formula>$B$26&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="62" priority="59">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="60">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="60" priority="58">
+      <formula>$B$8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="59" priority="57">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="58" priority="56">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="57" priority="55">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="56" priority="54">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="55" priority="53">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="54" priority="52">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="53" priority="51">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="52" priority="50">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="51" priority="49">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="50" priority="48">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="49" priority="47">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="48" priority="46">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="47" priority="45">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="46" priority="44">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="45" priority="43">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="44" priority="42">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="43" priority="41">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="42" priority="40">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="41" priority="39">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="40" priority="38">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="39" priority="37">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="38" priority="36">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="37" priority="35">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" dxfId="36" priority="34">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="35" priority="33">
+      <formula>$B$26&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="34" priority="32">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="33" priority="31">
+      <formula>$B$8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="32" priority="30">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="31" priority="29">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="30" priority="28">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="29" priority="27">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="28" priority="26">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="27" priority="25">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="26" priority="24">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="25" priority="23">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="24" priority="22">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" dxfId="23" priority="21">
+      <formula>$B$28&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="22" priority="20">
+      <formula>$B$26&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="21" priority="18">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="19">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="19" priority="17">
+      <formula>$B$8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="18" priority="16">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="17" priority="15">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="16" priority="14">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="15" priority="13">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="14" priority="12">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="12" priority="10">
+      <formula>$B$26&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="11" priority="8">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="9">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="9" priority="7">
+      <formula>$B$8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -18909,6 +21746,7 @@
     <hyperlink ref="D7" location="Pyxl!A1" display="Pyxl"/>
     <hyperlink ref="E7" location="Universal!A1" display="Universal"/>
     <hyperlink ref="F7" location="Niki!A1" display="Niki"/>
+    <hyperlink ref="C8" location="Felo!A1" display="Felo"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19127,17 +21965,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="29" priority="3">
+    <cfRule type="expression" dxfId="128" priority="3">
       <formula>$B$40&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="28" priority="6">
+    <cfRule type="expression" dxfId="127" priority="6">
       <formula>$B$36&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="27" priority="7">
+    <cfRule type="expression" dxfId="126" priority="7">
       <formula>$B$15=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19641,17 +22479,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="26" priority="8">
+    <cfRule type="expression" dxfId="125" priority="8">
       <formula>$B$37&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="25" priority="9">
+    <cfRule type="expression" dxfId="124" priority="9">
       <formula>$B$17=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="24" priority="61">
+    <cfRule type="expression" dxfId="123" priority="61">
       <formula>$B$93&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19914,17 +22752,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="122" priority="1">
       <formula>$B$23=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="22" priority="4">
+    <cfRule type="expression" dxfId="121" priority="4">
       <formula>$B$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="21" priority="5">
+    <cfRule type="expression" dxfId="120" priority="5">
       <formula>$B$45&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20087,17 +22925,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="20" priority="3">
+    <cfRule type="expression" dxfId="119" priority="3">
       <formula>$B$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="118" priority="2">
       <formula>$B$45&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="117" priority="1">
       <formula>$B$27=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21931,17 +24769,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="116" priority="3">
       <formula>$B$54&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="115" priority="2">
       <formula>$B$52&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="114" priority="1">
       <formula>$B$32=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22314,17 +25152,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="14" priority="7">
+    <cfRule type="expression" dxfId="113" priority="7">
       <formula>$C$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="13" priority="8">
+    <cfRule type="expression" dxfId="112" priority="8">
       <formula>$C$33&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="12" priority="9">
+    <cfRule type="expression" dxfId="111" priority="9">
       <formula>$C$15=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22471,17 +25309,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="110" priority="3">
       <formula>$B$53&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="109" priority="2">
       <formula>$B$51&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="108" priority="1">
       <formula>$B$33=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22619,17 +25457,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="107" priority="10">
       <formula>$B$38&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="7" priority="11">
+    <cfRule type="expression" dxfId="106" priority="11">
       <formula>$B$36&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="105" priority="12">
       <formula>$B$16=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29775,22 +32613,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="57" priority="4">
+    <cfRule type="expression" dxfId="156" priority="4">
       <formula>$B$37&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="56" priority="3">
+    <cfRule type="expression" dxfId="155" priority="3">
       <formula>$B$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="55" priority="2">
+    <cfRule type="expression" dxfId="154" priority="2">
       <formula>$B$17=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="153" priority="1">
       <formula>$B$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30867,17 +33705,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="104" priority="10">
       <formula>$B$82&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="103" priority="11">
       <formula>$B$80&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="3" priority="12">
+    <cfRule type="expression" dxfId="102" priority="12">
       <formula>$B$49=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32203,17 +35041,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="101" priority="3">
       <formula>$B$82&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="100" priority="2">
       <formula>$B$80&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="99" priority="1">
       <formula>$B$49=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32222,6 +35060,803 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:L89"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="2:12">
+      <c r="C1" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12">
+      <c r="H2" s="77" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="H3" s="51">
+        <v>1</v>
+      </c>
+      <c r="I3" s="53"/>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="51" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="H4" s="56">
+        <v>49400330</v>
+      </c>
+      <c r="I4" s="57"/>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="57"/>
+      <c r="H5" s="56" t="s">
+        <v>1852</v>
+      </c>
+      <c r="I5" s="57"/>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="56" t="s">
+        <v>851</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="57"/>
+      <c r="H6" s="56">
+        <v>12</v>
+      </c>
+      <c r="I6" s="57"/>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="56" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="57"/>
+      <c r="H7" s="56">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="I7" s="57"/>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="56"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="57"/>
+      <c r="H8" s="56">
+        <v>101.52</v>
+      </c>
+      <c r="I8" s="57"/>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" s="112" t="s">
+        <v>871</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="57"/>
+      <c r="H9" s="56">
+        <v>65</v>
+      </c>
+      <c r="I9" s="57"/>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="113" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="57"/>
+      <c r="H10" s="54">
+        <v>35.53</v>
+      </c>
+      <c r="I10" s="55"/>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="56"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="57"/>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" s="112" t="s">
+        <v>873</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="57"/>
+      <c r="G12" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1846</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" s="113" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="57"/>
+      <c r="H13" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="56"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="57"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="56" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="57"/>
+      <c r="G15" t="s">
+        <v>1848</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1843</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="56" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="57"/>
+      <c r="H16" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="56"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="57"/>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="113" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="57"/>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="56"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="57"/>
+      <c r="H19" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="113" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="57"/>
+      <c r="H20" s="111" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="56"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="57"/>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="56" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="57"/>
+      <c r="H22" t="s">
+        <v>1856</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="56"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="57"/>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="B24" s="113" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="57"/>
+      <c r="H24" s="111" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="B25" s="113" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="57"/>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="B26" s="113" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="57"/>
+    </row>
+    <row r="27" spans="2:12">
+      <c r="B27" s="113" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="57"/>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" s="56"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="57"/>
+    </row>
+    <row r="29" spans="2:12">
+      <c r="B29" s="56" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="57"/>
+    </row>
+    <row r="30" spans="2:12">
+      <c r="B30" s="56" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="57"/>
+    </row>
+    <row r="31" spans="2:12">
+      <c r="B31" s="56"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="57"/>
+    </row>
+    <row r="32" spans="2:12">
+      <c r="B32" s="56" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="57"/>
+      <c r="H32" t="s">
+        <v>1857</v>
+      </c>
+      <c r="K32" t="s">
+        <v>1518</v>
+      </c>
+      <c r="L32" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" s="56" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="57"/>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" s="56" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="57"/>
+      <c r="H34" s="6" t="s">
+        <v>1858</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" s="56" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="57"/>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" s="56"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="57"/>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" s="56" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="57"/>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="B38" s="56" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="57"/>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39" s="56" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="57"/>
+    </row>
+    <row r="40" spans="2:12">
+      <c r="B40" s="56" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="57"/>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41" s="56" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="57"/>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="B42" s="56" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="57"/>
+    </row>
+    <row r="43" spans="2:12">
+      <c r="B43" s="56"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="57"/>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="B44" s="56" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="57"/>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="B45" s="56" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="57"/>
+    </row>
+    <row r="46" spans="2:12">
+      <c r="B46" s="56" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="57"/>
+    </row>
+    <row r="47" spans="2:12">
+      <c r="B47" s="56"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="57"/>
+    </row>
+    <row r="48" spans="2:12">
+      <c r="B48" s="56" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="57"/>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="56" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="57"/>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="56" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="57"/>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="56"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="57"/>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="56"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="57"/>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53" s="56" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="57"/>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54" s="56" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="57"/>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55" s="56"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="57"/>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="56" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="57"/>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="56" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="57"/>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="56" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="57"/>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59" s="56" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="57"/>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="B60" s="56" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="57"/>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="B61" s="56" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="57"/>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="B62" s="56" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="57"/>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="B63" s="56" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="57"/>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64" s="56" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="57"/>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="B65" s="56" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="57"/>
+    </row>
+    <row r="66" spans="2:8">
+      <c r="B66" s="56" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="57"/>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="B67" s="56" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="57"/>
+    </row>
+    <row r="68" spans="2:8">
+      <c r="B68" s="56" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="57"/>
+    </row>
+    <row r="69" spans="2:8">
+      <c r="B69" s="56" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="57"/>
+    </row>
+    <row r="70" spans="2:8">
+      <c r="B70" s="56"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="57"/>
+    </row>
+    <row r="71" spans="2:8">
+      <c r="B71" s="56" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="57"/>
+    </row>
+    <row r="72" spans="2:8">
+      <c r="B72" s="56" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="57"/>
+    </row>
+    <row r="73" spans="2:8">
+      <c r="B73" s="56"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="57"/>
+    </row>
+    <row r="74" spans="2:8">
+      <c r="B74" s="113" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="57"/>
+    </row>
+    <row r="75" spans="2:8">
+      <c r="B75" s="113" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="57"/>
+    </row>
+    <row r="76" spans="2:8">
+      <c r="B76" s="56"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="57"/>
+    </row>
+    <row r="77" spans="2:8">
+      <c r="B77" s="113" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="57"/>
+    </row>
+    <row r="78" spans="2:8">
+      <c r="B78" s="56"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="57"/>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="B79" s="56" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="57"/>
+      <c r="H79" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="B80" s="56" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="57"/>
+      <c r="H80" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9">
+      <c r="B81" s="56" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="57"/>
+      <c r="H81" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9">
+      <c r="B82" s="56" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="57"/>
+    </row>
+    <row r="83" spans="2:9">
+      <c r="B83" s="56"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="57"/>
+      <c r="H83" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9">
+      <c r="B84" s="56" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="57"/>
+      <c r="H84" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9">
+      <c r="B85" s="56" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="57"/>
+      <c r="H85" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9">
+      <c r="B86" s="56" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="57"/>
+    </row>
+    <row r="87" spans="2:9">
+      <c r="B87" s="56"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="57"/>
+      <c r="H87" s="114" t="s">
+        <v>1904</v>
+      </c>
+      <c r="I87" s="32" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9">
+      <c r="B88" s="56"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="57"/>
+    </row>
+    <row r="89" spans="2:9">
+      <c r="B89" s="54" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="55"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>#REF!=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>#REF!&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>#REF!&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="C1" location="Home!A1" display="Home!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -34557,17 +38192,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="53" priority="4">
+    <cfRule type="expression" dxfId="152" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="52" priority="3">
+    <cfRule type="expression" dxfId="151" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="51" priority="10">
+    <cfRule type="expression" dxfId="150" priority="10">
       <formula>$C$12=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34859,17 +38494,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="50" priority="2">
+    <cfRule type="expression" dxfId="149" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="49" priority="5">
+    <cfRule type="expression" dxfId="148" priority="5">
       <formula>$B$44&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="48" priority="6">
+    <cfRule type="expression" dxfId="147" priority="6">
       <formula>$B$42&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35246,17 +38881,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="47" priority="4">
+    <cfRule type="expression" dxfId="146" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="46" priority="3">
+    <cfRule type="expression" dxfId="145" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="45" priority="2">
+    <cfRule type="expression" dxfId="144" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35535,22 +39170,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="44" priority="4">
+    <cfRule type="expression" dxfId="143" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="43" priority="3">
+    <cfRule type="expression" dxfId="142" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="42" priority="2">
+    <cfRule type="expression" dxfId="141" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="140" priority="1">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35920,22 +39555,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="40" priority="4">
+    <cfRule type="expression" dxfId="139" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="39" priority="3">
+    <cfRule type="expression" dxfId="138" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="38" priority="2">
+    <cfRule type="expression" dxfId="137" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="136" priority="1">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37255,17 +40890,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="36" priority="4">
+    <cfRule type="expression" dxfId="135" priority="4">
       <formula>$B$103&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="35" priority="3">
+    <cfRule type="expression" dxfId="134" priority="3">
       <formula>$B$101&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="34" priority="2">
+    <cfRule type="expression" dxfId="133" priority="2">
       <formula>$B$83=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37406,22 +41041,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="33" priority="4">
+    <cfRule type="expression" dxfId="132" priority="4">
       <formula>$B$32&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="32" priority="3">
+    <cfRule type="expression" dxfId="131" priority="3">
       <formula>$B$30&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="31" priority="2">
+    <cfRule type="expression" dxfId="130" priority="2">
       <formula>$B$12=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="129" priority="1">
       <formula>$B$30&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Regex 04.02.25.xlsx
+++ b/Regex 04.02.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="787" firstSheet="3" activeTab="23"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="787" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3283" uniqueCount="1906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3315" uniqueCount="1930">
   <si>
     <t>with (?mx) with description</t>
   </si>
@@ -16990,17 +16990,312 @@
       <t>1, '494 003 30', 'SD CA Nail-lifter x 100', 12, 8.46, 65.0, 35.532000000000004]</t>
     </r>
   </si>
+  <si>
+    <t>[^\s]*</t>
+  </si>
+  <si>
+    <t>^ at the beginning of a character class means NOT</t>
+  </si>
+  <si>
+    <t>\s = any whitespace character (space, tab, newline, etc.)</t>
+  </si>
+  <si>
+    <t>Examples it matches:</t>
+  </si>
+  <si>
+    <t>A 9 ( / -</t>
+  </si>
+  <si>
+    <t>Examples it does not match:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ' (space)</t>
+  </si>
+  <si>
+    <t>\t (tab)</t>
+  </si>
+  <si>
+    <t>\n (newline)</t>
+  </si>
+  <si>
+    <t>Match any character that is not whitespace 0 or more times</t>
+  </si>
+  <si>
+    <t>.*</t>
+  </si>
+  <si>
+    <t>Match any character (except newline in most regex engines) 0 or more times</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So it matches </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>everything until the end of the line</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, including spaces.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">How </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>findall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() works</t>
+    </r>
+  </si>
+  <si>
+    <t>pattern = r"match this (?:match that)"</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = "match this match that"</t>
+    </r>
+  </si>
+  <si>
+    <t>['match this match that']</t>
+  </si>
+  <si>
+    <r>
+      <t>pattern = r"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>match this</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (?:match that)"</t>
+    </r>
+  </si>
+  <si>
+    <t>['match this']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When there is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>one capturing group</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, findall() returns only that group's contents:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When there are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no capturing groups</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, findall() returns the full matches:</t>
+    </r>
+  </si>
+  <si>
+    <t>pattern = r"(match) (this) (?:match that)"</t>
+  </si>
+  <si>
+    <t>[('match', 'this')]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When there are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>multiple capturing groups</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, findall() returns </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tuples</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="72">
+  <fonts count="73">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -17777,73 +18072,73 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -17851,23 +18146,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -17888,33 +18183,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -17922,30 +18217,439 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="293">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -18594,412 +19298,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -20002,9 +20300,9 @@
   <colors>
     <mruColors>
       <color rgb="FFDA7BB9"/>
+      <color rgb="FFA47A20"/>
       <color rgb="FF179A77"/>
       <color rgb="FFA626A4"/>
-      <color rgb="FFA47A20"/>
       <color rgb="FF7D7DFF"/>
       <color rgb="FFFF33CC"/>
     </mruColors>
@@ -20026,13 +20324,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>337</xdr:row>
+      <xdr:row>359</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>538163</xdr:colOff>
-      <xdr:row>345</xdr:row>
+      <xdr:row>367</xdr:row>
       <xdr:rowOff>147638</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -20073,13 +20371,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>566738</xdr:colOff>
-      <xdr:row>337</xdr:row>
+      <xdr:row>359</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>345</xdr:row>
+      <xdr:row>367</xdr:row>
       <xdr:rowOff>147638</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -20120,13 +20418,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>350</xdr:row>
+      <xdr:row>372</xdr:row>
       <xdr:rowOff>176213</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>547687</xdr:colOff>
-      <xdr:row>352</xdr:row>
+      <xdr:row>374</xdr:row>
       <xdr:rowOff>4763</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -20167,13 +20465,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>223842</xdr:colOff>
-      <xdr:row>351</xdr:row>
+      <xdr:row>373</xdr:row>
       <xdr:rowOff>4</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>352</xdr:row>
+      <xdr:row>374</xdr:row>
       <xdr:rowOff>4763</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -21254,474 +21552,474 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="98" priority="96">
+    <cfRule type="expression" dxfId="156" priority="96">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="97" priority="95">
+    <cfRule type="expression" dxfId="155" priority="95">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="96" priority="94">
+    <cfRule type="expression" dxfId="154" priority="94">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:F8">
-    <cfRule type="expression" dxfId="95" priority="93">
+    <cfRule type="expression" dxfId="153" priority="93">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="94" priority="92">
+    <cfRule type="expression" dxfId="152" priority="92">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="93" priority="90">
+    <cfRule type="expression" dxfId="151" priority="90">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="91">
+    <cfRule type="expression" dxfId="150" priority="91">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:F8">
-    <cfRule type="expression" dxfId="91" priority="89">
+    <cfRule type="expression" dxfId="149" priority="89">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="90" priority="88">
+    <cfRule type="expression" dxfId="148" priority="88">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="89" priority="87">
+    <cfRule type="expression" dxfId="147" priority="87">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="88" priority="86">
+    <cfRule type="expression" dxfId="146" priority="86">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="87" priority="85">
+    <cfRule type="expression" dxfId="145" priority="85">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="86" priority="84">
+    <cfRule type="expression" dxfId="144" priority="84">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="85" priority="83">
+    <cfRule type="expression" dxfId="143" priority="83">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="84" priority="82">
+    <cfRule type="expression" dxfId="142" priority="82">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="83" priority="81">
+    <cfRule type="expression" dxfId="141" priority="81">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="82" priority="80">
+    <cfRule type="expression" dxfId="140" priority="80">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="81" priority="79">
+    <cfRule type="expression" dxfId="139" priority="79">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="80" priority="78">
+    <cfRule type="expression" dxfId="138" priority="78">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="79" priority="77">
+    <cfRule type="expression" dxfId="137" priority="77">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="78" priority="76">
+    <cfRule type="expression" dxfId="136" priority="76">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="77" priority="75">
+    <cfRule type="expression" dxfId="135" priority="75">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="76" priority="74">
+    <cfRule type="expression" dxfId="134" priority="74">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="75" priority="73">
+    <cfRule type="expression" dxfId="133" priority="73">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="74" priority="72">
+    <cfRule type="expression" dxfId="132" priority="72">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="73" priority="71">
+    <cfRule type="expression" dxfId="131" priority="71">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="72" priority="70">
+    <cfRule type="expression" dxfId="130" priority="70">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="71" priority="69">
+    <cfRule type="expression" dxfId="129" priority="69">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="70" priority="68">
+    <cfRule type="expression" dxfId="128" priority="68">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="69" priority="67">
+    <cfRule type="expression" dxfId="127" priority="67">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="68" priority="66">
+    <cfRule type="expression" dxfId="126" priority="66">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="67" priority="65">
+    <cfRule type="expression" dxfId="125" priority="65">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="66" priority="64">
+    <cfRule type="expression" dxfId="124" priority="64">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="65" priority="63">
+    <cfRule type="expression" dxfId="123" priority="63">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="64" priority="62">
+    <cfRule type="expression" dxfId="122" priority="62">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="63" priority="61">
+    <cfRule type="expression" dxfId="121" priority="61">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="62" priority="59">
+    <cfRule type="expression" dxfId="120" priority="59">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="60">
+    <cfRule type="expression" dxfId="119" priority="60">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="60" priority="58">
+    <cfRule type="expression" dxfId="118" priority="58">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="59" priority="57">
+    <cfRule type="expression" dxfId="117" priority="57">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="58" priority="56">
+    <cfRule type="expression" dxfId="116" priority="56">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="57" priority="55">
+    <cfRule type="expression" dxfId="115" priority="55">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="56" priority="54">
+    <cfRule type="expression" dxfId="114" priority="54">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="55" priority="53">
+    <cfRule type="expression" dxfId="113" priority="53">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="54" priority="52">
+    <cfRule type="expression" dxfId="112" priority="52">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="53" priority="51">
+    <cfRule type="expression" dxfId="111" priority="51">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="52" priority="50">
+    <cfRule type="expression" dxfId="110" priority="50">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="51" priority="49">
+    <cfRule type="expression" dxfId="109" priority="49">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="50" priority="48">
+    <cfRule type="expression" dxfId="108" priority="48">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="49" priority="47">
+    <cfRule type="expression" dxfId="107" priority="47">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="48" priority="46">
+    <cfRule type="expression" dxfId="106" priority="46">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="47" priority="45">
+    <cfRule type="expression" dxfId="105" priority="45">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="46" priority="44">
+    <cfRule type="expression" dxfId="104" priority="44">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="45" priority="43">
+    <cfRule type="expression" dxfId="103" priority="43">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="44" priority="42">
+    <cfRule type="expression" dxfId="102" priority="42">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="43" priority="41">
+    <cfRule type="expression" dxfId="101" priority="41">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="42" priority="40">
+    <cfRule type="expression" dxfId="100" priority="40">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="41" priority="39">
+    <cfRule type="expression" dxfId="99" priority="39">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="40" priority="38">
+    <cfRule type="expression" dxfId="98" priority="38">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="39" priority="37">
+    <cfRule type="expression" dxfId="97" priority="37">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="38" priority="36">
+    <cfRule type="expression" dxfId="96" priority="36">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="37" priority="35">
+    <cfRule type="expression" dxfId="95" priority="35">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="36" priority="34">
+    <cfRule type="expression" dxfId="94" priority="34">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="35" priority="33">
+    <cfRule type="expression" dxfId="93" priority="33">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="34" priority="32">
+    <cfRule type="expression" dxfId="92" priority="32">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="33" priority="31">
+    <cfRule type="expression" dxfId="91" priority="31">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="32" priority="30">
+    <cfRule type="expression" dxfId="90" priority="30">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="31" priority="29">
+    <cfRule type="expression" dxfId="89" priority="29">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="30" priority="28">
+    <cfRule type="expression" dxfId="88" priority="28">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="29" priority="27">
+    <cfRule type="expression" dxfId="87" priority="27">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="28" priority="26">
+    <cfRule type="expression" dxfId="86" priority="26">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="27" priority="25">
+    <cfRule type="expression" dxfId="85" priority="25">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="26" priority="24">
+    <cfRule type="expression" dxfId="84" priority="24">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="25" priority="23">
+    <cfRule type="expression" dxfId="83" priority="23">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="24" priority="22">
+    <cfRule type="expression" dxfId="82" priority="22">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="23" priority="21">
+    <cfRule type="expression" dxfId="81" priority="21">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="22" priority="20">
+    <cfRule type="expression" dxfId="80" priority="20">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="21" priority="18">
+    <cfRule type="expression" dxfId="79" priority="18">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="19">
+    <cfRule type="expression" dxfId="78" priority="19">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="19" priority="17">
+    <cfRule type="expression" dxfId="77" priority="17">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="76" priority="16">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="17" priority="15">
+    <cfRule type="expression" dxfId="75" priority="15">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="16" priority="14">
+    <cfRule type="expression" dxfId="74" priority="14">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="73" priority="13">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="72" priority="12">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="71" priority="11">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="12" priority="10">
+    <cfRule type="expression" dxfId="70" priority="10">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="11" priority="8">
+    <cfRule type="expression" dxfId="69" priority="8">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="68" priority="9">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="67" priority="7">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="66" priority="6">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="65" priority="5">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="64" priority="4">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="63" priority="3">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="62" priority="2">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21965,17 +22263,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="128" priority="3">
+    <cfRule type="expression" dxfId="35" priority="3">
       <formula>$B$40&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="127" priority="6">
+    <cfRule type="expression" dxfId="34" priority="6">
       <formula>$B$36&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="126" priority="7">
+    <cfRule type="expression" dxfId="33" priority="7">
       <formula>$B$15=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22479,17 +22777,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="125" priority="8">
+    <cfRule type="expression" dxfId="32" priority="8">
       <formula>$B$37&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="124" priority="9">
+    <cfRule type="expression" dxfId="31" priority="9">
       <formula>$B$17=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="123" priority="61">
+    <cfRule type="expression" dxfId="30" priority="61">
       <formula>$B$93&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22752,17 +23050,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="122" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>$B$23=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="121" priority="4">
+    <cfRule type="expression" dxfId="28" priority="4">
       <formula>$B$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="120" priority="5">
+    <cfRule type="expression" dxfId="27" priority="5">
       <formula>$B$45&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22925,17 +23223,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="119" priority="3">
+    <cfRule type="expression" dxfId="26" priority="3">
       <formula>$B$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="118" priority="2">
+    <cfRule type="expression" dxfId="25" priority="2">
       <formula>$B$45&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="117" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>$B$27=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24769,17 +25067,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="116" priority="3">
+    <cfRule type="expression" dxfId="23" priority="3">
       <formula>$B$54&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="115" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>$B$52&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="114" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>$B$32=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25152,17 +25450,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="113" priority="7">
+    <cfRule type="expression" dxfId="20" priority="7">
       <formula>$C$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="112" priority="8">
+    <cfRule type="expression" dxfId="19" priority="8">
       <formula>$C$33&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="111" priority="9">
+    <cfRule type="expression" dxfId="18" priority="9">
       <formula>$C$15=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25309,17 +25607,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="110" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$B$53&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="109" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>$B$51&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="108" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$B$33=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25457,17 +25755,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="107" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>$B$38&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="106" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>$B$36&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="105" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$B$16=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25480,7 +25778,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O367"/>
+  <dimension ref="A1:O377"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
@@ -25672,1592 +25970,1618 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="8" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="D33" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="D34" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="D35" s="8" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="E36" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="D37" s="8" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="E38" s="6" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="E39" s="6"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1917</v>
+      </c>
+      <c r="E40" s="6"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="C41" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="8" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="8"/>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="8" t="s">
+    <row r="46" spans="1:10">
+      <c r="A46" s="8"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B47" s="8" t="s">
         <v>1184</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>1169</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F47" s="8" t="s">
         <v>1171</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J47" s="8" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
-      <c r="A38" t="s">
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
         <v>1166</v>
       </c>
-      <c r="B38" s="49" t="s">
+      <c r="B48" s="49" t="s">
         <v>1179</v>
       </c>
-      <c r="D38">
+      <c r="D48">
         <v>1</v>
-      </c>
-      <c r="F38" t="s">
-        <v>29</v>
-      </c>
-      <c r="J38" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B39" s="49" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="F39" t="s">
-        <v>29</v>
-      </c>
-      <c r="J39" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B40" s="49" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D40">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B41" s="49" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D41">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>29</v>
-      </c>
-      <c r="J41" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B43" s="49" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="F43" t="s">
-        <v>29</v>
-      </c>
-      <c r="J43" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B44" s="49" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D44">
-        <v>2</v>
-      </c>
-      <c r="F44" t="s">
-        <v>29</v>
-      </c>
-      <c r="J44" t="s">
-        <v>1175</v>
-      </c>
-      <c r="L44" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B45" s="49" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D45">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>29</v>
-      </c>
-      <c r="J45" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B46" s="49" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D46">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>29</v>
-      </c>
-      <c r="J46" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="B47" s="49"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B48" s="49" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D48">
-        <v>5</v>
       </c>
       <c r="F48" t="s">
         <v>29</v>
       </c>
       <c r="J48" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>1185</v>
+        <v>1168</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F49" t="s">
         <v>29</v>
       </c>
       <c r="J49" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B50" s="49" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+      <c r="F50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J50" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B51" s="49" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D51">
+        <v>6</v>
+      </c>
+      <c r="F51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J51" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B53" s="49" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>29</v>
+      </c>
+      <c r="J53" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B54" s="49" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="F54" t="s">
+        <v>29</v>
+      </c>
+      <c r="J54" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L54" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B55" s="49" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+      <c r="F55" t="s">
+        <v>29</v>
+      </c>
+      <c r="J55" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B56" s="49" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="F56" t="s">
+        <v>29</v>
+      </c>
+      <c r="J56" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="B57" s="49"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B58" s="49" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>29</v>
+      </c>
+      <c r="J58" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B59" s="49" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="F59" t="s">
+        <v>29</v>
+      </c>
+      <c r="J59" t="s">
         <v>1186</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
-      <c r="B50" s="49"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="10" t="s">
+    <row r="60" spans="1:12">
+      <c r="B60" s="49"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="10" t="s">
+    <row r="64" spans="1:12">
+      <c r="A64" s="10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="10"/>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="24" t="s">
+    <row r="65" spans="1:3">
+      <c r="A65" s="10"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C66" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="24" t="s">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C67" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="24"/>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="8" t="s">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24"/>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="8" t="s">
         <v>1148</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="8"/>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="8"/>
-      <c r="B61" t="s">
+    <row r="70" spans="1:3">
+      <c r="A70" s="8"/>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="8"/>
+      <c r="B71" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="8"/>
-      <c r="C62" t="s">
+    <row r="72" spans="1:3">
+      <c r="A72" s="8"/>
+      <c r="C72" t="s">
         <v>1149</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="8"/>
-      <c r="C63" t="s">
+    <row r="73" spans="1:3">
+      <c r="A73" s="8"/>
+      <c r="C73" t="s">
         <v>1150</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="8"/>
-      <c r="C64" t="s">
+    <row r="74" spans="1:3">
+      <c r="A74" s="8"/>
+      <c r="C74" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="8"/>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="8"/>
-      <c r="C66" t="s">
+    <row r="75" spans="1:3">
+      <c r="A75" s="8"/>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="8"/>
+      <c r="C76" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="8"/>
-      <c r="C67" t="s">
+    <row r="77" spans="1:3">
+      <c r="A77" s="8"/>
+      <c r="C77" t="s">
         <v>1161</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="8"/>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24"/>
-      <c r="B69" t="s">
+    <row r="78" spans="1:3">
+      <c r="A78" s="8"/>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="24"/>
+      <c r="B79" t="s">
         <v>1152</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24"/>
-      <c r="C70" t="s">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24"/>
+      <c r="C80" t="s">
         <v>1153</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24"/>
-      <c r="C71" t="s">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24"/>
+      <c r="C81" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24"/>
-      <c r="C72" t="s">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24"/>
+      <c r="C82" t="s">
         <v>1155</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24"/>
-      <c r="C73" t="s">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24"/>
+      <c r="C83" t="s">
         <v>1156</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24"/>
-      <c r="C74" t="s">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24"/>
+      <c r="C84" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24"/>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="48" t="s">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24"/>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="48" t="s">
         <v>1158</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="48"/>
-      <c r="B77" t="s">
+    <row r="87" spans="1:3">
+      <c r="A87" s="48"/>
+      <c r="B87" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="48"/>
-      <c r="B78" t="s">
+    <row r="88" spans="1:3">
+      <c r="A88" s="48"/>
+      <c r="B88" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="48"/>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="48"/>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="34" t="s">
+    <row r="89" spans="1:3">
+      <c r="A89" s="48"/>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="48"/>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="34" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
-      <c r="B83" s="34" t="s">
+    <row r="93" spans="1:3">
+      <c r="B93" s="34" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="B84" s="34" t="s">
+    <row r="94" spans="1:3">
+      <c r="B94" s="34" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="B85" s="34" t="s">
+    <row r="95" spans="1:3">
+      <c r="B95" s="34" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="B86" s="34" t="s">
+    <row r="96" spans="1:3">
+      <c r="B96" s="34" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="B87" s="34" t="s">
+    <row r="97" spans="1:2">
+      <c r="B97" s="34" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
-      <c r="B88" s="34" t="s">
+    <row r="98" spans="1:2">
+      <c r="B98" s="34" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
-      <c r="B89" s="34"/>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
+    <row r="99" spans="1:2">
+      <c r="B99" s="34"/>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
         <v>771</v>
       </c>
-      <c r="B90" s="34"/>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" t="s">
+      <c r="B100" s="34"/>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
         <v>770</v>
       </c>
-      <c r="B91" s="34"/>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" t="s">
+      <c r="B101" s="34"/>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
         <v>4</v>
       </c>
-      <c r="B92" s="34"/>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="B93" s="34"/>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="8" t="s">
+      <c r="B102" s="34"/>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="B103" s="34"/>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="8" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
-      <c r="B97" t="s">
+    <row r="107" spans="1:2">
+      <c r="B107" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
-      <c r="B99" t="s">
+    <row r="109" spans="1:2">
+      <c r="B109" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
-      <c r="B100" t="s">
+    <row r="110" spans="1:2">
+      <c r="B110" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
-      <c r="B101" t="s">
+    <row r="111" spans="1:2">
+      <c r="B111" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
-      <c r="B102" t="s">
+    <row r="112" spans="1:2">
+      <c r="B112" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
-      <c r="B104" t="s">
+    <row r="114" spans="1:5">
+      <c r="B114" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
-      <c r="B106" t="s">
+    <row r="116" spans="1:5">
+      <c r="B116" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
-      <c r="B107" t="s">
+    <row r="117" spans="1:5">
+      <c r="B117" t="s">
         <v>292</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E117" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
-      <c r="B109" t="s">
+    <row r="119" spans="1:5">
+      <c r="B119" t="s">
         <v>293</v>
       </c>
-      <c r="E109" s="5">
+      <c r="E119" s="5">
         <v>3000025478</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
-      <c r="B110" t="s">
+    <row r="120" spans="1:5">
+      <c r="B120" t="s">
         <v>294</v>
       </c>
-      <c r="E110" s="5">
+      <c r="E120" s="5">
         <v>3000025469</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="8" t="s">
+    <row r="122" spans="1:5">
+      <c r="A122" s="8" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="A113" s="8"/>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="B114" t="s">
+    <row r="123" spans="1:5">
+      <c r="A123" s="8"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="B124" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" t="s">
+    <row r="126" spans="1:5">
+      <c r="B126" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" t="s">
+    <row r="127" spans="1:5">
+      <c r="B127" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" t="s">
+    <row r="128" spans="1:5">
+      <c r="B128" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" t="s">
+    <row r="129" spans="1:6">
+      <c r="B129" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
-      <c r="B121" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
-      <c r="B123" t="s">
+    <row r="133" spans="1:6">
+      <c r="B133" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
-      <c r="B124" t="s">
+    <row r="134" spans="1:6">
+      <c r="B134" t="s">
         <v>292</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="F134" s="5" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" t="s">
         <v>293</v>
       </c>
-      <c r="F126" s="27">
+      <c r="F136" s="27">
         <v>45246</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" t="s">
+    <row r="137" spans="1:6">
+      <c r="B137" t="s">
         <v>300</v>
       </c>
-      <c r="F127" s="27">
+      <c r="F137" s="27">
         <v>45246</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="8" t="s">
+    <row r="139" spans="1:6">
+      <c r="A139" s="8" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
-      <c r="B131" t="s">
+    <row r="141" spans="1:6">
+      <c r="B141" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
-      <c r="B132" t="s">
+    <row r="142" spans="1:6">
+      <c r="B142" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
-      <c r="B134" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
-      <c r="B135" t="s">
+    <row r="145" spans="2:6">
+      <c r="B145" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
-      <c r="B136" t="s">
+    <row r="146" spans="2:6">
+      <c r="B146" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
-      <c r="B137" t="s">
+    <row r="147" spans="2:6">
+      <c r="B147" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
-      <c r="B139" t="s">
+    <row r="149" spans="2:6">
+      <c r="B149" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
-      <c r="B141" t="s">
+    <row r="151" spans="2:6">
+      <c r="B151" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
-      <c r="B143" t="s">
+    <row r="153" spans="2:6">
+      <c r="B153" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
-      <c r="B144" t="s">
+    <row r="154" spans="2:6">
+      <c r="B154" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
-      <c r="B146" t="s">
+    <row r="156" spans="2:6">
+      <c r="B156" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
-      <c r="B147" t="s">
+    <row r="157" spans="2:6">
+      <c r="B157" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
-      <c r="B149" t="s">
+    <row r="159" spans="2:6">
+      <c r="B159" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
-      <c r="B150" t="s">
+    <row r="160" spans="2:6">
+      <c r="B160" t="s">
         <v>312</v>
       </c>
-      <c r="F150" s="27">
+      <c r="F160" s="27">
         <v>45246</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
-      <c r="B151" t="s">
+    <row r="161" spans="1:9">
+      <c r="B161" t="s">
         <v>313</v>
       </c>
-      <c r="F151" s="27">
+      <c r="F161" s="27">
         <v>45248</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
-      <c r="A153" s="8" t="s">
+    <row r="163" spans="1:9">
+      <c r="A163" s="8" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
-      <c r="A154" s="8"/>
-      <c r="B154" t="s">
+    <row r="164" spans="1:9">
+      <c r="A164" s="8"/>
+      <c r="B164" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
-      <c r="A155" s="8"/>
-    </row>
-    <row r="156" spans="1:9">
-      <c r="C156" t="s">
+    <row r="165" spans="1:9">
+      <c r="A165" s="8"/>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="C166" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
-      <c r="C157" t="s">
+    <row r="167" spans="1:9">
+      <c r="C167" t="s">
         <v>749</v>
       </c>
-      <c r="I157" t="s">
+      <c r="I167" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
-      <c r="C159" t="s">
+    <row r="169" spans="1:9">
+      <c r="C169" t="s">
         <v>747</v>
       </c>
-      <c r="I159" t="s">
+      <c r="I169" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
-      <c r="C161" t="s">
+    <row r="171" spans="1:9">
+      <c r="C171" t="s">
         <v>744</v>
       </c>
-      <c r="I161" t="s">
+      <c r="I171" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
-      <c r="C163" t="s">
+    <row r="173" spans="1:9">
+      <c r="C173" t="s">
         <v>745</v>
       </c>
-      <c r="E163" s="5" t="s">
+      <c r="E173" s="5" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
-      <c r="A165" s="8" t="s">
+    <row r="175" spans="1:9">
+      <c r="A175" s="8" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
-      <c r="A166" s="8"/>
-    </row>
-    <row r="167" spans="1:9">
-      <c r="B167" t="s">
+    <row r="176" spans="1:9">
+      <c r="A176" s="8"/>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
-      <c r="B168" t="s">
+    <row r="178" spans="2:6">
+      <c r="B178" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="169" spans="1:9">
-      <c r="B169" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9">
-      <c r="B170" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9">
-      <c r="B172" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9">
-      <c r="B173" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9">
-      <c r="B174" t="s">
-        <v>292</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9">
-      <c r="F175" s="5"/>
-    </row>
-    <row r="176" spans="1:9">
-      <c r="F176" s="5"/>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="F177" s="5"/>
-    </row>
-    <row r="178" spans="2:6">
-      <c r="B178" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="F178" s="5"/>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6">
+      <c r="B183" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" t="s">
+        <v>292</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="F185" s="5"/>
+    </row>
+    <row r="186" spans="2:6">
+      <c r="F186" s="5"/>
+    </row>
+    <row r="187" spans="2:6">
+      <c r="F187" s="5"/>
+    </row>
+    <row r="188" spans="2:6">
+      <c r="B188" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="F188" s="5"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" t="s">
         <v>780</v>
       </c>
-      <c r="F179" s="5"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" t="s">
+      <c r="F189" s="5"/>
+    </row>
+    <row r="190" spans="2:6">
+      <c r="B190" t="s">
         <v>781</v>
       </c>
-      <c r="F180" s="5"/>
-    </row>
-    <row r="181" spans="2:6">
-      <c r="F181" s="5"/>
-    </row>
-    <row r="182" spans="2:6">
-      <c r="C182">
-        <v>1</v>
-      </c>
-      <c r="D182" t="s">
-        <v>779</v>
-      </c>
-      <c r="F182" s="5"/>
-    </row>
-    <row r="183" spans="2:6">
-      <c r="C183">
-        <v>2</v>
-      </c>
-      <c r="D183" t="s">
-        <v>782</v>
-      </c>
-      <c r="F183" s="5"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="F184" s="5"/>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" t="s">
-        <v>783</v>
-      </c>
-      <c r="F185" s="5"/>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" t="s">
-        <v>784</v>
-      </c>
-      <c r="F186" s="5"/>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" t="s">
-        <v>785</v>
-      </c>
-      <c r="F187" s="5"/>
-    </row>
-    <row r="188" spans="2:6">
-      <c r="F188" s="5"/>
-    </row>
-    <row r="189" spans="2:6">
-      <c r="F189" s="5"/>
-    </row>
-    <row r="190" spans="2:6">
       <c r="F190" s="5"/>
     </row>
     <row r="191" spans="2:6">
       <c r="F191" s="5"/>
     </row>
     <row r="192" spans="2:6">
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192" t="s">
+        <v>779</v>
+      </c>
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="2:6">
+      <c r="C193">
+        <v>2</v>
+      </c>
+      <c r="D193" t="s">
+        <v>782</v>
+      </c>
       <c r="F193" s="5"/>
     </row>
     <row r="194" spans="2:6">
       <c r="F194" s="5"/>
     </row>
+    <row r="195" spans="2:6">
+      <c r="B195" t="s">
+        <v>783</v>
+      </c>
+      <c r="F195" s="5"/>
+    </row>
     <row r="196" spans="2:6">
       <c r="B196" t="s">
+        <v>784</v>
+      </c>
+      <c r="F196" s="5"/>
+    </row>
+    <row r="197" spans="2:6">
+      <c r="B197" t="s">
+        <v>785</v>
+      </c>
+      <c r="F197" s="5"/>
+    </row>
+    <row r="198" spans="2:6">
+      <c r="F198" s="5"/>
+    </row>
+    <row r="199" spans="2:6">
+      <c r="F199" s="5"/>
+    </row>
+    <row r="200" spans="2:6">
+      <c r="F200" s="5"/>
+    </row>
+    <row r="201" spans="2:6">
+      <c r="F201" s="5"/>
+    </row>
+    <row r="202" spans="2:6">
+      <c r="F202" s="5"/>
+    </row>
+    <row r="203" spans="2:6">
+      <c r="F203" s="5"/>
+    </row>
+    <row r="204" spans="2:6">
+      <c r="F204" s="5"/>
+    </row>
+    <row r="206" spans="2:6">
+      <c r="B206" t="s">
         <v>1232</v>
       </c>
     </row>
-    <row r="198" spans="2:6">
-      <c r="B198" t="s">
+    <row r="208" spans="2:6">
+      <c r="B208" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="199" spans="2:6">
-      <c r="C199" s="35" t="s">
+    <row r="209" spans="2:4">
+      <c r="C209" s="35" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="200" spans="2:6">
-      <c r="C200" s="35" t="s">
+    <row r="210" spans="2:4">
+      <c r="C210" s="35" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="201" spans="2:6">
-      <c r="C201" s="35" t="s">
+    <row r="211" spans="2:4">
+      <c r="C211" s="35" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="202" spans="2:6">
-      <c r="D202" t="s">
+    <row r="212" spans="2:4">
+      <c r="D212" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="204" spans="2:6">
-      <c r="B204" t="s">
+    <row r="214" spans="2:4">
+      <c r="B214" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="206" spans="2:6">
-      <c r="B206" s="8" t="s">
+    <row r="216" spans="2:4">
+      <c r="B216" s="8" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="207" spans="2:6">
-      <c r="C207" s="35" t="s">
+    <row r="217" spans="2:4">
+      <c r="C217" s="35" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="209" spans="2:13">
-      <c r="C209" t="s">
+    <row r="219" spans="2:4">
+      <c r="C219" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="211" spans="2:13">
-      <c r="B211" s="36" t="s">
+    <row r="221" spans="2:4">
+      <c r="B221" s="36" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="212" spans="2:13" ht="15">
-      <c r="B212" s="36" t="s">
+    <row r="222" spans="2:4" ht="15">
+      <c r="B222" s="36" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="213" spans="2:13">
-      <c r="B213" s="36"/>
-    </row>
-    <row r="214" spans="2:13">
-      <c r="B214" s="36" t="s">
+    <row r="223" spans="2:4">
+      <c r="B223" s="36"/>
+    </row>
+    <row r="224" spans="2:4">
+      <c r="B224" s="36" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="215" spans="2:13">
-      <c r="B215" s="36"/>
-    </row>
-    <row r="216" spans="2:13">
-      <c r="B216" s="36" t="s">
+    <row r="225" spans="2:13">
+      <c r="B225" s="36"/>
+    </row>
+    <row r="226" spans="2:13">
+      <c r="B226" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="E216" s="8" t="s">
+      <c r="E226" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="G216" s="8" t="s">
+      <c r="G226" s="8" t="s">
         <v>994</v>
       </c>
-      <c r="J216" s="8"/>
-      <c r="K216" s="8"/>
-      <c r="L216" s="8"/>
-      <c r="M216" s="8"/>
-    </row>
-    <row r="217" spans="2:13">
-      <c r="B217" s="50" t="s">
+      <c r="J226" s="8"/>
+      <c r="K226" s="8"/>
+      <c r="L226" s="8"/>
+      <c r="M226" s="8"/>
+    </row>
+    <row r="227" spans="2:13">
+      <c r="B227" s="50" t="s">
         <v>872</v>
       </c>
-      <c r="E217" s="50" t="s">
+      <c r="E227" s="50" t="s">
         <v>1266</v>
       </c>
-      <c r="G217" s="50" t="s">
+      <c r="G227" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="J217" s="8"/>
-      <c r="K217" s="8"/>
-      <c r="L217" s="8"/>
-      <c r="M217" s="8"/>
-    </row>
-    <row r="218" spans="2:13">
-      <c r="B218" s="36"/>
-      <c r="E218" s="8"/>
-      <c r="G218" s="50" t="s">
+      <c r="J227" s="8"/>
+      <c r="K227" s="8"/>
+      <c r="L227" s="8"/>
+      <c r="M227" s="8"/>
+    </row>
+    <row r="228" spans="2:13">
+      <c r="B228" s="36"/>
+      <c r="E228" s="8"/>
+      <c r="G228" s="50" t="s">
         <v>292</v>
       </c>
-      <c r="J218" s="8"/>
-      <c r="K218" s="8"/>
-      <c r="L218" s="8"/>
-      <c r="M218" s="8"/>
-    </row>
-    <row r="219" spans="2:13">
-      <c r="B219" s="50" t="s">
+      <c r="J228" s="8"/>
+      <c r="K228" s="8"/>
+      <c r="L228" s="8"/>
+      <c r="M228" s="8"/>
+    </row>
+    <row r="229" spans="2:13">
+      <c r="B229" s="50" t="s">
         <v>1269</v>
       </c>
-      <c r="E219" s="8"/>
-      <c r="G219" s="8"/>
-      <c r="J219" s="50" t="s">
+      <c r="E229" s="8"/>
+      <c r="G229" s="8"/>
+      <c r="J229" s="50" t="s">
         <v>1240</v>
       </c>
-      <c r="K219" s="50" t="s">
+      <c r="K229" s="50" t="s">
         <v>1241</v>
       </c>
-      <c r="L219" s="8"/>
-      <c r="M219" s="8"/>
-    </row>
-    <row r="220" spans="2:13">
-      <c r="B220" s="50" t="s">
+      <c r="L229" s="8"/>
+      <c r="M229" s="8"/>
+    </row>
+    <row r="230" spans="2:13">
+      <c r="B230" s="50" t="s">
         <v>1247</v>
       </c>
-      <c r="E220" t="s">
+      <c r="E230" t="s">
         <v>1254</v>
       </c>
-      <c r="G220" t="s">
+      <c r="G230" t="s">
         <v>1244</v>
       </c>
-      <c r="J220" t="s">
+      <c r="J230" t="s">
         <v>1245</v>
       </c>
-      <c r="K220" t="s">
+      <c r="K230" t="s">
         <v>1246</v>
       </c>
-      <c r="L220" s="8"/>
-      <c r="M220" s="8"/>
-    </row>
-    <row r="221" spans="2:13">
-      <c r="B221" s="50"/>
-      <c r="L221" s="8"/>
-      <c r="M221" s="8"/>
-    </row>
-    <row r="222" spans="2:13">
-      <c r="B222" s="50"/>
-      <c r="J222" s="50" t="s">
+      <c r="L230" s="8"/>
+      <c r="M230" s="8"/>
+    </row>
+    <row r="231" spans="2:13">
+      <c r="B231" s="50"/>
+      <c r="L231" s="8"/>
+      <c r="M231" s="8"/>
+    </row>
+    <row r="232" spans="2:13">
+      <c r="B232" s="50"/>
+      <c r="J232" s="50" t="s">
         <v>1240</v>
       </c>
-      <c r="K222" s="50" t="s">
+      <c r="K232" s="50" t="s">
         <v>1248</v>
       </c>
-      <c r="L222" s="50" t="s">
+      <c r="L232" s="50" t="s">
         <v>1241</v>
       </c>
-      <c r="M222" s="50" t="s">
+      <c r="M232" s="50" t="s">
         <v>1248</v>
       </c>
     </row>
-    <row r="223" spans="2:13">
-      <c r="B223" s="50" t="s">
+    <row r="233" spans="2:13">
+      <c r="B233" s="50" t="s">
         <v>1253</v>
       </c>
-      <c r="E223" t="s">
+      <c r="E233" t="s">
         <v>1249</v>
       </c>
-      <c r="G223" t="s">
+      <c r="G233" t="s">
         <v>1244</v>
       </c>
-      <c r="J223" t="s">
+      <c r="J233" t="s">
         <v>1245</v>
       </c>
-      <c r="K223" t="s">
+      <c r="K233" t="s">
         <v>1245</v>
       </c>
-      <c r="L223" t="s">
+      <c r="L233" t="s">
         <v>1246</v>
       </c>
-      <c r="M223" t="s">
+      <c r="M233" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="224" spans="2:13">
-      <c r="B224" s="50"/>
-    </row>
-    <row r="225" spans="2:15">
-      <c r="B225" s="50"/>
-      <c r="J225" s="50" t="s">
+    <row r="234" spans="2:13">
+      <c r="B234" s="50"/>
+    </row>
+    <row r="235" spans="2:13">
+      <c r="B235" s="50"/>
+      <c r="J235" s="50" t="s">
         <v>1240</v>
       </c>
-      <c r="K225" s="50" t="s">
+      <c r="K235" s="50" t="s">
         <v>1241</v>
       </c>
-      <c r="L225" s="50" t="s">
+      <c r="L235" s="50" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="226" spans="2:15">
-      <c r="B226" s="50" t="s">
+    <row r="236" spans="2:13">
+      <c r="B236" s="50" t="s">
         <v>1255</v>
       </c>
-      <c r="E226" t="s">
+      <c r="E236" t="s">
         <v>1252</v>
       </c>
-      <c r="G226" t="s">
+      <c r="G236" t="s">
         <v>1234</v>
       </c>
-      <c r="J226" t="s">
+      <c r="J236" t="s">
         <v>1237</v>
       </c>
-      <c r="K226" t="s">
+      <c r="K236" t="s">
         <v>1238</v>
       </c>
-      <c r="L226" t="s">
+      <c r="L236" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="227" spans="2:15">
-      <c r="B227" s="50"/>
-    </row>
-    <row r="228" spans="2:15">
-      <c r="B228" s="50" t="s">
+    <row r="237" spans="2:13">
+      <c r="B237" s="50"/>
+    </row>
+    <row r="238" spans="2:13">
+      <c r="B238" s="50" t="s">
         <v>1268</v>
       </c>
-      <c r="J228" s="50" t="s">
+      <c r="J238" s="50" t="s">
         <v>1240</v>
       </c>
-      <c r="K228" s="50" t="s">
+      <c r="K238" s="50" t="s">
         <v>1241</v>
       </c>
     </row>
-    <row r="229" spans="2:15">
-      <c r="B229" s="50" t="s">
+    <row r="239" spans="2:13">
+      <c r="B239" s="50" t="s">
         <v>1256</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E239" t="s">
         <v>1251</v>
       </c>
-      <c r="G229" t="s">
+      <c r="G239" t="s">
         <v>1235</v>
       </c>
-      <c r="J229" t="s">
+      <c r="J239" t="s">
         <v>1238</v>
       </c>
-      <c r="K229" t="s">
+      <c r="K239" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="230" spans="2:15">
-      <c r="B230" s="50"/>
-    </row>
-    <row r="231" spans="2:15">
-      <c r="B231" s="50" t="s">
-        <v>1267</v>
-      </c>
-      <c r="J231" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K231" s="50" t="s">
-        <v>1241</v>
-      </c>
-      <c r="L231" s="50" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="232" spans="2:15">
-      <c r="B232" s="50" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E232" t="s">
-        <v>1250</v>
-      </c>
-      <c r="G232" t="s">
-        <v>1257</v>
-      </c>
-      <c r="J232" t="s">
-        <v>1258</v>
-      </c>
-      <c r="K232" t="s">
-        <v>1259</v>
-      </c>
-      <c r="L232">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="2:15">
-      <c r="B233" s="50"/>
-    </row>
-    <row r="234" spans="2:15">
-      <c r="B234" s="50"/>
-      <c r="J234" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K234" s="50" t="s">
-        <v>1248</v>
-      </c>
-      <c r="L234" s="50" t="s">
-        <v>1241</v>
-      </c>
-      <c r="M234" s="50" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="235" spans="2:15">
-      <c r="B235" s="32" t="s">
-        <v>1263</v>
-      </c>
-      <c r="E235" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G235" t="s">
-        <v>1262</v>
-      </c>
-      <c r="J235" t="s">
-        <v>1258</v>
-      </c>
-      <c r="K235" t="s">
-        <v>1264</v>
-      </c>
-      <c r="L235" t="s">
-        <v>1259</v>
-      </c>
-      <c r="M235" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="236" spans="2:15">
-      <c r="B236" s="50"/>
-    </row>
-    <row r="237" spans="2:15">
-      <c r="B237" s="50" t="s">
-        <v>1275</v>
-      </c>
-      <c r="J237" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K237" s="50" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="238" spans="2:15">
-      <c r="B238" s="50" t="s">
-        <v>1272</v>
-      </c>
-      <c r="E238" t="s">
-        <v>1270</v>
-      </c>
-      <c r="G238" t="s">
-        <v>1271</v>
-      </c>
-      <c r="J238" t="s">
-        <v>1273</v>
-      </c>
-      <c r="K238" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="239" spans="2:15">
-      <c r="B239" s="50"/>
-    </row>
-    <row r="240" spans="2:15">
+    <row r="240" spans="2:13">
       <c r="B240" s="50"/>
-      <c r="J240" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K240" s="50" t="s">
-        <v>1248</v>
-      </c>
-      <c r="L240" s="50" t="s">
-        <v>1241</v>
-      </c>
-      <c r="M240" s="50" t="s">
-        <v>1248</v>
-      </c>
-      <c r="N240" s="50" t="s">
-        <v>1242</v>
-      </c>
-      <c r="O240" s="50" t="s">
-        <v>1248</v>
-      </c>
     </row>
     <row r="241" spans="2:15">
       <c r="B241" s="50" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J241" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K241" s="50" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L241" s="50" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="242" spans="2:15">
+      <c r="B242" s="50" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E242" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G242" t="s">
+        <v>1257</v>
+      </c>
+      <c r="J242" t="s">
+        <v>1258</v>
+      </c>
+      <c r="K242" t="s">
+        <v>1259</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="2:15">
+      <c r="B243" s="50"/>
+    </row>
+    <row r="244" spans="2:15">
+      <c r="B244" s="50"/>
+      <c r="J244" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K244" s="50" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L244" s="50" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M244" s="50" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="245" spans="2:15">
+      <c r="B245" s="32" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E245" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G245" t="s">
+        <v>1262</v>
+      </c>
+      <c r="J245" t="s">
+        <v>1258</v>
+      </c>
+      <c r="K245" t="s">
+        <v>1264</v>
+      </c>
+      <c r="L245" t="s">
+        <v>1259</v>
+      </c>
+      <c r="M245" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="246" spans="2:15">
+      <c r="B246" s="50"/>
+    </row>
+    <row r="247" spans="2:15">
+      <c r="B247" s="50" t="s">
+        <v>1275</v>
+      </c>
+      <c r="J247" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K247" s="50" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="248" spans="2:15">
+      <c r="B248" s="50" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E248" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G248" t="s">
+        <v>1271</v>
+      </c>
+      <c r="J248" t="s">
+        <v>1273</v>
+      </c>
+      <c r="K248" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="249" spans="2:15">
+      <c r="B249" s="50"/>
+    </row>
+    <row r="250" spans="2:15">
+      <c r="B250" s="50"/>
+      <c r="J250" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K250" s="50" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L250" s="50" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M250" s="50" t="s">
+        <v>1248</v>
+      </c>
+      <c r="N250" s="50" t="s">
+        <v>1242</v>
+      </c>
+      <c r="O250" s="50" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="251" spans="2:15">
+      <c r="B251" s="50" t="s">
         <v>1278</v>
       </c>
-      <c r="E241" t="s">
+      <c r="E251" t="s">
         <v>1276</v>
       </c>
-      <c r="G241" t="s">
+      <c r="G251" t="s">
         <v>1277</v>
       </c>
-      <c r="J241" t="s">
+      <c r="J251" t="s">
         <v>1279</v>
       </c>
-      <c r="K241">
+      <c r="K251">
         <v>1</v>
       </c>
-      <c r="L241" t="s">
+      <c r="L251" t="s">
         <v>1280</v>
       </c>
-      <c r="M241">
+      <c r="M251">
         <v>22</v>
       </c>
-      <c r="N241" t="s">
+      <c r="N251" t="s">
         <v>1281</v>
       </c>
-      <c r="O241">
+      <c r="O251">
         <v>333</v>
-      </c>
-    </row>
-    <row r="242" spans="2:15">
-      <c r="B242" s="36"/>
-    </row>
-    <row r="243" spans="2:15">
-      <c r="B243" s="50" t="s">
-        <v>1286</v>
-      </c>
-      <c r="J243" s="50" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K243" s="50" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="244" spans="2:15">
-      <c r="B244" s="50" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E244" t="s">
-        <v>1282</v>
-      </c>
-      <c r="G244" t="s">
-        <v>1283</v>
-      </c>
-      <c r="J244" t="s">
-        <v>1285</v>
-      </c>
-      <c r="K244" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="245" spans="2:15">
-      <c r="B245" s="36"/>
-    </row>
-    <row r="246" spans="2:15">
-      <c r="B246" s="36"/>
-    </row>
-    <row r="247" spans="2:15">
-      <c r="B247" s="36" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="248" spans="2:15">
-      <c r="B248" s="36"/>
-      <c r="C248" t="s">
-        <v>49</v>
-      </c>
-      <c r="H248" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="249" spans="2:15">
-      <c r="B249" s="36"/>
-      <c r="C249" t="s">
-        <v>278</v>
-      </c>
-      <c r="H249" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="250" spans="2:15">
-      <c r="B250" s="36"/>
-      <c r="C250" t="s">
-        <v>600</v>
-      </c>
-      <c r="H250" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="251" spans="2:15">
-      <c r="B251" s="36"/>
-      <c r="C251" t="s">
-        <v>1289</v>
-      </c>
-      <c r="H251" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="252" spans="2:15">
       <c r="B252" s="36"/>
-      <c r="C252" t="s">
-        <v>1291</v>
-      </c>
-      <c r="H252" t="s">
-        <v>1290</v>
-      </c>
     </row>
     <row r="253" spans="2:15">
-      <c r="B253" s="36"/>
-      <c r="C253" t="s">
-        <v>1288</v>
+      <c r="B253" s="50" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J253" s="50" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K253" s="50" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="254" spans="2:15">
-      <c r="B254" s="36"/>
+      <c r="B254" s="50" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E254" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G254" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J254" t="s">
+        <v>1285</v>
+      </c>
+      <c r="K254" t="s">
+        <v>1285</v>
+      </c>
     </row>
     <row r="255" spans="2:15">
       <c r="B255" s="36"/>
-      <c r="C255" t="s">
-        <v>1289</v>
-      </c>
     </row>
     <row r="256" spans="2:15">
       <c r="B256" s="36"/>
-      <c r="C256" s="8" t="s">
+    </row>
+    <row r="257" spans="2:8">
+      <c r="B257" s="36" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="258" spans="2:8">
+      <c r="B258" s="36"/>
+      <c r="C258" t="s">
+        <v>49</v>
+      </c>
+      <c r="H258" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="259" spans="2:8">
+      <c r="B259" s="36"/>
+      <c r="C259" t="s">
+        <v>278</v>
+      </c>
+      <c r="H259" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="260" spans="2:8">
+      <c r="B260" s="36"/>
+      <c r="C260" t="s">
+        <v>600</v>
+      </c>
+      <c r="H260" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="261" spans="2:8">
+      <c r="B261" s="36"/>
+      <c r="C261" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H261" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="262" spans="2:8">
+      <c r="B262" s="36"/>
+      <c r="C262" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H262" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="263" spans="2:8">
+      <c r="B263" s="36"/>
+      <c r="C263" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="264" spans="2:8">
+      <c r="B264" s="36"/>
+    </row>
+    <row r="265" spans="2:8">
+      <c r="B265" s="36"/>
+      <c r="C265" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="266" spans="2:8">
+      <c r="B266" s="36"/>
+      <c r="C266" s="8" t="s">
         <v>1297</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
-      <c r="B257" s="36"/>
-      <c r="D257" t="s">
+    <row r="267" spans="2:8">
+      <c r="B267" s="36"/>
+      <c r="D267" t="s">
         <v>1296</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
-      <c r="B258" s="36"/>
-    </row>
-    <row r="259" spans="1:6">
-      <c r="B259" s="36"/>
-      <c r="D259" t="s">
+    <row r="268" spans="2:8">
+      <c r="B268" s="36"/>
+    </row>
+    <row r="269" spans="2:8">
+      <c r="B269" s="36"/>
+      <c r="D269" t="s">
         <v>1298</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
-      <c r="B260" s="36"/>
-      <c r="D260" t="s">
+    <row r="270" spans="2:8">
+      <c r="B270" s="36"/>
+      <c r="D270" t="s">
         <v>1299</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
-      <c r="B261" s="36"/>
-      <c r="D261" t="s">
+    <row r="271" spans="2:8">
+      <c r="B271" s="36"/>
+      <c r="D271" t="s">
         <v>1300</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
-      <c r="B262" s="36"/>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="A264" s="8" t="s">
+    <row r="272" spans="2:8">
+      <c r="B272" s="36"/>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="8" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
-      <c r="B266" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
-      <c r="B268" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
-      <c r="B269" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
-      <c r="B271" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
-      <c r="B272" t="s">
-        <v>790</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8">
-      <c r="A274" s="8" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:6">
       <c r="B276" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
-      <c r="B277" t="s">
+    <row r="278" spans="1:6">
+      <c r="B278" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="B279" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="B281" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="B282" t="s">
+        <v>790</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="8" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="B286" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="B287" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
-      <c r="B279" t="s">
+    <row r="289" spans="1:8">
+      <c r="B289" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
-      <c r="B280" t="s">
+    <row r="290" spans="1:8">
+      <c r="B290" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
-      <c r="C281" s="5" t="s">
+    <row r="291" spans="1:8">
+      <c r="C291" s="5" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
-      <c r="A283" s="8" t="s">
+    <row r="293" spans="1:8">
+      <c r="A293" s="8" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
-      <c r="B285" t="s">
+    <row r="295" spans="1:8">
+      <c r="B295" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
-      <c r="B287" t="s">
+    <row r="297" spans="1:8">
+      <c r="B297" t="s">
         <v>798</v>
       </c>
-      <c r="H287" t="s">
+      <c r="H297" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
-      <c r="B288" t="s">
+    <row r="298" spans="1:8">
+      <c r="B298" t="s">
         <v>799</v>
       </c>
-      <c r="H288" t="s">
+      <c r="H298" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
-      <c r="B289" t="s">
+    <row r="299" spans="1:8">
+      <c r="B299" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
-      <c r="C290" s="5" t="s">
+    <row r="300" spans="1:8">
+      <c r="C300" s="5" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
-      <c r="A292" s="8" t="s">
+    <row r="302" spans="1:8">
+      <c r="A302" s="8" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
-      <c r="B294" t="s">
+    <row r="304" spans="1:8">
+      <c r="B304" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9">
-      <c r="B296" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9">
-      <c r="B297" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9">
-      <c r="B298" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9">
-      <c r="C299" s="5" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9">
-      <c r="A302" s="8" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9">
-      <c r="B304" t="s">
-        <v>810</v>
-      </c>
-      <c r="I304" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="306" spans="1:10">
       <c r="B306" t="s">
-        <v>1</v>
-      </c>
-      <c r="I306" t="s">
-        <v>1</v>
+        <v>803</v>
       </c>
     </row>
     <row r="307" spans="1:10">
       <c r="B307" t="s">
-        <v>811</v>
-      </c>
-      <c r="I307" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
     </row>
     <row r="308" spans="1:10">
       <c r="B308" t="s">
-        <v>815</v>
-      </c>
-      <c r="I308" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
     </row>
     <row r="309" spans="1:10">
-      <c r="B309" t="s">
-        <v>813</v>
-      </c>
-      <c r="I309" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="310" spans="1:10">
-      <c r="C310" s="5" t="b">
+      <c r="C309" s="5" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10">
+      <c r="A312" s="8" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10">
+      <c r="B314" t="s">
+        <v>810</v>
+      </c>
+      <c r="I314" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10">
+      <c r="B316" t="s">
         <v>1</v>
       </c>
-      <c r="J310" s="5" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="313" spans="1:10">
-      <c r="A313" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="315" spans="1:10">
-      <c r="B315" t="s">
+      <c r="I316" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:10">
       <c r="B317" t="s">
-        <v>818</v>
+        <v>811</v>
+      </c>
+      <c r="I317" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="318" spans="1:10">
       <c r="B318" t="s">
-        <v>819</v>
+        <v>815</v>
+      </c>
+      <c r="I318" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="319" spans="1:10">
       <c r="B319" t="s">
-        <v>820</v>
+        <v>813</v>
+      </c>
+      <c r="I319" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="320" spans="1:10">
-      <c r="C320" s="5" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3">
-      <c r="A322" s="8" t="s">
-        <v>822</v>
+      <c r="C320" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J320" s="5" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="323" spans="1:3">
-      <c r="B323" t="s">
-        <v>823</v>
+      <c r="A323" s="8" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -27265,152 +27589,187 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
-      <c r="B326" t="s">
-        <v>824</v>
-      </c>
-    </row>
     <row r="327" spans="1:3">
       <c r="B327" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="B328" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
     </row>
     <row r="329" spans="1:3">
-      <c r="C329" s="5" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3">
-      <c r="A331" s="8" t="s">
-        <v>828</v>
+      <c r="B329" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="C330" s="5" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" s="8" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="B333" t="s">
-        <v>1</v>
+        <v>823</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="B335" t="s">
-        <v>831</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="B336" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="B337" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="B338" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="C339" s="5" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" s="8" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="B343" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="B345" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="B346" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
-      <c r="B337" t="s">
+    <row r="347" spans="1:3">
+      <c r="B347" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
-      <c r="C338" s="5" t="s">
+    <row r="348" spans="1:3">
+      <c r="C348" s="5" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
-      <c r="A341" s="8" t="s">
+    <row r="351" spans="1:3">
+      <c r="A351" s="8" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
-      <c r="B342" t="s">
+    <row r="352" spans="1:3">
+      <c r="B352" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
-      <c r="B344" t="s">
+    <row r="354" spans="1:5">
+      <c r="B354" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
-      <c r="B345" t="s">
+    <row r="355" spans="1:5">
+      <c r="B355" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
-      <c r="B347" t="s">
+    <row r="357" spans="1:5">
+      <c r="B357" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
-      <c r="B349" t="s">
+    <row r="359" spans="1:5">
+      <c r="B359" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
-      <c r="B350" t="s">
+    <row r="360" spans="1:5">
+      <c r="B360" t="s">
         <v>80</v>
       </c>
-      <c r="E350" s="5" t="s">
+      <c r="E360" s="5" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
-      <c r="A353" s="8" t="s">
+    <row r="363" spans="1:5">
+      <c r="A363" s="8" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
-      <c r="B355" t="s">
+    <row r="365" spans="1:5">
+      <c r="B365" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
-      <c r="B357" t="s">
+    <row r="367" spans="1:5">
+      <c r="B367" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
-      <c r="B358" t="s">
+    <row r="368" spans="1:5">
+      <c r="B368" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
-      <c r="B359" t="s">
+    <row r="369" spans="2:7">
+      <c r="B369" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
-      <c r="B360" t="s">
+    <row r="370" spans="2:7">
+      <c r="B370" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
-      <c r="B362" t="s">
+    <row r="372" spans="2:7">
+      <c r="B372" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
-      <c r="B364" t="s">
+    <row r="374" spans="2:7">
+      <c r="B374" t="s">
         <v>904</v>
       </c>
-      <c r="G364" s="5" t="s">
+      <c r="G374" s="5" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
-      <c r="B365" t="s">
+    <row r="375" spans="2:7">
+      <c r="B375" t="s">
         <v>905</v>
       </c>
-      <c r="G365" s="5" t="s">
+      <c r="G375" s="5" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
-      <c r="B366" t="s">
+    <row r="376" spans="2:7">
+      <c r="B376" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
-      <c r="B367" t="s">
+    <row r="377" spans="2:7">
+      <c r="B377" t="s">
         <v>907</v>
       </c>
     </row>
@@ -32613,22 +32972,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="156" priority="4">
+    <cfRule type="expression" dxfId="60" priority="4">
       <formula>$B$37&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="155" priority="3">
+    <cfRule type="expression" dxfId="59" priority="3">
       <formula>$B$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="154" priority="2">
+    <cfRule type="expression" dxfId="58" priority="2">
       <formula>$B$17=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="153" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>$B$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33705,17 +34064,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="104" priority="10">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>$B$82&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="103" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$B$80&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="102" priority="12">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>$B$49=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35041,17 +35400,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="101" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>$B$82&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="100" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>$B$80&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="99" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$B$49=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35839,17 +36198,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35862,7 +36221,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M376"/>
+  <dimension ref="A1:M398"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="10.44140625" customWidth="1"/>
@@ -37350,7 +37709,7 @@
       <c r="H256" s="18"/>
       <c r="I256" s="57"/>
     </row>
-    <row r="257" spans="1:12">
+    <row r="257" spans="2:12">
       <c r="B257" s="8"/>
       <c r="C257" s="56" t="s">
         <v>1668</v>
@@ -37363,7 +37722,7 @@
       <c r="H257" s="18"/>
       <c r="I257" s="57"/>
     </row>
-    <row r="258" spans="1:12">
+    <row r="258" spans="2:12">
       <c r="B258" s="8"/>
       <c r="C258" s="54" t="s">
         <v>1663</v>
@@ -37379,7 +37738,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="259" spans="1:12">
+    <row r="259" spans="2:12">
       <c r="D259" s="5" t="s">
         <v>1664</v>
       </c>
@@ -37395,7 +37754,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="260" spans="1:12">
+    <row r="260" spans="2:12">
       <c r="D260" t="s">
         <v>1671</v>
       </c>
@@ -37403,806 +37762,935 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="262" spans="1:12">
-      <c r="A262" s="8" t="s">
+    <row r="262" spans="2:12">
+      <c r="B262" s="115" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="263" spans="2:12">
+      <c r="B263" s="115"/>
+      <c r="C263" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="264" spans="2:12">
+      <c r="B264" s="115"/>
+      <c r="D264" s="116" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E264" s="52"/>
+      <c r="F264" s="52"/>
+      <c r="G264" s="53"/>
+    </row>
+    <row r="265" spans="2:12">
+      <c r="B265" s="115"/>
+      <c r="D265" s="56" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E265" s="18"/>
+      <c r="F265" s="18"/>
+      <c r="G265" s="57"/>
+    </row>
+    <row r="266" spans="2:12">
+      <c r="B266" s="115"/>
+      <c r="D266" s="117" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E266" s="18"/>
+      <c r="F266" s="18"/>
+      <c r="G266" s="57"/>
+    </row>
+    <row r="267" spans="2:12">
+      <c r="D267" s="54" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E267" s="7"/>
+      <c r="F267" s="7"/>
+      <c r="G267" s="55"/>
+      <c r="I267" s="5" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="269" spans="2:12">
+      <c r="C269" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="270" spans="2:12">
+      <c r="D270" s="116" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E270" s="52"/>
+      <c r="F270" s="52"/>
+      <c r="G270" s="53"/>
+    </row>
+    <row r="271" spans="2:12">
+      <c r="D271" s="56" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E271" s="18"/>
+      <c r="F271" s="18"/>
+      <c r="G271" s="57"/>
+    </row>
+    <row r="272" spans="2:12">
+      <c r="D272" s="117" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E272" s="18"/>
+      <c r="F272" s="18"/>
+      <c r="G272" s="57"/>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="D273" s="54" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E273" s="7"/>
+      <c r="F273" s="7"/>
+      <c r="G273" s="55"/>
+      <c r="I273" s="5" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="C275" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="D276" s="116" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E276" s="52"/>
+      <c r="F276" s="52"/>
+      <c r="G276" s="53"/>
+    </row>
+    <row r="277" spans="1:9">
+      <c r="D277" s="56" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E277" s="18"/>
+      <c r="F277" s="18"/>
+      <c r="G277" s="57"/>
+    </row>
+    <row r="278" spans="1:9">
+      <c r="D278" s="117" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E278" s="18"/>
+      <c r="F278" s="18"/>
+      <c r="G278" s="57"/>
+    </row>
+    <row r="279" spans="1:9">
+      <c r="D279" s="54" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E279" s="7"/>
+      <c r="F279" s="7"/>
+      <c r="G279" s="55"/>
+      <c r="I279" s="5" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9">
+      <c r="A284" s="8" t="s">
         <v>1464</v>
       </c>
     </row>
-    <row r="263" spans="1:12">
-      <c r="B263" t="s">
+    <row r="285" spans="1:9">
+      <c r="B285" t="s">
         <v>1467</v>
       </c>
     </row>
-    <row r="264" spans="1:12">
-      <c r="B264" t="s">
+    <row r="286" spans="1:9">
+      <c r="B286" t="s">
         <v>1465</v>
       </c>
     </row>
-    <row r="265" spans="1:12">
-      <c r="B265" t="s">
+    <row r="287" spans="1:9">
+      <c r="B287" t="s">
         <v>1466</v>
       </c>
     </row>
-    <row r="267" spans="1:12">
-      <c r="B267" s="8" t="s">
+    <row r="289" spans="2:7">
+      <c r="B289" s="8" t="s">
         <v>1316</v>
       </c>
     </row>
-    <row r="268" spans="1:12">
-      <c r="B268" s="58" t="s">
+    <row r="290" spans="2:7">
+      <c r="B290" s="58" t="s">
         <v>1355</v>
       </c>
-      <c r="C268" s="52"/>
-      <c r="D268" s="52"/>
-      <c r="E268" s="53"/>
-    </row>
-    <row r="269" spans="1:12">
-      <c r="B269" s="66" t="s">
+      <c r="C290" s="52"/>
+      <c r="D290" s="52"/>
+      <c r="E290" s="53"/>
+    </row>
+    <row r="291" spans="2:7">
+      <c r="B291" s="66" t="s">
         <v>1471</v>
       </c>
-      <c r="C269" s="7"/>
-      <c r="D269" s="7"/>
-      <c r="E269" s="55"/>
-    </row>
-    <row r="271" spans="1:12">
-      <c r="B271" s="60" t="s">
+      <c r="C291" s="7"/>
+      <c r="D291" s="7"/>
+      <c r="E291" s="55"/>
+    </row>
+    <row r="293" spans="2:7">
+      <c r="B293" s="60" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="273" spans="2:7">
-      <c r="B273" s="4" t="s">
+    <row r="295" spans="2:7">
+      <c r="B295" s="4" t="s">
         <v>1357</v>
       </c>
     </row>
-    <row r="274" spans="2:7">
-      <c r="B274" s="58" t="s">
+    <row r="296" spans="2:7">
+      <c r="B296" s="58" t="s">
         <v>1470</v>
       </c>
-      <c r="C274" s="52"/>
-      <c r="D274" s="52"/>
-      <c r="E274" s="53"/>
-    </row>
-    <row r="275" spans="2:7">
-      <c r="B275" s="56"/>
-      <c r="C275" s="18"/>
-      <c r="D275" s="18"/>
-      <c r="E275" s="57"/>
-    </row>
-    <row r="276" spans="2:7">
-      <c r="B276" s="56" t="s">
+      <c r="C296" s="52"/>
+      <c r="D296" s="52"/>
+      <c r="E296" s="53"/>
+    </row>
+    <row r="297" spans="2:7">
+      <c r="B297" s="56"/>
+      <c r="C297" s="18"/>
+      <c r="D297" s="18"/>
+      <c r="E297" s="57"/>
+    </row>
+    <row r="298" spans="2:7">
+      <c r="B298" s="56" t="s">
         <v>1468</v>
       </c>
-      <c r="C276" s="18"/>
-      <c r="D276" s="18"/>
-      <c r="E276" s="57"/>
-    </row>
-    <row r="277" spans="2:7">
-      <c r="B277" s="56" t="s">
+      <c r="C298" s="18"/>
+      <c r="D298" s="18"/>
+      <c r="E298" s="57"/>
+    </row>
+    <row r="299" spans="2:7">
+      <c r="B299" s="56" t="s">
         <v>1415</v>
       </c>
-      <c r="C277" s="18"/>
-      <c r="D277" s="18"/>
-      <c r="E277" s="57"/>
-    </row>
-    <row r="278" spans="2:7">
-      <c r="B278" s="56"/>
-      <c r="C278" s="18"/>
-      <c r="D278" s="18"/>
-      <c r="E278" s="57"/>
-    </row>
-    <row r="279" spans="2:7">
-      <c r="B279" s="61" t="s">
-        <v>1473</v>
-      </c>
-      <c r="C279" s="18"/>
-      <c r="D279" s="18"/>
-      <c r="E279" s="57"/>
-    </row>
-    <row r="280" spans="2:7">
-      <c r="B280" s="56"/>
-      <c r="C280" s="18"/>
-      <c r="D280" s="18"/>
-      <c r="E280" s="57"/>
-    </row>
-    <row r="281" spans="2:7">
-      <c r="B281" s="56" t="s">
-        <v>1474</v>
-      </c>
-      <c r="C281" s="18"/>
-      <c r="D281" s="18"/>
-      <c r="E281" s="57"/>
-      <c r="G281" s="5" t="s">
-        <v>1476</v>
-      </c>
-    </row>
-    <row r="282" spans="2:7">
-      <c r="B282" s="56" t="s">
-        <v>1475</v>
-      </c>
-      <c r="C282" s="18"/>
-      <c r="D282" s="18"/>
-      <c r="E282" s="57"/>
-      <c r="G282" s="5" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="283" spans="2:7">
-      <c r="B283" s="56"/>
-      <c r="C283" s="18"/>
-      <c r="D283" s="18"/>
-      <c r="E283" s="57"/>
-    </row>
-    <row r="284" spans="2:7">
-      <c r="B284" s="56" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C284" s="18"/>
-      <c r="D284" s="18"/>
-      <c r="E284" s="57"/>
-    </row>
-    <row r="285" spans="2:7">
-      <c r="B285" s="56" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C285" s="18"/>
-      <c r="D285" s="18"/>
-      <c r="E285" s="57"/>
-      <c r="G285" t="s">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="286" spans="2:7">
-      <c r="B286" s="54" t="s">
-        <v>1481</v>
-      </c>
-      <c r="C286" s="7"/>
-      <c r="D286" s="7"/>
-      <c r="E286" s="55"/>
-      <c r="G286">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="287" spans="2:7">
-      <c r="G287" t="s">
-        <v>1478</v>
-      </c>
-    </row>
-    <row r="288" spans="2:7">
-      <c r="G288">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="291" spans="2:9">
-      <c r="B291" t="s">
-        <v>1482</v>
-      </c>
-    </row>
-    <row r="292" spans="2:9">
-      <c r="C292" s="59" t="s">
-        <v>1171</v>
-      </c>
-      <c r="D292" s="53"/>
-      <c r="E292" s="59" t="s">
-        <v>1483</v>
-      </c>
-      <c r="F292" s="53"/>
-      <c r="G292" s="59" t="s">
-        <v>1484</v>
-      </c>
-      <c r="H292" s="52"/>
-      <c r="I292" s="53"/>
-    </row>
-    <row r="293" spans="2:9">
-      <c r="C293" s="56" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D293" s="57"/>
-      <c r="E293" s="56" t="s">
-        <v>1485</v>
-      </c>
-      <c r="F293" s="57"/>
-      <c r="G293" s="56" t="s">
-        <v>1486</v>
-      </c>
-      <c r="H293" s="18"/>
-      <c r="I293" s="57"/>
-    </row>
-    <row r="294" spans="2:9">
-      <c r="C294" s="54" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D294" s="55"/>
-      <c r="E294" s="54" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F294" s="55"/>
-      <c r="G294" s="54" t="s">
-        <v>1488</v>
-      </c>
-      <c r="H294" s="7"/>
-      <c r="I294" s="55"/>
-    </row>
-    <row r="296" spans="2:9">
-      <c r="B296" s="8" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="297" spans="2:9">
-      <c r="C297" t="s">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="298" spans="2:9">
-      <c r="C298" s="58" t="s">
-        <v>1491</v>
-      </c>
-      <c r="D298" s="52"/>
-      <c r="E298" s="53"/>
-    </row>
-    <row r="299" spans="2:9">
-      <c r="C299" s="61" t="s">
-        <v>1492</v>
-      </c>
+      <c r="C299" s="18"/>
       <c r="D299" s="18"/>
       <c r="E299" s="57"/>
     </row>
-    <row r="300" spans="2:9">
-      <c r="C300" s="61" t="s">
-        <v>1493</v>
-      </c>
+    <row r="300" spans="2:7">
+      <c r="B300" s="56"/>
+      <c r="C300" s="18"/>
       <c r="D300" s="18"/>
       <c r="E300" s="57"/>
     </row>
-    <row r="301" spans="2:9">
-      <c r="C301" s="66" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D301" s="7"/>
-      <c r="E301" s="55"/>
-    </row>
-    <row r="303" spans="2:9">
-      <c r="B303" s="8" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="304" spans="2:9">
-      <c r="C304" s="67" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="305" spans="2:5">
-      <c r="C305" s="67" t="s">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="306" spans="2:5">
-      <c r="C306" s="67" t="s">
-        <v>1498</v>
-      </c>
-    </row>
-    <row r="309" spans="2:5">
-      <c r="B309" s="8" t="s">
-        <v>1579</v>
-      </c>
-    </row>
-    <row r="310" spans="2:5">
-      <c r="B310" t="s">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="312" spans="2:5">
-      <c r="B312" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="313" spans="2:5">
-      <c r="C313" t="s">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="314" spans="2:5">
-      <c r="C314" t="s">
-        <v>1502</v>
-      </c>
-    </row>
-    <row r="315" spans="2:5">
-      <c r="C315" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="317" spans="2:5">
-      <c r="B317" s="8" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="318" spans="2:5">
-      <c r="B318" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="C318" s="52"/>
-      <c r="D318" s="52"/>
-      <c r="E318" s="53"/>
-    </row>
-    <row r="319" spans="2:5">
-      <c r="B319" s="56"/>
-      <c r="C319" s="18"/>
-      <c r="D319" s="18"/>
-      <c r="E319" s="57"/>
-    </row>
-    <row r="320" spans="2:5">
-      <c r="B320" s="56" t="s">
-        <v>1468</v>
-      </c>
-      <c r="C320" s="18"/>
-      <c r="D320" s="18"/>
-      <c r="E320" s="57"/>
-    </row>
-    <row r="321" spans="2:9">
-      <c r="B321" s="56" t="s">
-        <v>1504</v>
-      </c>
-      <c r="C321" s="18"/>
+    <row r="301" spans="2:7">
+      <c r="B301" s="61" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C301" s="18"/>
+      <c r="D301" s="18"/>
+      <c r="E301" s="57"/>
+    </row>
+    <row r="302" spans="2:7">
+      <c r="B302" s="56"/>
+      <c r="C302" s="18"/>
+      <c r="D302" s="18"/>
+      <c r="E302" s="57"/>
+    </row>
+    <row r="303" spans="2:7">
+      <c r="B303" s="56" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C303" s="18"/>
+      <c r="D303" s="18"/>
+      <c r="E303" s="57"/>
+      <c r="G303" s="5" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="304" spans="2:7">
+      <c r="B304" s="56" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C304" s="18"/>
+      <c r="D304" s="18"/>
+      <c r="E304" s="57"/>
+      <c r="G304" s="5" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="305" spans="2:9">
+      <c r="B305" s="56"/>
+      <c r="C305" s="18"/>
+      <c r="D305" s="18"/>
+      <c r="E305" s="57"/>
+    </row>
+    <row r="306" spans="2:9">
+      <c r="B306" s="56" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C306" s="18"/>
+      <c r="D306" s="18"/>
+      <c r="E306" s="57"/>
+    </row>
+    <row r="307" spans="2:9">
+      <c r="B307" s="56" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C307" s="18"/>
+      <c r="D307" s="18"/>
+      <c r="E307" s="57"/>
+      <c r="G307" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="308" spans="2:9">
+      <c r="B308" s="54" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C308" s="7"/>
+      <c r="D308" s="7"/>
+      <c r="E308" s="55"/>
+      <c r="G308">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="309" spans="2:9">
+      <c r="G309" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="310" spans="2:9">
+      <c r="G310">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="313" spans="2:9">
+      <c r="B313" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="314" spans="2:9">
+      <c r="C314" s="59" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D314" s="53"/>
+      <c r="E314" s="59" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F314" s="53"/>
+      <c r="G314" s="59" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H314" s="52"/>
+      <c r="I314" s="53"/>
+    </row>
+    <row r="315" spans="2:9">
+      <c r="C315" s="56" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D315" s="57"/>
+      <c r="E315" s="56" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F315" s="57"/>
+      <c r="G315" s="56" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H315" s="18"/>
+      <c r="I315" s="57"/>
+    </row>
+    <row r="316" spans="2:9">
+      <c r="C316" s="54" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D316" s="55"/>
+      <c r="E316" s="54" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F316" s="55"/>
+      <c r="G316" s="54" t="s">
+        <v>1488</v>
+      </c>
+      <c r="H316" s="7"/>
+      <c r="I316" s="55"/>
+    </row>
+    <row r="318" spans="2:9">
+      <c r="B318" s="8" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="319" spans="2:9">
+      <c r="C319" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="320" spans="2:9">
+      <c r="C320" s="58" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D320" s="52"/>
+      <c r="E320" s="53"/>
+    </row>
+    <row r="321" spans="2:5">
+      <c r="C321" s="61" t="s">
+        <v>1492</v>
+      </c>
       <c r="D321" s="18"/>
       <c r="E321" s="57"/>
     </row>
-    <row r="322" spans="2:9">
-      <c r="B322" s="56"/>
-      <c r="C322" s="18"/>
+    <row r="322" spans="2:5">
+      <c r="C322" s="61" t="s">
+        <v>1493</v>
+      </c>
       <c r="D322" s="18"/>
       <c r="E322" s="57"/>
     </row>
-    <row r="323" spans="2:9">
-      <c r="B323" s="56" t="s">
-        <v>1469</v>
-      </c>
-      <c r="C323" s="18"/>
-      <c r="D323" s="18"/>
-      <c r="E323" s="57"/>
-    </row>
-    <row r="324" spans="2:9">
-      <c r="B324" s="56"/>
-      <c r="C324" s="18"/>
-      <c r="D324" s="18"/>
-      <c r="E324" s="57"/>
-    </row>
-    <row r="325" spans="2:9">
-      <c r="B325" s="56" t="s">
-        <v>1474</v>
-      </c>
-      <c r="C325" s="18"/>
-      <c r="D325" s="18"/>
-      <c r="E325" s="57"/>
-      <c r="G325" s="5" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="326" spans="2:9">
-      <c r="B326" s="56" t="s">
-        <v>1475</v>
-      </c>
-      <c r="C326" s="18"/>
-      <c r="D326" s="18"/>
-      <c r="E326" s="57"/>
-      <c r="G326" s="5" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="327" spans="2:9">
-      <c r="B327" s="56"/>
-      <c r="C327" s="18"/>
-      <c r="D327" s="18"/>
-      <c r="E327" s="57"/>
-    </row>
-    <row r="328" spans="2:9">
-      <c r="B328" s="56" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C328" s="18"/>
-      <c r="D328" s="18"/>
-      <c r="E328" s="57"/>
-    </row>
-    <row r="329" spans="2:9">
-      <c r="B329" s="56" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C329" s="18"/>
-      <c r="D329" s="18"/>
-      <c r="E329" s="57"/>
-      <c r="G329" s="5" t="s">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="330" spans="2:9">
-      <c r="B330" s="56" t="s">
-        <v>1509</v>
-      </c>
-      <c r="C330" s="18"/>
-      <c r="D330" s="18"/>
-      <c r="E330" s="57"/>
-      <c r="G330" s="5">
-        <v>123</v>
-      </c>
-      <c r="I330" t="s">
-        <v>1506</v>
-      </c>
-    </row>
-    <row r="331" spans="2:9">
-      <c r="B331" s="54" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C331" s="7"/>
-      <c r="D331" s="7"/>
-      <c r="E331" s="55"/>
-      <c r="G331" s="5">
-        <v>123</v>
-      </c>
-      <c r="I331" t="s">
-        <v>1507</v>
-      </c>
-    </row>
-    <row r="332" spans="2:9">
-      <c r="G332" s="5" t="s">
-        <v>1478</v>
-      </c>
-    </row>
-    <row r="333" spans="2:9">
-      <c r="G333" s="5">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="334" spans="2:9">
-      <c r="B334" s="8" t="s">
-        <v>1510</v>
-      </c>
-      <c r="G334" s="5">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="336" spans="2:9">
-      <c r="B336" s="51" t="s">
+    <row r="323" spans="2:5">
+      <c r="C323" s="66" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D323" s="7"/>
+      <c r="E323" s="55"/>
+    </row>
+    <row r="325" spans="2:5">
+      <c r="B325" s="8" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="326" spans="2:5">
+      <c r="C326" s="67" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="327" spans="2:5">
+      <c r="C327" s="67" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="328" spans="2:5">
+      <c r="C328" s="67" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="331" spans="2:5">
+      <c r="B331" s="8" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="332" spans="2:5">
+      <c r="B332" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="334" spans="2:5">
+      <c r="B334" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="335" spans="2:5">
+      <c r="C335" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="336" spans="2:5">
+      <c r="C336" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="337" spans="2:9">
+      <c r="C337" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="339" spans="2:9">
+      <c r="B339" s="8" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="340" spans="2:9">
+      <c r="B340" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C336" s="52"/>
-      <c r="D336" s="52"/>
-      <c r="E336" s="53"/>
-    </row>
-    <row r="337" spans="2:11">
-      <c r="B337" s="56"/>
-      <c r="C337" s="18"/>
-      <c r="D337" s="18"/>
-      <c r="E337" s="57"/>
-    </row>
-    <row r="338" spans="2:11">
-      <c r="B338" s="56" t="s">
-        <v>1677</v>
-      </c>
-      <c r="C338" s="18"/>
-      <c r="D338" s="18"/>
-      <c r="E338" s="57"/>
-    </row>
-    <row r="339" spans="2:11">
-      <c r="B339" s="56" t="s">
-        <v>1675</v>
-      </c>
-      <c r="C339" s="18"/>
-      <c r="D339" s="18"/>
-      <c r="E339" s="57"/>
-    </row>
-    <row r="340" spans="2:11">
-      <c r="B340" s="56"/>
-      <c r="C340" s="18"/>
-      <c r="D340" s="18"/>
-      <c r="E340" s="57"/>
-    </row>
-    <row r="341" spans="2:11">
-      <c r="B341" s="56" t="s">
-        <v>1469</v>
-      </c>
+      <c r="C340" s="52"/>
+      <c r="D340" s="52"/>
+      <c r="E340" s="53"/>
+    </row>
+    <row r="341" spans="2:9">
+      <c r="B341" s="56"/>
       <c r="C341" s="18"/>
       <c r="D341" s="18"/>
       <c r="E341" s="57"/>
     </row>
-    <row r="342" spans="2:11">
-      <c r="B342" s="56"/>
+    <row r="342" spans="2:9">
+      <c r="B342" s="56" t="s">
+        <v>1468</v>
+      </c>
       <c r="C342" s="18"/>
       <c r="D342" s="18"/>
       <c r="E342" s="57"/>
     </row>
-    <row r="343" spans="2:11">
+    <row r="343" spans="2:9">
       <c r="B343" s="56" t="s">
-        <v>1474</v>
+        <v>1504</v>
       </c>
       <c r="C343" s="18"/>
       <c r="D343" s="18"/>
       <c r="E343" s="57"/>
-      <c r="G343" s="5" t="s">
-        <v>1476</v>
-      </c>
-    </row>
-    <row r="344" spans="2:11">
-      <c r="B344" s="56" t="s">
-        <v>1475</v>
-      </c>
+    </row>
+    <row r="344" spans="2:9">
+      <c r="B344" s="56"/>
       <c r="C344" s="18"/>
       <c r="D344" s="18"/>
       <c r="E344" s="57"/>
-      <c r="G344" s="5" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="345" spans="2:11">
-      <c r="B345" s="56"/>
+    </row>
+    <row r="345" spans="2:9">
+      <c r="B345" s="56" t="s">
+        <v>1469</v>
+      </c>
       <c r="C345" s="18"/>
       <c r="D345" s="18"/>
       <c r="E345" s="57"/>
     </row>
-    <row r="346" spans="2:11">
-      <c r="B346" s="56" t="s">
-        <v>1479</v>
-      </c>
+    <row r="346" spans="2:9">
+      <c r="B346" s="56"/>
       <c r="C346" s="18"/>
       <c r="D346" s="18"/>
       <c r="E346" s="57"/>
     </row>
-    <row r="347" spans="2:11">
+    <row r="347" spans="2:9">
       <c r="B347" s="56" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="C347" s="18"/>
       <c r="D347" s="18"/>
       <c r="E347" s="57"/>
-      <c r="G347" s="68" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I347" t="s">
-        <v>1518</v>
-      </c>
-      <c r="K347" s="68" t="s">
-        <v>1519</v>
-      </c>
-    </row>
-    <row r="348" spans="2:11">
+      <c r="G347" s="5" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="348" spans="2:9">
       <c r="B348" s="56" t="s">
-        <v>1509</v>
+        <v>1475</v>
       </c>
       <c r="C348" s="18"/>
       <c r="D348" s="18"/>
       <c r="E348" s="57"/>
-      <c r="G348" s="69" t="s">
-        <v>1513</v>
-      </c>
-      <c r="I348" t="s">
-        <v>1514</v>
-      </c>
-      <c r="K348" s="69" t="s">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="349" spans="2:11">
-      <c r="B349" s="56" t="s">
-        <v>1508</v>
-      </c>
+      <c r="G348" s="5" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="349" spans="2:9">
+      <c r="B349" s="56"/>
       <c r="C349" s="18"/>
       <c r="D349" s="18"/>
       <c r="E349" s="57"/>
-      <c r="G349" s="69" t="s">
-        <v>1515</v>
-      </c>
-      <c r="I349" t="s">
-        <v>1516</v>
-      </c>
-      <c r="K349" s="69" t="s">
-        <v>1515</v>
-      </c>
-    </row>
-    <row r="350" spans="2:11">
+    </row>
+    <row r="350" spans="2:9">
       <c r="B350" s="56" t="s">
-        <v>1517</v>
+        <v>1479</v>
       </c>
       <c r="C350" s="18"/>
       <c r="D350" s="18"/>
       <c r="E350" s="57"/>
-      <c r="G350" s="69">
+    </row>
+    <row r="351" spans="2:9">
+      <c r="B351" s="56" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C351" s="18"/>
+      <c r="D351" s="18"/>
+      <c r="E351" s="57"/>
+      <c r="G351" s="5" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="352" spans="2:9">
+      <c r="B352" s="56" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C352" s="18"/>
+      <c r="D352" s="18"/>
+      <c r="E352" s="57"/>
+      <c r="G352" s="5">
         <v>123</v>
       </c>
-      <c r="I350" t="s">
-        <v>1516</v>
-      </c>
-      <c r="K350" s="69">
+      <c r="I352" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="353" spans="2:9">
+      <c r="B353" s="54" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C353" s="7"/>
+      <c r="D353" s="7"/>
+      <c r="E353" s="55"/>
+      <c r="G353" s="5">
+        <v>123</v>
+      </c>
+      <c r="I353" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="354" spans="2:9">
+      <c r="G354" s="5" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="355" spans="2:9">
+      <c r="G355" s="5">
         <v>456</v>
       </c>
     </row>
-    <row r="351" spans="2:11">
-      <c r="B351" s="54" t="s">
-        <v>1521</v>
-      </c>
-      <c r="C351" s="7"/>
-      <c r="D351" s="7"/>
-      <c r="E351" s="55"/>
-      <c r="G351" s="92" t="s">
-        <v>1676</v>
-      </c>
-      <c r="K351" s="70" t="s">
-        <v>1522</v>
-      </c>
-    </row>
-    <row r="353" spans="2:9">
-      <c r="I353" s="71" t="s">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="354" spans="2:9">
-      <c r="B354" s="8" t="s">
-        <v>1529</v>
-      </c>
-      <c r="I354" s="72"/>
-    </row>
-    <row r="355" spans="2:9">
-      <c r="I355" s="72"/>
-    </row>
     <row r="356" spans="2:9">
-      <c r="B356" s="51" t="s">
+      <c r="B356" s="8" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G356" s="5">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="358" spans="2:9">
+      <c r="B358" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C356" s="52"/>
-      <c r="D356" s="52"/>
-      <c r="E356" s="53"/>
-      <c r="I356" s="72"/>
-    </row>
-    <row r="357" spans="2:9">
-      <c r="B357" s="56"/>
-      <c r="C357" s="18"/>
-      <c r="D357" s="18"/>
-      <c r="E357" s="57"/>
-      <c r="I357" s="72"/>
-    </row>
-    <row r="358" spans="2:9">
-      <c r="B358" s="56" t="s">
-        <v>1527</v>
-      </c>
-      <c r="C358" s="18"/>
-      <c r="D358" s="18"/>
-      <c r="E358" s="57"/>
-      <c r="I358" s="72"/>
+      <c r="C358" s="52"/>
+      <c r="D358" s="52"/>
+      <c r="E358" s="53"/>
     </row>
     <row r="359" spans="2:9">
       <c r="B359" s="56"/>
       <c r="C359" s="18"/>
       <c r="D359" s="18"/>
       <c r="E359" s="57"/>
-      <c r="I359" s="72"/>
     </row>
     <row r="360" spans="2:9">
       <c r="B360" s="56" t="s">
-        <v>1528</v>
+        <v>1677</v>
       </c>
       <c r="C360" s="18"/>
       <c r="D360" s="18"/>
       <c r="E360" s="57"/>
-      <c r="I360" s="72"/>
     </row>
     <row r="361" spans="2:9">
-      <c r="B361" s="56"/>
+      <c r="B361" s="56" t="s">
+        <v>1675</v>
+      </c>
       <c r="C361" s="18"/>
       <c r="D361" s="18"/>
       <c r="E361" s="57"/>
-      <c r="I361" s="72"/>
     </row>
     <row r="362" spans="2:9">
-      <c r="B362" s="56" t="s">
-        <v>1530</v>
-      </c>
+      <c r="B362" s="56"/>
       <c r="C362" s="18"/>
       <c r="D362" s="18"/>
       <c r="E362" s="57"/>
-      <c r="I362" s="72"/>
     </row>
     <row r="363" spans="2:9">
       <c r="B363" s="56" t="s">
-        <v>1531</v>
+        <v>1469</v>
       </c>
       <c r="C363" s="18"/>
       <c r="D363" s="18"/>
       <c r="E363" s="57"/>
-      <c r="G363" t="s">
-        <v>1537</v>
-      </c>
-      <c r="I363" s="72"/>
     </row>
     <row r="364" spans="2:9">
-      <c r="B364" s="56" t="s">
-        <v>1532</v>
-      </c>
+      <c r="B364" s="56"/>
       <c r="C364" s="18"/>
       <c r="D364" s="18"/>
       <c r="E364" s="57"/>
-      <c r="G364" t="s">
-        <v>1538</v>
-      </c>
-      <c r="I364" s="72"/>
     </row>
     <row r="365" spans="2:9">
       <c r="B365" s="56" t="s">
-        <v>1533</v>
+        <v>1474</v>
       </c>
       <c r="C365" s="18"/>
       <c r="D365" s="18"/>
       <c r="E365" s="57"/>
-      <c r="G365" t="s">
-        <v>1539</v>
-      </c>
-      <c r="I365" s="72"/>
+      <c r="G365" s="5" t="s">
+        <v>1476</v>
+      </c>
     </row>
     <row r="366" spans="2:9">
       <c r="B366" s="56" t="s">
-        <v>1534</v>
+        <v>1475</v>
       </c>
       <c r="C366" s="18"/>
       <c r="D366" s="18"/>
       <c r="E366" s="57"/>
-      <c r="G366" t="s">
+      <c r="G366" s="5" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="367" spans="2:9">
+      <c r="B367" s="56"/>
+      <c r="C367" s="18"/>
+      <c r="D367" s="18"/>
+      <c r="E367" s="57"/>
+    </row>
+    <row r="368" spans="2:9">
+      <c r="B368" s="56" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C368" s="18"/>
+      <c r="D368" s="18"/>
+      <c r="E368" s="57"/>
+    </row>
+    <row r="369" spans="2:11">
+      <c r="B369" s="56" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C369" s="18"/>
+      <c r="D369" s="18"/>
+      <c r="E369" s="57"/>
+      <c r="G369" s="68" t="s">
+        <v>1512</v>
+      </c>
+      <c r="I369" t="s">
+        <v>1518</v>
+      </c>
+      <c r="K369" s="68" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="370" spans="2:11">
+      <c r="B370" s="56" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C370" s="18"/>
+      <c r="D370" s="18"/>
+      <c r="E370" s="57"/>
+      <c r="G370" s="69" t="s">
+        <v>1513</v>
+      </c>
+      <c r="I370" t="s">
+        <v>1514</v>
+      </c>
+      <c r="K370" s="69" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="371" spans="2:11">
+      <c r="B371" s="56" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C371" s="18"/>
+      <c r="D371" s="18"/>
+      <c r="E371" s="57"/>
+      <c r="G371" s="69" t="s">
+        <v>1515</v>
+      </c>
+      <c r="I371" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K371" s="69" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="372" spans="2:11">
+      <c r="B372" s="56" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C372" s="18"/>
+      <c r="D372" s="18"/>
+      <c r="E372" s="57"/>
+      <c r="G372" s="69">
+        <v>123</v>
+      </c>
+      <c r="I372" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K372" s="69">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="373" spans="2:11">
+      <c r="B373" s="54" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C373" s="7"/>
+      <c r="D373" s="7"/>
+      <c r="E373" s="55"/>
+      <c r="G373" s="92" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K373" s="70" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="375" spans="2:11">
+      <c r="I375" s="71" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="376" spans="2:11">
+      <c r="B376" s="8" t="s">
+        <v>1529</v>
+      </c>
+      <c r="I376" s="72"/>
+    </row>
+    <row r="377" spans="2:11">
+      <c r="I377" s="72"/>
+    </row>
+    <row r="378" spans="2:11">
+      <c r="B378" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C378" s="52"/>
+      <c r="D378" s="52"/>
+      <c r="E378" s="53"/>
+      <c r="I378" s="72"/>
+    </row>
+    <row r="379" spans="2:11">
+      <c r="B379" s="56"/>
+      <c r="C379" s="18"/>
+      <c r="D379" s="18"/>
+      <c r="E379" s="57"/>
+      <c r="I379" s="72"/>
+    </row>
+    <row r="380" spans="2:11">
+      <c r="B380" s="56" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C380" s="18"/>
+      <c r="D380" s="18"/>
+      <c r="E380" s="57"/>
+      <c r="I380" s="72"/>
+    </row>
+    <row r="381" spans="2:11">
+      <c r="B381" s="56"/>
+      <c r="C381" s="18"/>
+      <c r="D381" s="18"/>
+      <c r="E381" s="57"/>
+      <c r="I381" s="72"/>
+    </row>
+    <row r="382" spans="2:11">
+      <c r="B382" s="56" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C382" s="18"/>
+      <c r="D382" s="18"/>
+      <c r="E382" s="57"/>
+      <c r="I382" s="72"/>
+    </row>
+    <row r="383" spans="2:11">
+      <c r="B383" s="56"/>
+      <c r="C383" s="18"/>
+      <c r="D383" s="18"/>
+      <c r="E383" s="57"/>
+      <c r="I383" s="72"/>
+    </row>
+    <row r="384" spans="2:11">
+      <c r="B384" s="56" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C384" s="18"/>
+      <c r="D384" s="18"/>
+      <c r="E384" s="57"/>
+      <c r="I384" s="72"/>
+    </row>
+    <row r="385" spans="1:9">
+      <c r="B385" s="56" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C385" s="18"/>
+      <c r="D385" s="18"/>
+      <c r="E385" s="57"/>
+      <c r="G385" t="s">
+        <v>1537</v>
+      </c>
+      <c r="I385" s="72"/>
+    </row>
+    <row r="386" spans="1:9">
+      <c r="B386" s="56" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C386" s="18"/>
+      <c r="D386" s="18"/>
+      <c r="E386" s="57"/>
+      <c r="G386" t="s">
+        <v>1538</v>
+      </c>
+      <c r="I386" s="72"/>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="B387" s="56" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C387" s="18"/>
+      <c r="D387" s="18"/>
+      <c r="E387" s="57"/>
+      <c r="G387" t="s">
+        <v>1539</v>
+      </c>
+      <c r="I387" s="72"/>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="B388" s="56" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C388" s="18"/>
+      <c r="D388" s="18"/>
+      <c r="E388" s="57"/>
+      <c r="G388" t="s">
         <v>1540</v>
       </c>
-      <c r="I366" s="72"/>
-    </row>
-    <row r="367" spans="2:9">
-      <c r="B367" s="54" t="s">
+      <c r="I388" s="72"/>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="B389" s="54" t="s">
         <v>1535</v>
       </c>
-      <c r="C367" s="7"/>
-      <c r="D367" s="7"/>
-      <c r="E367" s="55"/>
-      <c r="G367" t="s">
+      <c r="C389" s="7"/>
+      <c r="D389" s="7"/>
+      <c r="E389" s="55"/>
+      <c r="G389" t="s">
         <v>1536</v>
       </c>
-      <c r="I367" s="72"/>
-    </row>
-    <row r="368" spans="2:9">
-      <c r="I368" s="72"/>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" s="8" t="s">
+      <c r="I389" s="72"/>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="I390" s="72"/>
+    </row>
+    <row r="392" spans="1:9">
+      <c r="A392" s="8" t="s">
         <v>1524</v>
       </c>
     </row>
-    <row r="371" spans="1:2">
-      <c r="B371" t="s">
+    <row r="393" spans="1:9">
+      <c r="B393" t="s">
         <v>1525</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
-      <c r="B372" t="s">
+    <row r="394" spans="1:9">
+      <c r="B394" t="s">
         <v>1526</v>
       </c>
     </row>
-    <row r="374" spans="1:2">
-      <c r="A374" s="8" t="s">
+    <row r="396" spans="1:9">
+      <c r="A396" s="8" t="s">
         <v>1649</v>
       </c>
     </row>
-    <row r="375" spans="1:2">
-      <c r="B375" t="s">
+    <row r="397" spans="1:9">
+      <c r="B397" t="s">
         <v>1647</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
-      <c r="B376" t="s">
+    <row r="398" spans="1:9">
+      <c r="B398" t="s">
         <v>1648</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="152" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="151" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="150" priority="10">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>$C$12=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38494,17 +38982,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="149" priority="2">
+    <cfRule type="expression" dxfId="56" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="148" priority="5">
+    <cfRule type="expression" dxfId="55" priority="5">
       <formula>$B$44&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="147" priority="6">
+    <cfRule type="expression" dxfId="54" priority="6">
       <formula>$B$42&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38881,17 +39369,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="146" priority="4">
+    <cfRule type="expression" dxfId="53" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="145" priority="3">
+    <cfRule type="expression" dxfId="52" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="144" priority="2">
+    <cfRule type="expression" dxfId="51" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39170,22 +39658,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="143" priority="4">
+    <cfRule type="expression" dxfId="50" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="142" priority="3">
+    <cfRule type="expression" dxfId="49" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="141" priority="2">
+    <cfRule type="expression" dxfId="48" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="140" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39555,22 +40043,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="139" priority="4">
+    <cfRule type="expression" dxfId="46" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="138" priority="3">
+    <cfRule type="expression" dxfId="45" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="137" priority="2">
+    <cfRule type="expression" dxfId="44" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="136" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40890,17 +41378,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="135" priority="4">
+    <cfRule type="expression" dxfId="42" priority="4">
       <formula>$B$103&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="134" priority="3">
+    <cfRule type="expression" dxfId="41" priority="3">
       <formula>$B$101&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="133" priority="2">
+    <cfRule type="expression" dxfId="40" priority="2">
       <formula>$B$83=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41041,22 +41529,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="132" priority="4">
+    <cfRule type="expression" dxfId="39" priority="4">
       <formula>$B$32&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="131" priority="3">
+    <cfRule type="expression" dxfId="38" priority="3">
       <formula>$B$30&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="130" priority="2">
+    <cfRule type="expression" dxfId="37" priority="2">
       <formula>$B$12=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="129" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>$B$30&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Regex 04.02.25.xlsx
+++ b/Regex 04.02.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="787" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="787" firstSheet="4" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="4" r:id="rId1"/>
@@ -31,13 +31,14 @@
     <sheet name="Universal" sheetId="22" r:id="rId22"/>
     <sheet name="Niki" sheetId="23" r:id="rId23"/>
     <sheet name="Felo" sheetId="24" r:id="rId24"/>
+    <sheet name="Invoice" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3315" uniqueCount="1930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3551" uniqueCount="2119">
   <si>
     <t>with (?mx) with description</t>
   </si>
@@ -17277,17 +17278,3243 @@
       <t>:</t>
     </r>
   </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t>import pandas as pd</t>
+  </si>
+  <si>
+    <t># --- Convert to DataFrames ---</t>
+  </si>
+  <si>
+    <t># Convert quantities to numbers</t>
+  </si>
+  <si>
+    <t># --- Combine all invoices into one (grouped by Article) ---</t>
+  </si>
+  <si>
+    <t># --- Merge with initial order ---</t>
+  </si>
+  <si>
+    <t># Output 1 DataFrame</t>
+  </si>
+  <si>
+    <t>print('\nOnly the remaining:\n')</t>
+  </si>
+  <si>
+    <t># Filter only rows with Remaining_Qty &gt; 0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>initial_order</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = """</t>
+    </r>
+  </si>
+  <si>
+    <t>partial_invoicing_2</t>
+  </si>
+  <si>
+    <t>1093900 20</t>
+  </si>
+  <si>
+    <t>1150650114 8</t>
+  </si>
+  <si>
+    <t>1152300400 80</t>
+  </si>
+  <si>
+    <t>1152900 80</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>invoice_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = """</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = """</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>re</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>matches_initial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>re</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>findall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(pattern, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>initial_order</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>matches_invoice_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>re</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>findall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(pattern, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>invoice_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>matches_invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>re</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>findall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(pattern, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print("Хванати артикули:", len(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>matches_initial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>))  # test</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_initial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DataFrame</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>matches_initial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>columns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=["Article", "Ordered_Qty"])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">df_invoice_1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pd.DataFrame</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>matches_invoice_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>columns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=["Article", "Invoiced_Qty"])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pd.DataFrame</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>matches_invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>columns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=["Article", "Invoiced_Qty"])</t>
+    </r>
+  </si>
+  <si>
+    <t>df_initial</t>
+  </si>
+  <si>
+    <t>1093900 10</t>
+  </si>
+  <si>
+    <t>1150650114 5</t>
+  </si>
+  <si>
+    <t>1152900 2</t>
+  </si>
+  <si>
+    <t>1152300400 70</t>
+  </si>
+  <si>
+    <t>df_invoice_1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_initial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">["Ordered_Qty"]   = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_initial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["Ordered_Qty"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>astype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(float)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">["Invoiced_Qty"] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["Invoiced_Qty"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>astype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(float)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">["Invoiced_Qty"] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["Invoiced_Qty"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>astype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(float)</t>
+    </r>
+  </si>
+  <si>
+    <t>df_invoice_2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all_invoices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>concat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>([</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">], </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ignore_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True)</t>
+    </r>
+  </si>
+  <si>
+    <t>all_invoices</t>
+  </si>
+  <si>
+    <t>1152300400 5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all_invoices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all_invoices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("Article", as_index=False)["Invoiced_Qty"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t># Print in custom format: index;Article;Remaining_Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    print(f"{i+1};{row['Article']};{row['Remaining_Qty']}")</t>
+  </si>
+  <si>
+    <t>df_remaining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Article  Invoiced_Qty</t>
+  </si>
+  <si>
+    <t>0  1152300400           5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Article Invoiced_Qty</t>
+  </si>
+  <si>
+    <t>0  1152300400            5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Article         Ordered_Qty     Invoiced_Qty</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_initial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>merge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all_invoices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="Article", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>how</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>="left").</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fillna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(0)</t>
+    </r>
+  </si>
+  <si>
+    <t>1     1150650114          8.0           5.0            3.0</t>
+  </si>
+  <si>
+    <t>3     1152300400         80.0          75.0            5.0</t>
+  </si>
+  <si>
+    <t>0     1093900               20.0          10.0           10.0</t>
+  </si>
+  <si>
+    <t>2     1152900                80.0           2.0           78.0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remaining_Qty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">["Ordered_Qty"] - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["Invoiced_Qty"]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      Article   Ordered_Qty   Invoiced_Qty   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remaining_Qty</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>0    1093900            10.0</t>
+  </si>
+  <si>
+    <t>1    1150650114        5.0</t>
+  </si>
+  <si>
+    <t>2    1152300400      75.0</t>
+  </si>
+  <si>
+    <t>3     1152900               2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Article         Invoiced_Qty</t>
+  </si>
+  <si>
+    <t>0    1093900             10.0</t>
+  </si>
+  <si>
+    <t>2    1152900               2.0</t>
+  </si>
+  <si>
+    <t>3    1152300400      70.0</t>
+  </si>
+  <si>
+    <t>4    1152300400         5.0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>remaining_only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remaining_Qty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] &gt; 0].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reset_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(drop=True)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for i, row in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>remaining_only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iterrows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>():</t>
+    </r>
+  </si>
+  <si>
+    <t>1;1093900;10.0</t>
+  </si>
+  <si>
+    <t>2;1150650114;3.0</t>
+  </si>
+  <si>
+    <t>3;1152900;78.0</t>
+  </si>
+  <si>
+    <t>4;1152300400;5.0</t>
+  </si>
+  <si>
+    <t>&lt;generator object DataFrame.iterrows at 0x000000000B30DE40&gt;</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>remaining_only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iterrows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>():</t>
+    </r>
+  </si>
+  <si>
+    <t>Ordered_Qty         20.0</t>
+  </si>
+  <si>
+    <t>Invoiced_Qty        10.0</t>
+  </si>
+  <si>
+    <t>Remaining_Qty       10.0</t>
+  </si>
+  <si>
+    <t>Name: 0, dtype: object</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>class 'int'&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;class 'pandas.core.series.Series'&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Article          1093900</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, row)  # test</t>
+    </r>
+  </si>
+  <si>
+    <t>3     1152300400      80.0</t>
+  </si>
+  <si>
+    <t>2     1152900            80.0</t>
+  </si>
+  <si>
+    <t>1     1150650114       8.0</t>
+  </si>
+  <si>
+    <t>0     1093900            20.0</t>
+  </si>
+  <si>
+    <t>3     1152300400       70.0</t>
+  </si>
+  <si>
+    <t>2     1152900               2.0</t>
+  </si>
+  <si>
+    <t>1     1150650114        5.0</t>
+  </si>
+  <si>
+    <t>0     1093900            10.0</t>
+  </si>
+  <si>
+    <t>1     1150650114        8</t>
+  </si>
+  <si>
+    <t>2     1152900             80</t>
+  </si>
+  <si>
+    <t>3     1152300400      80</t>
+  </si>
+  <si>
+    <t>0     1093900             20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Article   Ordered_Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Article    Ordered_Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Article    Invoiced_Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Article              Invoiced_Qty</t>
+  </si>
+  <si>
+    <t>1     1150650114         5</t>
+  </si>
+  <si>
+    <t>0     1093900              10</t>
+  </si>
+  <si>
+    <t>2     1152900                2</t>
+  </si>
+  <si>
+    <t>3     1152300400       70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Article   Invoiced_Qty</t>
+  </si>
+  <si>
+    <t># --- pivot the previous dataframe: all_invoices</t>
+  </si>
+  <si>
+    <r>
+      <t>ако някоя позиция е фактурирана напълно - ще се покаже на</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+  </si>
+  <si>
+    <t>0     1093900             20.0          10.0</t>
+  </si>
+  <si>
+    <t>1     1150650114        8.0             5.0</t>
+  </si>
+  <si>
+    <t>2     1152900             80.0             2.0</t>
+  </si>
+  <si>
+    <t>3     1152300400      80.0           75.0</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0     1093900             20.0            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0,0</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"># --- create new column Remaining_Qty and fill it with substracted quantity </t>
+  </si>
+  <si>
+    <t>control the DataFrame index</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ignore_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Used when concatenating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DataFrames</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Without it:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Article  Invoiced_Qty</t>
+  </si>
+  <si>
+    <t>0  1093900          10</t>
+  </si>
+  <si>
+    <t>1  1152900           2</t>
+  </si>
+  <si>
+    <r>
+      <t>pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>concat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>([df_invoice_1, df_invoice_2])</t>
+    </r>
+  </si>
+  <si>
+    <t>Result:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Article      Invoiced_Qty</t>
+  </si>
+  <si>
+    <t>0  1093900              10</t>
+  </si>
+  <si>
+    <t>1  1152900               2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1152300400            5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1152300400        5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Notice the duplicate index </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>concat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>([</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_invoice_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>],</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ignore_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True)</t>
+    </r>
+  </si>
+  <si>
+    <t>2  1152300400            5</t>
+  </si>
+  <si>
+    <t>Pandas creates a fresh continuous index</t>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all_invoices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all_invoices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False)["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Invoiced_Qty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Used with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all_invoices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all_invoices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Invoiced_Qty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>Article</t>
+  </si>
+  <si>
+    <t>1093900        10</t>
+  </si>
+  <si>
+    <t>1152900         2</t>
+  </si>
+  <si>
+    <t>1152300400     75</t>
+  </si>
+  <si>
+    <t>Name: Invoiced_Qty, dtype: float64</t>
+  </si>
+  <si>
+    <t>Here Article becomes the index</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">With </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False:</t>
+    </r>
+  </si>
+  <si>
+    <t>2     1152300400       75</t>
+  </si>
+  <si>
+    <t>1     1152900                2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Article        Invoiced_Qty</t>
+  </si>
+  <si>
+    <t>Article stays a normal column, which is convenient because you're about to do:</t>
+  </si>
+  <si>
+    <t>df_initial.merge(all_invoices, on="Article")</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ignore_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>With</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ignore_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True :</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>remaining_only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df_remaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remaining_Qty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] &gt; 0].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reset_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>drop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True)</t>
+    </r>
+  </si>
+  <si>
+    <t>Suppose after filtering you get:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Article    Remaining_Qty</t>
+  </si>
+  <si>
+    <t>1  1093900             10</t>
+  </si>
+  <si>
+    <t>3  1152900             78</t>
+  </si>
+  <si>
+    <t>Notice the index values are still 1 and 3 from the original DataFrame.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>With</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reset_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>drop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   index   Article   Remaining_Qty</t>
+  </si>
+  <si>
+    <t>0      1   1093900            10</t>
+  </si>
+  <si>
+    <t>1      3   1152900            78</t>
+  </si>
+  <si>
+    <t>reset_index() → renumbers rows and keeps the old index as a column</t>
+  </si>
+  <si>
+    <t>reset_index(drop=True) → renumbers rows and discards the old index.</t>
+  </si>
+  <si>
+    <r>
+      <t>pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>concat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(..., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ignore_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True)</t>
+    </r>
+  </si>
+  <si>
+    <t>make one clean index after joining dataframes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(..., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False)</t>
+    </r>
+  </si>
+  <si>
+    <t>keep Article as a regular column for the merge</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reset_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>drop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True)</t>
+    </r>
+  </si>
+  <si>
+    <t>after filtering remaining items, renumber rows from 0,1,2,... and throw away the old row numbers</t>
+  </si>
+  <si>
+    <r>
+      <t>3. .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reset_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>drop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True)</t>
+    </r>
+  </si>
+  <si>
+    <t>invoice_1</t>
+  </si>
+  <si>
+    <t>initial_order</t>
+  </si>
+  <si>
+    <t>invoice_2</t>
+  </si>
+  <si>
+    <t>matches_initial</t>
+  </si>
+  <si>
+    <t>matches_invoice_1</t>
+  </si>
+  <si>
+    <t>matches_invoice_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all_invoices = df_invoice_1 + df_invoice_2 </t>
+  </si>
+  <si>
+    <t>all_invoices - pivot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">df_remaining - vlookup all-invoices </t>
+  </si>
+  <si>
+    <t>remaining_only</t>
+  </si>
+  <si>
+    <t>remaining_only - filtered</t>
+  </si>
+  <si>
+    <t>for i, row in remaining_only.iterrows():</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>основната поръчка</t>
+  </si>
+  <si>
+    <t>първата фактура</t>
+  </si>
+  <si>
+    <t>втората фактура</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern </t>
+  </si>
+  <si>
+    <t>шаблона</t>
+  </si>
+  <si>
+    <t>concat</t>
+  </si>
+  <si>
+    <t>groupby</t>
+  </si>
+  <si>
+    <t>merge</t>
+  </si>
+  <si>
+    <t>list[tuples]</t>
+  </si>
+  <si>
+    <t>pd.DataFrame</t>
+  </si>
+  <si>
+    <t>re.findall</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.reset_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>drop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="73">
+  <fonts count="77">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -17856,6 +21083,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -18072,73 +21307,73 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -18146,23 +21381,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -18183,33 +21418,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -18217,33 +21452,51 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="293">
+  <dxfs count="333">
     <dxf>
       <fill>
         <patternFill>
@@ -18661,6 +21914,286 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -20299,11 +23832,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFA47A20"/>
       <color rgb="FFDA7BB9"/>
-      <color rgb="FFA47A20"/>
       <color rgb="FF179A77"/>
+      <color rgb="FF7D7DFF"/>
       <color rgb="FFA626A4"/>
-      <color rgb="FF7D7DFF"/>
       <color rgb="FFFF33CC"/>
     </mruColors>
   </colors>
@@ -20483,6 +24016,340 @@
         <a:xfrm rot="10800000">
           <a:off x="4595817" y="60626629"/>
           <a:ext cx="385758" cy="185734"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>211019</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>6626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>13253</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>105505</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Arrow Connector 4"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="7486462" y="7798904"/>
+          <a:ext cx="3459834" cy="2139714"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>52754</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>99646</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>539261</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>101234</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4894385" y="38621677"/>
+          <a:ext cx="486507" cy="1588"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>29307</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>146538</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>550984</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4870938" y="38668569"/>
+          <a:ext cx="521677" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>58615</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>550984</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>89511</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7948246" y="38609954"/>
+          <a:ext cx="492369" cy="1588"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>35169</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>568569</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>89511</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4876800" y="38428246"/>
+          <a:ext cx="5410200" cy="1588"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>23446</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>169985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>550984</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>105507</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Straight Arrow Connector 12"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9741877" y="38510308"/>
+          <a:ext cx="527538" cy="117230"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>264251</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>40550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>265839</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>113436</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Arrow Connector 14"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="10459279" y="39501417"/>
+          <a:ext cx="258417" cy="1588"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -20876,1150 +24743,1334 @@
       <c r="C8" s="19" t="s">
         <v>1829</v>
       </c>
-      <c r="D8" s="19"/>
+      <c r="D8" s="19" t="s">
+        <v>1930</v>
+      </c>
       <c r="E8" s="19"/>
       <c r="F8" s="19"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="292" priority="219">
+    <cfRule type="expression" dxfId="332" priority="257">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E5">
-    <cfRule type="expression" dxfId="291" priority="220">
+    <cfRule type="expression" dxfId="331" priority="258">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="290" priority="221">
+    <cfRule type="expression" dxfId="330" priority="259">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:F4 C4:C5 D3:F5">
-    <cfRule type="expression" dxfId="289" priority="222">
+    <cfRule type="expression" dxfId="329" priority="260">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="288" priority="223">
+    <cfRule type="expression" dxfId="328" priority="261">
       <formula>$B$27&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5 C3:F3 C4:D4">
-    <cfRule type="expression" dxfId="287" priority="224">
+    <cfRule type="expression" dxfId="327" priority="262">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="expression" dxfId="286" priority="260">
+    <cfRule type="expression" dxfId="326" priority="298">
       <formula>$B$9&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="285" priority="261">
+    <cfRule type="expression" dxfId="325" priority="299">
       <formula>$B$9&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="expression" dxfId="284" priority="262">
+    <cfRule type="expression" dxfId="324" priority="300">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="283" priority="263">
+    <cfRule type="expression" dxfId="323" priority="301">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="282" priority="264">
+    <cfRule type="expression" dxfId="322" priority="302">
       <formula>$B$15&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="281" priority="267">
+    <cfRule type="expression" dxfId="321" priority="305">
       <formula>$B$21&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:F5">
-    <cfRule type="expression" dxfId="280" priority="271">
+    <cfRule type="expression" dxfId="320" priority="309">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D5">
-    <cfRule type="expression" dxfId="279" priority="272">
+    <cfRule type="expression" dxfId="319" priority="310">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="278" priority="218">
+    <cfRule type="expression" dxfId="318" priority="256">
       <formula>$B$27&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="277" priority="217">
+    <cfRule type="expression" dxfId="317" priority="255">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="276" priority="216">
+    <cfRule type="expression" dxfId="316" priority="254">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="expression" dxfId="275" priority="215">
+    <cfRule type="expression" dxfId="315" priority="253">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="expression" dxfId="274" priority="214">
+    <cfRule type="expression" dxfId="314" priority="252">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="273" priority="213">
+    <cfRule type="expression" dxfId="313" priority="251">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="272" priority="212">
+    <cfRule type="expression" dxfId="312" priority="250">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="271" priority="211">
+    <cfRule type="expression" dxfId="311" priority="249">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="270" priority="210">
+    <cfRule type="expression" dxfId="310" priority="248">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="269" priority="209">
+    <cfRule type="expression" dxfId="309" priority="247">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="268" priority="208">
+    <cfRule type="expression" dxfId="308" priority="246">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="267" priority="207">
+    <cfRule type="expression" dxfId="307" priority="245">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="266" priority="206">
+    <cfRule type="expression" dxfId="306" priority="244">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="265" priority="205">
+    <cfRule type="expression" dxfId="305" priority="243">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:F6">
-    <cfRule type="expression" dxfId="264" priority="204">
+    <cfRule type="expression" dxfId="304" priority="242">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="263" priority="203">
+    <cfRule type="expression" dxfId="303" priority="241">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="262" priority="201">
+    <cfRule type="expression" dxfId="302" priority="239">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="261" priority="202">
+    <cfRule type="expression" dxfId="301" priority="240">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:F6">
-    <cfRule type="expression" dxfId="260" priority="200">
+    <cfRule type="expression" dxfId="300" priority="238">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="259" priority="199">
+    <cfRule type="expression" dxfId="299" priority="237">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="258" priority="198">
+    <cfRule type="expression" dxfId="298" priority="236">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="257" priority="197">
+    <cfRule type="expression" dxfId="297" priority="235">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="256" priority="196">
+    <cfRule type="expression" dxfId="296" priority="234">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="255" priority="195">
+    <cfRule type="expression" dxfId="295" priority="233">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="254" priority="194">
+    <cfRule type="expression" dxfId="294" priority="232">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="253" priority="193">
+    <cfRule type="expression" dxfId="293" priority="231">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="252" priority="192">
+    <cfRule type="expression" dxfId="292" priority="230">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="251" priority="191">
+    <cfRule type="expression" dxfId="291" priority="229">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="250" priority="190">
+    <cfRule type="expression" dxfId="290" priority="228">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="249" priority="189">
+    <cfRule type="expression" dxfId="289" priority="227">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="248" priority="188">
+    <cfRule type="expression" dxfId="288" priority="226">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="247" priority="187">
+    <cfRule type="expression" dxfId="287" priority="225">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="246" priority="186">
+    <cfRule type="expression" dxfId="286" priority="224">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="245" priority="185">
+    <cfRule type="expression" dxfId="285" priority="223">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="244" priority="184">
+    <cfRule type="expression" dxfId="284" priority="222">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="243" priority="183">
+    <cfRule type="expression" dxfId="283" priority="221">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="242" priority="182">
+    <cfRule type="expression" dxfId="282" priority="220">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="241" priority="181">
+    <cfRule type="expression" dxfId="281" priority="219">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="240" priority="180">
+    <cfRule type="expression" dxfId="280" priority="218">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="239" priority="179">
+    <cfRule type="expression" dxfId="279" priority="217">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="238" priority="178">
+    <cfRule type="expression" dxfId="278" priority="216">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="237" priority="177">
+    <cfRule type="expression" dxfId="277" priority="215">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="236" priority="176">
+    <cfRule type="expression" dxfId="276" priority="214">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="235" priority="175">
+    <cfRule type="expression" dxfId="275" priority="213">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="234" priority="174">
+    <cfRule type="expression" dxfId="274" priority="212">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="233" priority="173">
+    <cfRule type="expression" dxfId="273" priority="211">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="232" priority="172">
+    <cfRule type="expression" dxfId="272" priority="210">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="231" priority="171">
+    <cfRule type="expression" dxfId="271" priority="209">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="230" priority="170">
+    <cfRule type="expression" dxfId="270" priority="208">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:F7">
-    <cfRule type="expression" dxfId="229" priority="169">
+    <cfRule type="expression" dxfId="269" priority="207">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="228" priority="168">
+    <cfRule type="expression" dxfId="268" priority="206">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="227" priority="166">
+    <cfRule type="expression" dxfId="267" priority="204">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="226" priority="167">
+    <cfRule type="expression" dxfId="266" priority="205">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:F7">
-    <cfRule type="expression" dxfId="225" priority="165">
+    <cfRule type="expression" dxfId="265" priority="203">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="224" priority="164">
+    <cfRule type="expression" dxfId="264" priority="202">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="223" priority="163">
+    <cfRule type="expression" dxfId="263" priority="201">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="222" priority="162">
+    <cfRule type="expression" dxfId="262" priority="200">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="221" priority="161">
+    <cfRule type="expression" dxfId="261" priority="199">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="220" priority="160">
+    <cfRule type="expression" dxfId="260" priority="198">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="219" priority="159">
+    <cfRule type="expression" dxfId="259" priority="197">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="218" priority="158">
+    <cfRule type="expression" dxfId="258" priority="196">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="217" priority="157">
+    <cfRule type="expression" dxfId="257" priority="195">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="216" priority="156">
+    <cfRule type="expression" dxfId="256" priority="194">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="215" priority="155">
+    <cfRule type="expression" dxfId="255" priority="193">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="214" priority="154">
+    <cfRule type="expression" dxfId="254" priority="192">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="213" priority="153">
+    <cfRule type="expression" dxfId="253" priority="191">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="212" priority="152">
+    <cfRule type="expression" dxfId="252" priority="190">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="211" priority="151">
+    <cfRule type="expression" dxfId="251" priority="189">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="210" priority="150">
+    <cfRule type="expression" dxfId="250" priority="188">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="209" priority="149">
+    <cfRule type="expression" dxfId="249" priority="187">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="208" priority="148">
+    <cfRule type="expression" dxfId="248" priority="186">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="207" priority="147">
+    <cfRule type="expression" dxfId="247" priority="185">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="206" priority="146">
+    <cfRule type="expression" dxfId="246" priority="184">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="205" priority="145">
+    <cfRule type="expression" dxfId="245" priority="183">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="204" priority="144">
+    <cfRule type="expression" dxfId="244" priority="182">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="203" priority="143">
+    <cfRule type="expression" dxfId="243" priority="181">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="202" priority="142">
+    <cfRule type="expression" dxfId="242" priority="180">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="201" priority="141">
+    <cfRule type="expression" dxfId="241" priority="179">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="200" priority="140">
+    <cfRule type="expression" dxfId="240" priority="178">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="199" priority="139">
+    <cfRule type="expression" dxfId="239" priority="177">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="198" priority="138">
+    <cfRule type="expression" dxfId="238" priority="176">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="197" priority="137">
+    <cfRule type="expression" dxfId="237" priority="175">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="196" priority="135">
+    <cfRule type="expression" dxfId="236" priority="173">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="195" priority="136">
+    <cfRule type="expression" dxfId="235" priority="174">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="194" priority="134">
+    <cfRule type="expression" dxfId="234" priority="172">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="193" priority="133">
+    <cfRule type="expression" dxfId="233" priority="171">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="192" priority="132">
+    <cfRule type="expression" dxfId="232" priority="170">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="191" priority="131">
+    <cfRule type="expression" dxfId="231" priority="169">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="190" priority="130">
+    <cfRule type="expression" dxfId="230" priority="168">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="189" priority="129">
+    <cfRule type="expression" dxfId="229" priority="167">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="188" priority="128">
+    <cfRule type="expression" dxfId="228" priority="166">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="187" priority="127">
+    <cfRule type="expression" dxfId="227" priority="165">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="186" priority="126">
+    <cfRule type="expression" dxfId="226" priority="164">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="185" priority="125">
+    <cfRule type="expression" dxfId="225" priority="163">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="184" priority="124">
+    <cfRule type="expression" dxfId="224" priority="162">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="183" priority="123">
+    <cfRule type="expression" dxfId="223" priority="161">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="182" priority="122">
+    <cfRule type="expression" dxfId="222" priority="160">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="181" priority="121">
+    <cfRule type="expression" dxfId="221" priority="159">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="180" priority="120">
+    <cfRule type="expression" dxfId="220" priority="158">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="179" priority="119">
+    <cfRule type="expression" dxfId="219" priority="157">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="178" priority="118">
+    <cfRule type="expression" dxfId="218" priority="156">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="177" priority="117">
+    <cfRule type="expression" dxfId="217" priority="155">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="176" priority="116">
+    <cfRule type="expression" dxfId="216" priority="154">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="175" priority="115">
+    <cfRule type="expression" dxfId="215" priority="153">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="174" priority="114">
+    <cfRule type="expression" dxfId="214" priority="152">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="173" priority="113">
+    <cfRule type="expression" dxfId="213" priority="151">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="172" priority="112">
+    <cfRule type="expression" dxfId="212" priority="150">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="171" priority="111">
+    <cfRule type="expression" dxfId="211" priority="149">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="170" priority="110">
+    <cfRule type="expression" dxfId="210" priority="148">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="169" priority="109">
+    <cfRule type="expression" dxfId="209" priority="147">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="168" priority="108">
+    <cfRule type="expression" dxfId="208" priority="146">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="167" priority="107">
+    <cfRule type="expression" dxfId="207" priority="145">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="166" priority="106">
+    <cfRule type="expression" dxfId="206" priority="144">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="165" priority="105">
+    <cfRule type="expression" dxfId="205" priority="143">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="164" priority="104">
+    <cfRule type="expression" dxfId="204" priority="142">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="163" priority="103">
+    <cfRule type="expression" dxfId="203" priority="141">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="162" priority="102">
+    <cfRule type="expression" dxfId="202" priority="140">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="161" priority="101">
+    <cfRule type="expression" dxfId="201" priority="139">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="160" priority="100">
+    <cfRule type="expression" dxfId="200" priority="138">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="159" priority="99">
+    <cfRule type="expression" dxfId="199" priority="137">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="158" priority="98">
+    <cfRule type="expression" dxfId="198" priority="136">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="157" priority="97">
+    <cfRule type="expression" dxfId="197" priority="135">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="156" priority="96">
+    <cfRule type="expression" dxfId="196" priority="134">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="155" priority="95">
+    <cfRule type="expression" dxfId="195" priority="133">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="154" priority="94">
+    <cfRule type="expression" dxfId="194" priority="132">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:F8">
-    <cfRule type="expression" dxfId="153" priority="93">
+    <cfRule type="expression" dxfId="193" priority="131">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="152" priority="92">
+    <cfRule type="expression" dxfId="192" priority="130">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="151" priority="90">
+    <cfRule type="expression" dxfId="191" priority="128">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="91">
+    <cfRule type="expression" dxfId="190" priority="129">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:F8">
-    <cfRule type="expression" dxfId="149" priority="89">
+    <cfRule type="expression" dxfId="189" priority="127">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="148" priority="88">
+    <cfRule type="expression" dxfId="188" priority="126">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="147" priority="87">
+    <cfRule type="expression" dxfId="187" priority="125">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="146" priority="86">
+    <cfRule type="expression" dxfId="186" priority="124">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="145" priority="85">
+    <cfRule type="expression" dxfId="185" priority="123">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="144" priority="84">
+    <cfRule type="expression" dxfId="184" priority="122">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="143" priority="83">
+    <cfRule type="expression" dxfId="183" priority="121">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="142" priority="82">
+    <cfRule type="expression" dxfId="182" priority="120">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="141" priority="81">
+    <cfRule type="expression" dxfId="181" priority="119">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="140" priority="80">
+    <cfRule type="expression" dxfId="180" priority="118">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="139" priority="79">
+    <cfRule type="expression" dxfId="179" priority="117">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="138" priority="78">
+    <cfRule type="expression" dxfId="178" priority="116">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="137" priority="77">
+    <cfRule type="expression" dxfId="177" priority="115">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="136" priority="76">
+    <cfRule type="expression" dxfId="176" priority="114">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="135" priority="75">
+    <cfRule type="expression" dxfId="175" priority="113">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="134" priority="74">
+    <cfRule type="expression" dxfId="174" priority="112">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="133" priority="73">
+    <cfRule type="expression" dxfId="173" priority="111">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="132" priority="72">
+    <cfRule type="expression" dxfId="172" priority="110">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="131" priority="71">
+    <cfRule type="expression" dxfId="171" priority="109">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="130" priority="70">
+    <cfRule type="expression" dxfId="170" priority="108">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="129" priority="69">
+    <cfRule type="expression" dxfId="169" priority="107">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="128" priority="68">
+    <cfRule type="expression" dxfId="168" priority="106">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="127" priority="67">
+    <cfRule type="expression" dxfId="167" priority="105">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="126" priority="66">
+    <cfRule type="expression" dxfId="166" priority="104">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="125" priority="65">
+    <cfRule type="expression" dxfId="165" priority="103">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="124" priority="64">
+    <cfRule type="expression" dxfId="164" priority="102">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="123" priority="63">
+    <cfRule type="expression" dxfId="163" priority="101">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="122" priority="62">
+    <cfRule type="expression" dxfId="162" priority="100">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="121" priority="61">
+    <cfRule type="expression" dxfId="161" priority="99">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="120" priority="59">
+    <cfRule type="expression" dxfId="160" priority="97">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="119" priority="60">
+    <cfRule type="expression" dxfId="159" priority="98">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="118" priority="58">
+    <cfRule type="expression" dxfId="158" priority="96">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="117" priority="57">
+    <cfRule type="expression" dxfId="157" priority="95">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="116" priority="56">
+    <cfRule type="expression" dxfId="156" priority="94">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="115" priority="55">
+    <cfRule type="expression" dxfId="155" priority="93">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="114" priority="54">
+    <cfRule type="expression" dxfId="154" priority="92">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="113" priority="53">
+    <cfRule type="expression" dxfId="153" priority="91">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="112" priority="52">
+    <cfRule type="expression" dxfId="152" priority="90">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="111" priority="51">
+    <cfRule type="expression" dxfId="151" priority="89">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="110" priority="50">
+    <cfRule type="expression" dxfId="150" priority="88">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="109" priority="49">
+    <cfRule type="expression" dxfId="149" priority="87">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="108" priority="48">
+    <cfRule type="expression" dxfId="148" priority="86">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="107" priority="47">
+    <cfRule type="expression" dxfId="147" priority="85">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="106" priority="46">
+    <cfRule type="expression" dxfId="146" priority="84">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="105" priority="45">
+    <cfRule type="expression" dxfId="145" priority="83">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="104" priority="44">
+    <cfRule type="expression" dxfId="144" priority="82">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="103" priority="43">
+    <cfRule type="expression" dxfId="143" priority="81">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="102" priority="42">
+    <cfRule type="expression" dxfId="142" priority="80">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="101" priority="41">
+    <cfRule type="expression" dxfId="141" priority="79">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="100" priority="40">
+    <cfRule type="expression" dxfId="140" priority="78">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="99" priority="39">
+    <cfRule type="expression" dxfId="139" priority="77">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="98" priority="38">
+    <cfRule type="expression" dxfId="138" priority="76">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="97" priority="37">
+    <cfRule type="expression" dxfId="137" priority="75">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="96" priority="36">
+    <cfRule type="expression" dxfId="136" priority="74">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="95" priority="35">
+    <cfRule type="expression" dxfId="135" priority="73">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="94" priority="34">
+    <cfRule type="expression" dxfId="134" priority="72">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="93" priority="33">
+    <cfRule type="expression" dxfId="133" priority="71">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="92" priority="32">
+    <cfRule type="expression" dxfId="132" priority="70">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="91" priority="31">
+    <cfRule type="expression" dxfId="131" priority="69">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="90" priority="30">
+    <cfRule type="expression" dxfId="130" priority="68">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="89" priority="29">
+    <cfRule type="expression" dxfId="129" priority="67">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="88" priority="28">
+    <cfRule type="expression" dxfId="128" priority="66">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="87" priority="27">
+    <cfRule type="expression" dxfId="127" priority="65">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="86" priority="26">
+    <cfRule type="expression" dxfId="126" priority="64">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="85" priority="25">
+    <cfRule type="expression" dxfId="125" priority="63">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="84" priority="24">
+    <cfRule type="expression" dxfId="124" priority="62">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="83" priority="23">
+    <cfRule type="expression" dxfId="123" priority="61">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="82" priority="22">
+    <cfRule type="expression" dxfId="122" priority="60">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="81" priority="21">
+    <cfRule type="expression" dxfId="121" priority="59">
       <formula>$B$28&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="80" priority="20">
+    <cfRule type="expression" dxfId="120" priority="58">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="79" priority="18">
+    <cfRule type="expression" dxfId="119" priority="56">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="19">
+    <cfRule type="expression" dxfId="118" priority="57">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="77" priority="17">
+    <cfRule type="expression" dxfId="117" priority="55">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="76" priority="16">
+    <cfRule type="expression" dxfId="116" priority="54">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="75" priority="15">
+    <cfRule type="expression" dxfId="115" priority="53">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="74" priority="14">
+    <cfRule type="expression" dxfId="114" priority="52">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="73" priority="13">
+    <cfRule type="expression" dxfId="113" priority="51">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="72" priority="12">
+    <cfRule type="expression" dxfId="112" priority="50">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="71" priority="11">
+    <cfRule type="expression" dxfId="111" priority="49">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="70" priority="10">
+    <cfRule type="expression" dxfId="110" priority="48">
       <formula>$B$26&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="69" priority="8">
+    <cfRule type="expression" dxfId="109" priority="46">
       <formula>$B$10&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="9">
+    <cfRule type="expression" dxfId="108" priority="47">
       <formula>$B$10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="67" priority="7">
+    <cfRule type="expression" dxfId="107" priority="45">
       <formula>$B$8=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="66" priority="6">
+    <cfRule type="expression" dxfId="106" priority="44">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="65" priority="5">
+    <cfRule type="expression" dxfId="105" priority="43">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="64" priority="4">
+    <cfRule type="expression" dxfId="104" priority="42">
       <formula>$B$16&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="63" priority="3">
+    <cfRule type="expression" dxfId="103" priority="41">
       <formula>$B$14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="62" priority="2">
+    <cfRule type="expression" dxfId="102" priority="40">
       <formula>$B$20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="101" priority="39">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="100" priority="37">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="38">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="98" priority="36">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="97" priority="35">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="96" priority="34">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="95" priority="33">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="94" priority="32">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="93" priority="31">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="92" priority="30">
+      <formula>$B$26&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="91" priority="28">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="29">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="89" priority="27">
+      <formula>$B$8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="88" priority="26">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="87" priority="25">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="86" priority="24">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="85" priority="23">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="84" priority="22">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="83" priority="21">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="82" priority="20">
+      <formula>$B$26&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="81" priority="18">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="19">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="79" priority="17">
+      <formula>$B$8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="78" priority="16">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="77" priority="15">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="76" priority="14">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="75" priority="13">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="74" priority="12">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="73" priority="11">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="72" priority="10">
+      <formula>$B$26&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="71" priority="8">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="9">
+      <formula>$B$10&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="69" priority="7">
+      <formula>$B$8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="68" priority="6">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="67" priority="5">
+      <formula>$B$22&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="66" priority="4">
+      <formula>$B$16&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="65" priority="3">
+      <formula>$B$14=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="64" priority="2">
+      <formula>$B$20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="63" priority="1">
       <formula>$B$22&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22045,6 +26096,7 @@
     <hyperlink ref="E7" location="Universal!A1" display="Universal"/>
     <hyperlink ref="F7" location="Niki!A1" display="Niki"/>
     <hyperlink ref="C8" location="Felo!A1" display="Felo"/>
+    <hyperlink ref="D8" location="Invoice!A1" display="Invoice"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22263,17 +26315,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="35" priority="3">
+    <cfRule type="expression" dxfId="34" priority="3">
       <formula>$B$40&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="34" priority="6">
+    <cfRule type="expression" dxfId="33" priority="6">
       <formula>$B$36&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="33" priority="7">
+    <cfRule type="expression" dxfId="32" priority="7">
       <formula>$B$15=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22777,17 +26829,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="32" priority="8">
+    <cfRule type="expression" dxfId="31" priority="8">
       <formula>$B$37&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="31" priority="9">
+    <cfRule type="expression" dxfId="30" priority="9">
       <formula>$B$17=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="30" priority="61">
+    <cfRule type="expression" dxfId="29" priority="61">
       <formula>$B$93&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23050,17 +27102,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>$B$23=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="28" priority="4">
+    <cfRule type="expression" dxfId="27" priority="4">
       <formula>$B$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="27" priority="5">
+    <cfRule type="expression" dxfId="26" priority="5">
       <formula>$B$45&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23223,17 +27275,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="26" priority="3">
+    <cfRule type="expression" dxfId="25" priority="3">
       <formula>$B$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="25" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>$B$45&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>$B$27=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25067,17 +29119,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="23" priority="3">
+    <cfRule type="expression" dxfId="22" priority="3">
       <formula>$B$54&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="21" priority="2">
       <formula>$B$52&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>$B$32=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25450,17 +29502,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="20" priority="7">
+    <cfRule type="expression" dxfId="19" priority="7">
       <formula>$C$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="19" priority="8">
+    <cfRule type="expression" dxfId="18" priority="8">
       <formula>$C$33&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="18" priority="9">
+    <cfRule type="expression" dxfId="17" priority="9">
       <formula>$C$15=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25607,17 +29659,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="16" priority="3">
       <formula>$B$53&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>$B$51&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>$B$33=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25755,17 +29807,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="13" priority="10">
       <formula>$B$38&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="12" priority="11">
       <formula>$B$36&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>$B$16=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32972,22 +37024,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="60" priority="4">
+    <cfRule type="expression" dxfId="62" priority="4">
       <formula>$B$37&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="59" priority="3">
+    <cfRule type="expression" dxfId="61" priority="3">
       <formula>$B$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="58" priority="2">
+    <cfRule type="expression" dxfId="60" priority="2">
       <formula>$B$17=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>$B$35&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34064,17 +38116,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$B$82&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>$B$80&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="9" priority="12">
+    <cfRule type="expression" dxfId="8" priority="12">
       <formula>$B$49=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35400,17 +39452,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$B$82&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$B$80&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>$B$49=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36198,17 +40250,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36216,6 +40268,1664 @@
     <hyperlink ref="C1" location="Home!A1" display="Home!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R216"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="C1" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="8" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="8"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="51" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="53"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="56" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="57"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="56"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="57"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="124" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="57"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="56" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="57"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="56" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="57"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="125" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="57"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="56" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="57"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="57"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="56"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="57"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="124" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="57"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="56" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="57"/>
+    </row>
+    <row r="17" spans="2:16">
+      <c r="B17" s="56" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="57"/>
+    </row>
+    <row r="18" spans="2:16">
+      <c r="B18" s="125" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="57"/>
+    </row>
+    <row r="19" spans="2:16">
+      <c r="B19" s="56" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="57"/>
+    </row>
+    <row r="20" spans="2:16">
+      <c r="B20" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="57"/>
+    </row>
+    <row r="21" spans="2:16">
+      <c r="B21" s="56"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="57"/>
+    </row>
+    <row r="22" spans="2:16">
+      <c r="B22" s="124" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="57"/>
+    </row>
+    <row r="23" spans="2:16">
+      <c r="B23" s="56" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="57"/>
+    </row>
+    <row r="24" spans="2:16">
+      <c r="B24" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="57"/>
+    </row>
+    <row r="25" spans="2:16">
+      <c r="B25" s="56"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="57"/>
+    </row>
+    <row r="26" spans="2:16">
+      <c r="B26" s="56" t="s">
+        <v>232</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="57"/>
+    </row>
+    <row r="27" spans="2:16">
+      <c r="B27" s="56"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="57"/>
+    </row>
+    <row r="28" spans="2:16">
+      <c r="B28" s="124" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="57"/>
+    </row>
+    <row r="29" spans="2:16">
+      <c r="B29" s="124" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="57"/>
+    </row>
+    <row r="30" spans="2:16">
+      <c r="B30" s="124" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="57"/>
+    </row>
+    <row r="31" spans="2:16">
+      <c r="B31" s="56"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="57"/>
+    </row>
+    <row r="32" spans="2:16">
+      <c r="B32" s="124" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="57"/>
+      <c r="J32" s="118" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M32" s="118" t="s">
+        <v>1960</v>
+      </c>
+      <c r="P32" s="118" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18">
+      <c r="B33" s="56"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="57"/>
+      <c r="J33" s="51" t="s">
+        <v>2021</v>
+      </c>
+      <c r="K33" s="53"/>
+      <c r="M33" s="51" t="s">
+        <v>2029</v>
+      </c>
+      <c r="N33" s="53"/>
+      <c r="P33" s="51" t="s">
+        <v>1974</v>
+      </c>
+      <c r="Q33" s="53"/>
+    </row>
+    <row r="34" spans="2:18">
+      <c r="B34" s="56" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="57"/>
+      <c r="J34" s="56" t="s">
+        <v>2020</v>
+      </c>
+      <c r="K34" s="57"/>
+      <c r="M34" s="56" t="s">
+        <v>2026</v>
+      </c>
+      <c r="N34" s="57"/>
+      <c r="P34" s="54" t="s">
+        <v>1975</v>
+      </c>
+      <c r="Q34" s="55"/>
+    </row>
+    <row r="35" spans="2:18">
+      <c r="B35" s="124" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="57"/>
+      <c r="J35" s="56" t="s">
+        <v>2017</v>
+      </c>
+      <c r="K35" s="57"/>
+      <c r="M35" s="56" t="s">
+        <v>2025</v>
+      </c>
+      <c r="N35" s="57"/>
+    </row>
+    <row r="36" spans="2:18">
+      <c r="B36" s="124" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="57"/>
+      <c r="J36" s="56" t="s">
+        <v>2018</v>
+      </c>
+      <c r="K36" s="57"/>
+      <c r="M36" s="56" t="s">
+        <v>2027</v>
+      </c>
+      <c r="N36" s="57"/>
+    </row>
+    <row r="37" spans="2:18">
+      <c r="B37" s="124" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="57"/>
+      <c r="J37" s="54" t="s">
+        <v>2019</v>
+      </c>
+      <c r="K37" s="55"/>
+      <c r="M37" s="54" t="s">
+        <v>2028</v>
+      </c>
+      <c r="N37" s="55"/>
+    </row>
+    <row r="38" spans="2:18">
+      <c r="B38" s="56"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="57"/>
+    </row>
+    <row r="39" spans="2:18">
+      <c r="B39" s="56" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="57"/>
+    </row>
+    <row r="40" spans="2:18">
+      <c r="B40" s="124" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="57"/>
+      <c r="J40" s="118" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M40" s="118" t="s">
+        <v>1960</v>
+      </c>
+      <c r="P40" s="118" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18">
+      <c r="B41" s="124" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="57"/>
+      <c r="J41" s="51" t="s">
+        <v>2022</v>
+      </c>
+      <c r="K41" s="53"/>
+      <c r="M41" s="51" t="s">
+        <v>2023</v>
+      </c>
+      <c r="N41" s="53"/>
+      <c r="P41" s="51" t="s">
+        <v>2024</v>
+      </c>
+      <c r="Q41" s="52"/>
+      <c r="R41" s="53"/>
+    </row>
+    <row r="42" spans="2:18">
+      <c r="B42" s="124" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="57"/>
+      <c r="J42" s="56" t="s">
+        <v>2012</v>
+      </c>
+      <c r="K42" s="57"/>
+      <c r="M42" s="56" t="s">
+        <v>2016</v>
+      </c>
+      <c r="N42" s="57"/>
+      <c r="P42" s="121" t="s">
+        <v>1973</v>
+      </c>
+      <c r="Q42" s="18"/>
+      <c r="R42" s="57"/>
+    </row>
+    <row r="43" spans="2:18">
+      <c r="B43" s="56"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="57"/>
+      <c r="J43" s="56" t="s">
+        <v>2011</v>
+      </c>
+      <c r="K43" s="57"/>
+      <c r="M43" s="56" t="s">
+        <v>2015</v>
+      </c>
+      <c r="N43" s="57"/>
+      <c r="P43" s="54"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="55"/>
+    </row>
+    <row r="44" spans="2:18">
+      <c r="B44" s="56"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="57"/>
+      <c r="J44" s="56" t="s">
+        <v>2010</v>
+      </c>
+      <c r="K44" s="57"/>
+      <c r="M44" s="56" t="s">
+        <v>2014</v>
+      </c>
+      <c r="N44" s="57"/>
+    </row>
+    <row r="45" spans="2:18">
+      <c r="B45" s="56"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="57"/>
+      <c r="J45" s="54" t="s">
+        <v>2009</v>
+      </c>
+      <c r="K45" s="55"/>
+      <c r="M45" s="54" t="s">
+        <v>2013</v>
+      </c>
+      <c r="N45" s="55"/>
+    </row>
+    <row r="46" spans="2:18">
+      <c r="B46" s="56"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="57"/>
+    </row>
+    <row r="47" spans="2:18">
+      <c r="B47" s="56"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="57"/>
+    </row>
+    <row r="48" spans="2:18">
+      <c r="B48" s="56" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="57"/>
+      <c r="J48" s="118" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12">
+      <c r="B49" s="127" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="57"/>
+      <c r="J49" s="51" t="s">
+        <v>1972</v>
+      </c>
+      <c r="K49" s="52"/>
+      <c r="L49" s="53"/>
+    </row>
+    <row r="50" spans="2:12">
+      <c r="B50" s="56"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="57"/>
+      <c r="J50" s="56" t="s">
+        <v>1990</v>
+      </c>
+      <c r="K50" s="18"/>
+      <c r="L50" s="57"/>
+    </row>
+    <row r="51" spans="2:12">
+      <c r="B51" s="56"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="57"/>
+      <c r="J51" s="56" t="s">
+        <v>1986</v>
+      </c>
+      <c r="K51" s="18"/>
+      <c r="L51" s="57"/>
+    </row>
+    <row r="52" spans="2:12">
+      <c r="B52" s="56"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="57"/>
+      <c r="J52" s="56" t="s">
+        <v>1991</v>
+      </c>
+      <c r="K52" s="18"/>
+      <c r="L52" s="57"/>
+    </row>
+    <row r="53" spans="2:12">
+      <c r="B53" s="56"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="57"/>
+      <c r="J53" s="56" t="s">
+        <v>1992</v>
+      </c>
+      <c r="K53" s="18"/>
+      <c r="L53" s="57"/>
+    </row>
+    <row r="54" spans="2:12">
+      <c r="B54" s="56"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="57"/>
+      <c r="J54" s="122" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K54" s="7"/>
+      <c r="L54" s="55"/>
+    </row>
+    <row r="55" spans="2:12">
+      <c r="B55" s="56"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="57"/>
+    </row>
+    <row r="56" spans="2:12">
+      <c r="B56" s="56" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="57"/>
+    </row>
+    <row r="57" spans="2:12">
+      <c r="B57" s="124" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="57"/>
+      <c r="J57" s="118" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12">
+      <c r="B58" s="56"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="57"/>
+      <c r="J58" s="51" t="s">
+        <v>1989</v>
+      </c>
+      <c r="K58" s="52"/>
+      <c r="L58" s="53"/>
+    </row>
+    <row r="59" spans="2:12">
+      <c r="B59" s="56"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="57"/>
+      <c r="J59" s="56" t="s">
+        <v>1985</v>
+      </c>
+      <c r="K59" s="18"/>
+      <c r="L59" s="57"/>
+    </row>
+    <row r="60" spans="2:12">
+      <c r="B60" s="56"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="57"/>
+      <c r="J60" s="56" t="s">
+        <v>1986</v>
+      </c>
+      <c r="K60" s="18"/>
+      <c r="L60" s="57"/>
+    </row>
+    <row r="61" spans="2:12">
+      <c r="B61" s="56"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="57"/>
+      <c r="J61" s="56" t="s">
+        <v>1987</v>
+      </c>
+      <c r="K61" s="18"/>
+      <c r="L61" s="57"/>
+    </row>
+    <row r="62" spans="2:12">
+      <c r="B62" s="56"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="57"/>
+      <c r="J62" s="121" t="s">
+        <v>1988</v>
+      </c>
+      <c r="K62" s="18"/>
+      <c r="L62" s="57"/>
+    </row>
+    <row r="63" spans="2:12">
+      <c r="B63" s="56"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="57"/>
+      <c r="J63" s="119"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="55"/>
+    </row>
+    <row r="64" spans="2:12">
+      <c r="B64" s="56"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="57"/>
+    </row>
+    <row r="65" spans="2:18">
+      <c r="B65" s="124" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C65" s="63"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="57"/>
+      <c r="J65" s="118" t="s">
+        <v>1971</v>
+      </c>
+      <c r="O65" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18">
+      <c r="B66" s="121" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="57"/>
+      <c r="J66" s="51" t="s">
+        <v>1976</v>
+      </c>
+      <c r="K66" s="52"/>
+      <c r="L66" s="52"/>
+      <c r="M66" s="53"/>
+      <c r="O66" s="51" t="s">
+        <v>1976</v>
+      </c>
+      <c r="P66" s="52"/>
+      <c r="Q66" s="52"/>
+      <c r="R66" s="53"/>
+    </row>
+    <row r="67" spans="2:18">
+      <c r="B67" s="56"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="57"/>
+      <c r="J67" s="56" t="s">
+        <v>2032</v>
+      </c>
+      <c r="K67" s="18"/>
+      <c r="L67" s="18"/>
+      <c r="M67" s="57"/>
+      <c r="O67" s="56" t="s">
+        <v>2036</v>
+      </c>
+      <c r="P67" s="18"/>
+      <c r="Q67" s="18"/>
+      <c r="R67" s="57"/>
+    </row>
+    <row r="68" spans="2:18">
+      <c r="B68" s="56"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="57"/>
+      <c r="J68" s="56" t="s">
+        <v>2033</v>
+      </c>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
+      <c r="M68" s="57"/>
+      <c r="O68" s="56" t="s">
+        <v>2033</v>
+      </c>
+      <c r="P68" s="18"/>
+      <c r="Q68" s="18"/>
+      <c r="R68" s="57"/>
+    </row>
+    <row r="69" spans="2:18">
+      <c r="B69" s="56"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="57"/>
+      <c r="J69" s="56" t="s">
+        <v>2034</v>
+      </c>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
+      <c r="M69" s="57"/>
+      <c r="O69" s="56" t="s">
+        <v>2034</v>
+      </c>
+      <c r="P69" s="18"/>
+      <c r="Q69" s="18"/>
+      <c r="R69" s="57"/>
+    </row>
+    <row r="70" spans="2:18">
+      <c r="B70" s="56"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="57"/>
+      <c r="J70" s="54" t="s">
+        <v>2035</v>
+      </c>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="55"/>
+      <c r="O70" s="54" t="s">
+        <v>2035</v>
+      </c>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
+      <c r="R70" s="55"/>
+    </row>
+    <row r="71" spans="2:18">
+      <c r="B71" s="56"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="57"/>
+    </row>
+    <row r="72" spans="2:18">
+      <c r="B72" s="56" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="57"/>
+    </row>
+    <row r="73" spans="2:18">
+      <c r="B73" s="121" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="57"/>
+    </row>
+    <row r="74" spans="2:18">
+      <c r="B74" s="56"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="57"/>
+      <c r="J74" s="118" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18">
+      <c r="B75" s="56"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="57"/>
+      <c r="J75" s="51" t="s">
+        <v>1983</v>
+      </c>
+      <c r="K75" s="52"/>
+      <c r="L75" s="52"/>
+      <c r="M75" s="52"/>
+      <c r="N75" s="52"/>
+      <c r="O75" s="53"/>
+    </row>
+    <row r="76" spans="2:18">
+      <c r="B76" s="56"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="57"/>
+      <c r="J76" s="56" t="s">
+        <v>1980</v>
+      </c>
+      <c r="K76" s="18"/>
+      <c r="L76" s="18"/>
+      <c r="M76" s="18"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="57"/>
+    </row>
+    <row r="77" spans="2:18">
+      <c r="B77" s="56"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="57"/>
+      <c r="J77" s="56" t="s">
+        <v>1978</v>
+      </c>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="57"/>
+    </row>
+    <row r="78" spans="2:18">
+      <c r="B78" s="56"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="57"/>
+      <c r="J78" s="56" t="s">
+        <v>1981</v>
+      </c>
+      <c r="K78" s="18"/>
+      <c r="L78" s="18"/>
+      <c r="M78" s="18"/>
+      <c r="N78" s="18"/>
+      <c r="O78" s="57"/>
+    </row>
+    <row r="79" spans="2:18">
+      <c r="B79" s="56"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="57"/>
+      <c r="J79" s="54" t="s">
+        <v>1979</v>
+      </c>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+      <c r="M79" s="7"/>
+      <c r="N79" s="7"/>
+      <c r="O79" s="55"/>
+    </row>
+    <row r="80" spans="2:18">
+      <c r="B80" s="56"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="57"/>
+    </row>
+    <row r="81" spans="2:12">
+      <c r="B81" s="56" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="57"/>
+    </row>
+    <row r="82" spans="2:12">
+      <c r="B82" s="56" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="57"/>
+    </row>
+    <row r="83" spans="2:12">
+      <c r="B83" s="56" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="57"/>
+    </row>
+    <row r="84" spans="2:12">
+      <c r="B84" s="56"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="57"/>
+    </row>
+    <row r="85" spans="2:12">
+      <c r="B85" s="56" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="57"/>
+    </row>
+    <row r="86" spans="2:12">
+      <c r="B86" s="127" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="57"/>
+    </row>
+    <row r="87" spans="2:12">
+      <c r="B87" s="56"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="57"/>
+    </row>
+    <row r="88" spans="2:12">
+      <c r="B88" s="56" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="57"/>
+    </row>
+    <row r="89" spans="2:12">
+      <c r="B89" s="56" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="57"/>
+      <c r="H89" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="K89" s="120" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12">
+      <c r="B90" s="54" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="55"/>
+      <c r="H90" s="51" t="s">
+        <v>1996</v>
+      </c>
+      <c r="I90" s="53"/>
+      <c r="L90" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12">
+      <c r="H91" s="56" t="s">
+        <v>1997</v>
+      </c>
+      <c r="I91" s="57"/>
+    </row>
+    <row r="92" spans="2:12">
+      <c r="H92" s="56" t="s">
+        <v>1998</v>
+      </c>
+      <c r="I92" s="57"/>
+    </row>
+    <row r="93" spans="2:12">
+      <c r="H93" s="54" t="s">
+        <v>1999</v>
+      </c>
+      <c r="I93" s="55"/>
+    </row>
+    <row r="96" spans="2:12">
+      <c r="H96" t="s">
+        <v>2008</v>
+      </c>
+      <c r="K96" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="H97" s="123" t="s">
+        <v>2007</v>
+      </c>
+      <c r="I97" s="52"/>
+      <c r="J97" s="53"/>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="H98" s="56" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I98" s="18"/>
+      <c r="J98" s="57"/>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="H99" s="56" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I99" s="18"/>
+      <c r="J99" s="57"/>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="H100" s="56" t="s">
+        <v>2004</v>
+      </c>
+      <c r="I100" s="18"/>
+      <c r="J100" s="57"/>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="H101" s="54" t="s">
+        <v>2005</v>
+      </c>
+      <c r="I101" s="7"/>
+      <c r="J101" s="55"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="8" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="B107" s="126" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="B108" s="126"/>
+      <c r="C108" s="126" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="B110" s="126"/>
+      <c r="C110" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10">
+      <c r="C113" s="8" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="114" spans="2:10">
+      <c r="B114" s="8"/>
+      <c r="D114" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10">
+      <c r="B115" s="8"/>
+    </row>
+    <row r="116" spans="2:10">
+      <c r="D116" s="128" t="s">
+        <v>1960</v>
+      </c>
+      <c r="G116" s="128" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J116" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10">
+      <c r="D117" t="s">
+        <v>2042</v>
+      </c>
+      <c r="G117" t="s">
+        <v>2042</v>
+      </c>
+      <c r="J117" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10">
+      <c r="D118" t="s">
+        <v>2043</v>
+      </c>
+      <c r="G118" s="126" t="s">
+        <v>2051</v>
+      </c>
+      <c r="J118" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10">
+      <c r="D119" t="s">
+        <v>2044</v>
+      </c>
+      <c r="J119" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="120" spans="2:10">
+      <c r="J120" s="126" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10">
+      <c r="D121" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10">
+      <c r="C123" s="126" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10">
+      <c r="D125" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10">
+      <c r="D127" s="8" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10">
+      <c r="D128" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8">
+      <c r="D129" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8">
+      <c r="D130" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8">
+      <c r="D131" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8">
+      <c r="D133" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8">
+      <c r="B135" s="8" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8">
+      <c r="C136" s="126" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8">
+      <c r="C138" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="140" spans="2:8">
+      <c r="C140" s="8" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="141" spans="2:8">
+      <c r="D141" s="126" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="143" spans="2:8">
+      <c r="D143" s="8" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="144" spans="2:8">
+      <c r="E144" s="51" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F144" s="52"/>
+      <c r="G144" s="52"/>
+      <c r="H144" s="53"/>
+    </row>
+    <row r="145" spans="3:8">
+      <c r="E145" s="56" t="s">
+        <v>2061</v>
+      </c>
+      <c r="F145" s="18"/>
+      <c r="G145" s="18"/>
+      <c r="H145" s="57"/>
+    </row>
+    <row r="146" spans="3:8">
+      <c r="E146" s="56" t="s">
+        <v>2062</v>
+      </c>
+      <c r="F146" s="18"/>
+      <c r="G146" s="18"/>
+      <c r="H146" s="57"/>
+    </row>
+    <row r="147" spans="3:8">
+      <c r="E147" s="56" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F147" s="18"/>
+      <c r="G147" s="18"/>
+      <c r="H147" s="57"/>
+    </row>
+    <row r="148" spans="3:8">
+      <c r="E148" s="54" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="55"/>
+    </row>
+    <row r="150" spans="3:8">
+      <c r="D150" s="88" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="151" spans="3:8">
+      <c r="E151" s="88"/>
+    </row>
+    <row r="152" spans="3:8">
+      <c r="C152" s="8" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="154" spans="3:8">
+      <c r="D154" s="8" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="155" spans="3:8">
+      <c r="E155" s="51" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F155" s="52"/>
+      <c r="G155" s="53"/>
+    </row>
+    <row r="156" spans="3:8">
+      <c r="E156" s="56" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F156" s="18"/>
+      <c r="G156" s="57"/>
+    </row>
+    <row r="157" spans="3:8">
+      <c r="E157" s="56" t="s">
+        <v>2068</v>
+      </c>
+      <c r="F157" s="18"/>
+      <c r="G157" s="57"/>
+    </row>
+    <row r="158" spans="3:8">
+      <c r="E158" s="54" t="s">
+        <v>2067</v>
+      </c>
+      <c r="F158" s="7"/>
+      <c r="G158" s="55"/>
+    </row>
+    <row r="160" spans="3:8">
+      <c r="D160" s="88" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="E161" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="C165" s="126" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="167" spans="2:6">
+      <c r="C167" s="126" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="168" spans="2:6">
+      <c r="D168" s="51" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E168" s="52"/>
+      <c r="F168" s="53"/>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="D169" s="56" t="s">
+        <v>2077</v>
+      </c>
+      <c r="E169" s="18"/>
+      <c r="F169" s="57"/>
+    </row>
+    <row r="170" spans="2:6">
+      <c r="D170" s="54" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E170" s="7"/>
+      <c r="F170" s="55"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="D172" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="174" spans="2:6">
+      <c r="C174" s="126" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="D176" s="8" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="D177" s="51" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E177" s="52"/>
+      <c r="F177" s="53"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="D178" s="56" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E178" s="18"/>
+      <c r="F178" s="57"/>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="D179" s="54" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E179" s="7"/>
+      <c r="F179" s="55"/>
+    </row>
+    <row r="182" spans="2:6">
+      <c r="C182" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6">
+      <c r="C183" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="186" spans="2:6">
+      <c r="B186" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="187" spans="2:6">
+      <c r="C187" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="188" spans="2:6">
+      <c r="B188" s="126" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="C189" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="190" spans="2:6">
+      <c r="B190" s="126" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="191" spans="2:6">
+      <c r="C191" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="194" spans="2:5">
+      <c r="B194" s="8" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="195" spans="2:5">
+      <c r="B195" s="77" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E195" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5">
+      <c r="B196" s="77" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E196" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="197" spans="2:5">
+      <c r="B197" s="77" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E197" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="198" spans="2:5">
+      <c r="B198" s="77" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E198" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="199" spans="2:5">
+      <c r="B199" s="114" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E199" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="200" spans="2:5">
+      <c r="B200" s="114" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E200" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="201" spans="2:5">
+      <c r="B201" s="114" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E201" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="202" spans="2:5">
+      <c r="B202" s="118" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="203" spans="2:5">
+      <c r="B203" s="118" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="204" spans="2:5">
+      <c r="B204" s="118" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="205" spans="2:5">
+      <c r="B205" s="118" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="206" spans="2:5">
+      <c r="B206" s="118" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="207" spans="2:5">
+      <c r="B207" s="118" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="208" spans="2:5">
+      <c r="B208" s="118" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="209" spans="2:18">
+      <c r="B209" s="118" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="211" spans="2:18">
+      <c r="D211" t="s">
+        <v>2116</v>
+      </c>
+      <c r="F211" t="s">
+        <v>2115</v>
+      </c>
+      <c r="Q211" s="135" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="212" spans="2:18">
+      <c r="B212" s="131" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D212" s="130" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E212" s="98"/>
+      <c r="F212" s="133" t="s">
+        <v>1955</v>
+      </c>
+      <c r="G212" s="98"/>
+      <c r="Q212" s="129" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="213" spans="2:18">
+      <c r="B213" s="131" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C213" s="131" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D213" s="130" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E213" s="98"/>
+      <c r="F213" s="132" t="s">
+        <v>1960</v>
+      </c>
+      <c r="G213" s="55"/>
+      <c r="I213" s="133" t="s">
+        <v>2099</v>
+      </c>
+      <c r="J213" s="97"/>
+      <c r="K213" s="97"/>
+      <c r="L213" s="98"/>
+      <c r="N213" s="133" t="s">
+        <v>2100</v>
+      </c>
+      <c r="O213" s="98"/>
+    </row>
+    <row r="214" spans="2:18">
+      <c r="B214" s="131" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D214" s="130" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E214" s="98"/>
+      <c r="F214" s="129" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G214" s="98"/>
+      <c r="J214" s="134" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K214" s="18"/>
+      <c r="L214" s="18"/>
+      <c r="N214" s="135" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="215" spans="2:18">
+      <c r="J215" s="126" t="s">
+        <v>2039</v>
+      </c>
+      <c r="N215" s="126" t="s">
+        <v>2117</v>
+      </c>
+      <c r="Q215" s="133" t="s">
+        <v>2102</v>
+      </c>
+      <c r="R215" s="98"/>
+    </row>
+    <row r="216" spans="2:18">
+      <c r="Q216" s="126" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>#REF!=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>#REF!&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="C1" location="Home!A1" display="Home!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -38680,17 +44390,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="58" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="56" priority="10">
       <formula>$C$12=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38982,17 +44692,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="56" priority="2">
+    <cfRule type="expression" dxfId="55" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="55" priority="5">
+    <cfRule type="expression" dxfId="54" priority="5">
       <formula>$B$44&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="54" priority="6">
+    <cfRule type="expression" dxfId="53" priority="6">
       <formula>$B$42&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39369,17 +45079,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="53" priority="4">
+    <cfRule type="expression" dxfId="52" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="52" priority="3">
+    <cfRule type="expression" dxfId="51" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="51" priority="2">
+    <cfRule type="expression" dxfId="50" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39658,22 +45368,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="50" priority="4">
+    <cfRule type="expression" dxfId="49" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="49" priority="3">
+    <cfRule type="expression" dxfId="48" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="48" priority="2">
+    <cfRule type="expression" dxfId="47" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40043,22 +45753,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="46" priority="4">
+    <cfRule type="expression" dxfId="45" priority="4">
       <formula>$B$31&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="45" priority="3">
+    <cfRule type="expression" dxfId="44" priority="3">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="44" priority="2">
+    <cfRule type="expression" dxfId="43" priority="2">
       <formula>$B$11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>$B$29&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41378,17 +47088,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="42" priority="4">
+    <cfRule type="expression" dxfId="41" priority="4">
       <formula>$B$103&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="41" priority="3">
+    <cfRule type="expression" dxfId="40" priority="3">
       <formula>$B$101&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="40" priority="2">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>$B$83=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41529,22 +47239,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="39" priority="4">
+    <cfRule type="expression" dxfId="38" priority="4">
       <formula>$B$32&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="38" priority="3">
+    <cfRule type="expression" dxfId="37" priority="3">
       <formula>$B$30&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="37" priority="2">
+    <cfRule type="expression" dxfId="36" priority="2">
       <formula>$B$12=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>$B$30&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
